--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_sector_publico_e_instituciones.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_sector_publico_e_instituciones.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="datos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metadatos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="datos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="metadatos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -54,6 +54,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -346,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q265"/>
+  <dimension ref="A1:Q269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,7 +575,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -582,7 +655,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -657,7 +735,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -732,7 +815,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -807,7 +895,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -882,7 +975,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -957,7 +1055,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1135,12 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1215,12 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -1182,7 +1295,12 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -1257,7 +1375,12 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -1332,7 +1455,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -1407,7 +1535,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1615,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1695,12 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1775,12 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -1707,7 +1855,12 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -1782,7 +1935,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -1857,7 +2015,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -1932,7 +2095,12 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -2007,7 +2175,12 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2255,12 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -2157,7 +2335,12 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -2232,7 +2415,12 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2495,12 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2575,12 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -2457,7 +2655,12 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -2532,7 +2735,12 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -2607,7 +2815,12 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -2682,7 +2895,12 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2975,12 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -2832,7 +3055,12 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -2907,7 +3135,12 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -2982,7 +3215,12 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3295,12 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -3132,7 +3375,12 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3455,12 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3535,12 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -3357,7 +3615,12 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -3432,7 +3695,12 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -3507,7 +3775,12 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -3582,7 +3855,12 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -3657,7 +3935,12 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -3732,7 +4015,12 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -3807,7 +4095,12 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -3882,7 +4175,12 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -3957,7 +4255,12 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -4032,7 +4335,12 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -4107,7 +4415,12 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -4182,7 +4495,12 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -4257,7 +4575,12 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -4332,7 +4655,12 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -4407,7 +4735,12 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -4482,7 +4815,12 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -4557,7 +4895,12 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -4632,7 +4975,12 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -4707,7 +5055,12 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -4782,7 +5135,12 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -4857,7 +5215,12 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -4932,7 +5295,12 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -5007,7 +5375,12 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -5082,7 +5455,12 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -5157,7 +5535,12 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -5232,7 +5615,12 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -5307,7 +5695,12 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5775,12 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -5418,7 +5816,7 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>1960</v>
+        <v>2026</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -5432,22 +5830,22 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Ingresos públicos</t>
+          <t>Deuda pública</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>ingresos_publicos</t>
+          <t>deuda_publica</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>GC.REV.XGRT.GD.ZS</t>
+          <t>GC.DOD.TOTL.GD.ZS</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Ingresos públicos excluidas donaciones como porcentaje del PIB</t>
+          <t>Deuda del gobierno central como porcentaje del PIB</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -5457,7 +5855,12 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
         </is>
       </c>
     </row>
@@ -5493,7 +5896,7 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -5532,7 +5935,12 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -5568,7 +5976,7 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -5607,7 +6015,12 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -5643,7 +6056,7 @@
         </is>
       </c>
       <c r="G71" t="n">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -5682,7 +6095,12 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -5718,7 +6136,7 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -5757,7 +6175,12 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -5793,7 +6216,7 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -5832,7 +6255,12 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -5868,7 +6296,7 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -5907,7 +6335,12 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -5943,7 +6376,7 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -5982,7 +6415,12 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -6018,7 +6456,7 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -6057,7 +6495,12 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -6093,7 +6536,7 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -6132,7 +6575,12 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -6168,7 +6616,7 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -6207,7 +6655,12 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -6243,7 +6696,7 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -6282,7 +6735,12 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -6318,7 +6776,7 @@
         </is>
       </c>
       <c r="G80" t="n">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -6357,7 +6815,12 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6856,7 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -6432,7 +6895,12 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6936,7 @@
         </is>
       </c>
       <c r="G82" t="n">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -6507,7 +6975,12 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -6543,7 +7016,7 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -6582,7 +7055,12 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -6618,7 +7096,7 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -6657,7 +7135,12 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -6693,7 +7176,7 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -6732,7 +7215,12 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -6768,7 +7256,7 @@
         </is>
       </c>
       <c r="G86" t="n">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -6807,7 +7295,12 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -6843,7 +7336,7 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -6882,7 +7375,12 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -6918,7 +7416,7 @@
         </is>
       </c>
       <c r="G88" t="n">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -6957,7 +7455,12 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -6993,7 +7496,7 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -7032,7 +7535,12 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -7068,7 +7576,7 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -7107,7 +7615,12 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -7143,7 +7656,7 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -7182,7 +7695,12 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -7218,7 +7736,7 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -7257,7 +7775,12 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -7293,7 +7816,7 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -7332,7 +7855,12 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -7368,7 +7896,7 @@
         </is>
       </c>
       <c r="G94" t="n">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -7407,7 +7935,12 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -7443,7 +7976,7 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -7482,7 +8015,12 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -7518,7 +8056,7 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -7557,7 +8095,12 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -7593,7 +8136,7 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -7632,7 +8175,12 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -7668,7 +8216,7 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -7707,7 +8255,12 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -7743,7 +8296,7 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -7782,7 +8335,12 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -7818,7 +8376,7 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -7857,7 +8415,12 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -7893,7 +8456,7 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -7932,7 +8495,12 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -7968,7 +8536,7 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -8007,7 +8575,12 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -8043,7 +8616,7 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -8082,7 +8655,12 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -8118,7 +8696,7 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -8157,7 +8735,12 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -8193,7 +8776,7 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -8232,7 +8815,12 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -8268,7 +8856,7 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -8307,7 +8895,12 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8936,7 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -8382,7 +8975,12 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -8418,7 +9016,7 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -8457,7 +9055,12 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -8493,7 +9096,7 @@
         </is>
       </c>
       <c r="G109" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -8532,7 +9135,12 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -8568,7 +9176,7 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -8607,7 +9215,12 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -8643,7 +9256,7 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -8682,7 +9295,12 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -8718,7 +9336,7 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -8757,7 +9375,12 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -8793,7 +9416,7 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -8832,7 +9455,12 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -8868,7 +9496,7 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -8907,7 +9535,12 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -8943,7 +9576,7 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -8982,7 +9615,12 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -9018,7 +9656,7 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -9057,7 +9695,12 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -9093,7 +9736,7 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -9132,7 +9775,12 @@
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -9168,7 +9816,7 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -9207,7 +9855,12 @@
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -9243,7 +9896,7 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -9282,7 +9935,12 @@
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -9318,7 +9976,7 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -9357,7 +10015,12 @@
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -9393,7 +10056,7 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -9432,7 +10095,12 @@
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -9468,7 +10136,7 @@
         </is>
       </c>
       <c r="G122" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -9507,7 +10175,12 @@
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -9543,7 +10216,7 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -9582,7 +10255,12 @@
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -9618,7 +10296,7 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -9657,7 +10335,12 @@
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -9693,7 +10376,7 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -9732,7 +10415,12 @@
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -9768,7 +10456,7 @@
         </is>
       </c>
       <c r="G126" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -9807,7 +10495,12 @@
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -9843,7 +10536,7 @@
         </is>
       </c>
       <c r="G127" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -9882,7 +10575,12 @@
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -9918,7 +10616,7 @@
         </is>
       </c>
       <c r="G128" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -9957,7 +10655,12 @@
       </c>
       <c r="P128" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -9993,7 +10696,7 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
@@ -10032,7 +10735,12 @@
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -10068,7 +10776,7 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -10107,7 +10815,12 @@
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -10143,7 +10856,7 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -10182,7 +10895,12 @@
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -10218,7 +10936,7 @@
         </is>
       </c>
       <c r="G132" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -10257,7 +10975,12 @@
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -10293,7 +11016,7 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -10332,7 +11055,12 @@
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -10368,7 +11096,7 @@
         </is>
       </c>
       <c r="G134" t="n">
-        <v>1960</v>
+        <v>2025</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -10382,22 +11110,22 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Fiscalidad</t>
+          <t>Ingresos públicos</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>fiscalidad</t>
+          <t>ingresos_publicos</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>GC.TAX.TOTL.GD.ZS</t>
+          <t>GC.REV.XGRT.GD.ZS</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Ingresos tributarios como porcentaje del PIB</t>
+          <t>Ingresos públicos excluidas donaciones como porcentaje del PIB</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
@@ -10407,7 +11135,12 @@
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -10443,7 +11176,7 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>1961</v>
+        <v>2026</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -10457,22 +11190,22 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Fiscalidad</t>
+          <t>Ingresos públicos</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>fiscalidad</t>
+          <t>ingresos_publicos</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>GC.TAX.TOTL.GD.ZS</t>
+          <t>GC.REV.XGRT.GD.ZS</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Ingresos tributarios como porcentaje del PIB</t>
+          <t>Ingresos públicos excluidas donaciones como porcentaje del PIB</t>
         </is>
       </c>
       <c r="O135" t="inlineStr">
@@ -10482,7 +11215,12 @@
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -10518,7 +11256,7 @@
         </is>
       </c>
       <c r="G136" t="n">
-        <v>1962</v>
+        <v>1960</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -10557,7 +11295,12 @@
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -10593,7 +11336,7 @@
         </is>
       </c>
       <c r="G137" t="n">
-        <v>1963</v>
+        <v>1961</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -10632,7 +11375,12 @@
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -10668,7 +11416,7 @@
         </is>
       </c>
       <c r="G138" t="n">
-        <v>1964</v>
+        <v>1962</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -10707,7 +11455,12 @@
       </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -10743,7 +11496,7 @@
         </is>
       </c>
       <c r="G139" t="n">
-        <v>1965</v>
+        <v>1963</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -10782,7 +11535,12 @@
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -10818,7 +11576,7 @@
         </is>
       </c>
       <c r="G140" t="n">
-        <v>1966</v>
+        <v>1964</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -10857,7 +11615,12 @@
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -10893,7 +11656,7 @@
         </is>
       </c>
       <c r="G141" t="n">
-        <v>1967</v>
+        <v>1965</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -10932,7 +11695,12 @@
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -10968,7 +11736,7 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>1968</v>
+        <v>1966</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -11007,7 +11775,12 @@
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -11043,7 +11816,7 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>1969</v>
+        <v>1967</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -11082,7 +11855,12 @@
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -11118,7 +11896,7 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -11157,7 +11935,12 @@
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -11193,7 +11976,7 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>1971</v>
+        <v>1969</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -11232,7 +12015,12 @@
       </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -11268,7 +12056,7 @@
         </is>
       </c>
       <c r="G146" t="n">
-        <v>1972</v>
+        <v>1970</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -11307,7 +12095,12 @@
       </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -11343,7 +12136,7 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>1973</v>
+        <v>1971</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -11382,7 +12175,12 @@
       </c>
       <c r="P147" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -11418,7 +12216,7 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>1974</v>
+        <v>1972</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -11457,7 +12255,12 @@
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -11493,7 +12296,7 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -11532,7 +12335,12 @@
       </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -11568,7 +12376,7 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>1976</v>
+        <v>1974</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -11607,7 +12415,12 @@
       </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -11643,7 +12456,7 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>1977</v>
+        <v>1975</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -11682,7 +12495,12 @@
       </c>
       <c r="P151" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -11718,7 +12536,7 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>1978</v>
+        <v>1976</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -11757,7 +12575,12 @@
       </c>
       <c r="P152" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -11793,7 +12616,7 @@
         </is>
       </c>
       <c r="G153" t="n">
-        <v>1979</v>
+        <v>1977</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -11832,7 +12655,12 @@
       </c>
       <c r="P153" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -11868,7 +12696,7 @@
         </is>
       </c>
       <c r="G154" t="n">
-        <v>1980</v>
+        <v>1978</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -11907,7 +12735,12 @@
       </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -11943,7 +12776,7 @@
         </is>
       </c>
       <c r="G155" t="n">
-        <v>1981</v>
+        <v>1979</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -11982,7 +12815,12 @@
       </c>
       <c r="P155" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -12018,7 +12856,7 @@
         </is>
       </c>
       <c r="G156" t="n">
-        <v>1982</v>
+        <v>1980</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -12057,7 +12895,12 @@
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -12093,7 +12936,7 @@
         </is>
       </c>
       <c r="G157" t="n">
-        <v>1983</v>
+        <v>1981</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -12132,7 +12975,12 @@
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -12168,7 +13016,7 @@
         </is>
       </c>
       <c r="G158" t="n">
-        <v>1984</v>
+        <v>1982</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
@@ -12207,7 +13055,12 @@
       </c>
       <c r="P158" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -12243,7 +13096,7 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>1985</v>
+        <v>1983</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
@@ -12282,7 +13135,12 @@
       </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -12318,7 +13176,7 @@
         </is>
       </c>
       <c r="G160" t="n">
-        <v>1986</v>
+        <v>1984</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
@@ -12357,7 +13215,12 @@
       </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -12393,7 +13256,7 @@
         </is>
       </c>
       <c r="G161" t="n">
-        <v>1987</v>
+        <v>1985</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
@@ -12432,7 +13295,12 @@
       </c>
       <c r="P161" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -12468,7 +13336,7 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>1988</v>
+        <v>1986</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
@@ -12507,7 +13375,12 @@
       </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -12543,7 +13416,7 @@
         </is>
       </c>
       <c r="G163" t="n">
-        <v>1989</v>
+        <v>1987</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
@@ -12582,7 +13455,12 @@
       </c>
       <c r="P163" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -12618,7 +13496,7 @@
         </is>
       </c>
       <c r="G164" t="n">
-        <v>1990</v>
+        <v>1988</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
@@ -12657,7 +13535,12 @@
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -12693,7 +13576,7 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>1991</v>
+        <v>1989</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -12732,7 +13615,12 @@
       </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -12768,7 +13656,7 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>1992</v>
+        <v>1990</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -12807,7 +13695,12 @@
       </c>
       <c r="P166" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -12843,7 +13736,7 @@
         </is>
       </c>
       <c r="G167" t="n">
-        <v>1993</v>
+        <v>1991</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
@@ -12882,7 +13775,12 @@
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -12918,7 +13816,7 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>1994</v>
+        <v>1992</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
@@ -12957,7 +13855,12 @@
       </c>
       <c r="P168" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -12993,7 +13896,7 @@
         </is>
       </c>
       <c r="G169" t="n">
-        <v>1995</v>
+        <v>1993</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
@@ -13032,7 +13935,12 @@
       </c>
       <c r="P169" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -13068,7 +13976,7 @@
         </is>
       </c>
       <c r="G170" t="n">
-        <v>1996</v>
+        <v>1994</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
@@ -13107,7 +14015,12 @@
       </c>
       <c r="P170" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -13143,7 +14056,7 @@
         </is>
       </c>
       <c r="G171" t="n">
-        <v>1997</v>
+        <v>1995</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
@@ -13182,7 +14095,12 @@
       </c>
       <c r="P171" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -13218,7 +14136,7 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>1998</v>
+        <v>1996</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
@@ -13257,7 +14175,12 @@
       </c>
       <c r="P172" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -13293,7 +14216,7 @@
         </is>
       </c>
       <c r="G173" t="n">
-        <v>1999</v>
+        <v>1997</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
@@ -13332,7 +14255,12 @@
       </c>
       <c r="P173" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -13368,7 +14296,7 @@
         </is>
       </c>
       <c r="G174" t="n">
-        <v>2000</v>
+        <v>1998</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
@@ -13407,7 +14335,12 @@
       </c>
       <c r="P174" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -13443,7 +14376,7 @@
         </is>
       </c>
       <c r="G175" t="n">
-        <v>2001</v>
+        <v>1999</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
@@ -13482,7 +14415,12 @@
       </c>
       <c r="P175" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -13518,7 +14456,7 @@
         </is>
       </c>
       <c r="G176" t="n">
-        <v>2002</v>
+        <v>2000</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
@@ -13557,7 +14495,12 @@
       </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -13593,7 +14536,7 @@
         </is>
       </c>
       <c r="G177" t="n">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
@@ -13632,7 +14575,12 @@
       </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -13668,7 +14616,7 @@
         </is>
       </c>
       <c r="G178" t="n">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
@@ -13707,7 +14655,12 @@
       </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -13743,7 +14696,7 @@
         </is>
       </c>
       <c r="G179" t="n">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
@@ -13782,7 +14735,12 @@
       </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -13818,7 +14776,7 @@
         </is>
       </c>
       <c r="G180" t="n">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
@@ -13857,7 +14815,12 @@
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -13893,7 +14856,7 @@
         </is>
       </c>
       <c r="G181" t="n">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
@@ -13932,7 +14895,12 @@
       </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -13968,7 +14936,7 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
@@ -14007,7 +14975,12 @@
       </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -14043,7 +15016,7 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
@@ -14082,7 +15055,12 @@
       </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -14118,7 +15096,7 @@
         </is>
       </c>
       <c r="G184" t="n">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
@@ -14157,7 +15135,12 @@
       </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -14193,7 +15176,7 @@
         </is>
       </c>
       <c r="G185" t="n">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
@@ -14232,7 +15215,12 @@
       </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -14268,7 +15256,7 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
@@ -14307,7 +15295,12 @@
       </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -14343,7 +15336,7 @@
         </is>
       </c>
       <c r="G187" t="n">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
@@ -14382,7 +15375,12 @@
       </c>
       <c r="P187" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -14418,7 +15416,7 @@
         </is>
       </c>
       <c r="G188" t="n">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
@@ -14457,7 +15455,12 @@
       </c>
       <c r="P188" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -14493,7 +15496,7 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
@@ -14532,7 +15535,12 @@
       </c>
       <c r="P189" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -14568,7 +15576,7 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="H190" t="inlineStr">
         <is>
@@ -14607,7 +15615,12 @@
       </c>
       <c r="P190" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -14643,7 +15656,7 @@
         </is>
       </c>
       <c r="G191" t="n">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
@@ -14682,7 +15695,12 @@
       </c>
       <c r="P191" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -14718,7 +15736,7 @@
         </is>
       </c>
       <c r="G192" t="n">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
@@ -14757,7 +15775,12 @@
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -14793,7 +15816,7 @@
         </is>
       </c>
       <c r="G193" t="n">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
@@ -14832,7 +15855,12 @@
       </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -14868,7 +15896,7 @@
         </is>
       </c>
       <c r="G194" t="n">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
@@ -14907,7 +15935,12 @@
       </c>
       <c r="P194" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -14943,7 +15976,7 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
@@ -14982,7 +16015,12 @@
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -15018,7 +16056,7 @@
         </is>
       </c>
       <c r="G196" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="H196" t="inlineStr">
         <is>
@@ -15057,7 +16095,12 @@
       </c>
       <c r="P196" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -15093,7 +16136,7 @@
         </is>
       </c>
       <c r="G197" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
@@ -15132,7 +16175,12 @@
       </c>
       <c r="P197" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -15168,7 +16216,7 @@
         </is>
       </c>
       <c r="G198" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
@@ -15207,7 +16255,12 @@
       </c>
       <c r="P198" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -15243,7 +16296,7 @@
         </is>
       </c>
       <c r="G199" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
@@ -15282,7 +16335,12 @@
       </c>
       <c r="P199" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -15318,7 +16376,7 @@
         </is>
       </c>
       <c r="G200" t="n">
-        <v>1960</v>
+        <v>2024</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
@@ -15332,22 +16390,22 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>Gasto público</t>
+          <t>Fiscalidad</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>gasto_publico</t>
+          <t>fiscalidad</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>GC.XPN.TOTL.GD.ZS</t>
+          <t>GC.TAX.TOTL.GD.ZS</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Gasto público como porcentaje del PIB</t>
+          <t>Ingresos tributarios como porcentaje del PIB</t>
         </is>
       </c>
       <c r="O200" t="inlineStr">
@@ -15357,7 +16415,12 @@
       </c>
       <c r="P200" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -15393,7 +16456,7 @@
         </is>
       </c>
       <c r="G201" t="n">
-        <v>1961</v>
+        <v>2025</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
@@ -15407,22 +16470,22 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>Gasto público</t>
+          <t>Fiscalidad</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>gasto_publico</t>
+          <t>fiscalidad</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>GC.XPN.TOTL.GD.ZS</t>
+          <t>GC.TAX.TOTL.GD.ZS</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Gasto público como porcentaje del PIB</t>
+          <t>Ingresos tributarios como porcentaje del PIB</t>
         </is>
       </c>
       <c r="O201" t="inlineStr">
@@ -15432,7 +16495,12 @@
       </c>
       <c r="P201" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -15468,7 +16536,7 @@
         </is>
       </c>
       <c r="G202" t="n">
-        <v>1962</v>
+        <v>2026</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
@@ -15482,22 +16550,22 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>Gasto público</t>
+          <t>Fiscalidad</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>gasto_publico</t>
+          <t>fiscalidad</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>GC.XPN.TOTL.GD.ZS</t>
+          <t>GC.TAX.TOTL.GD.ZS</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Gasto público como porcentaje del PIB</t>
+          <t>Ingresos tributarios como porcentaje del PIB</t>
         </is>
       </c>
       <c r="O202" t="inlineStr">
@@ -15507,7 +16575,12 @@
       </c>
       <c r="P202" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -15543,7 +16616,7 @@
         </is>
       </c>
       <c r="G203" t="n">
-        <v>1963</v>
+        <v>1960</v>
       </c>
       <c r="H203" t="inlineStr">
         <is>
@@ -15582,7 +16655,12 @@
       </c>
       <c r="P203" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -15618,7 +16696,7 @@
         </is>
       </c>
       <c r="G204" t="n">
-        <v>1964</v>
+        <v>1961</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
@@ -15657,7 +16735,12 @@
       </c>
       <c r="P204" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -15693,7 +16776,7 @@
         </is>
       </c>
       <c r="G205" t="n">
-        <v>1965</v>
+        <v>1962</v>
       </c>
       <c r="H205" t="inlineStr">
         <is>
@@ -15732,7 +16815,12 @@
       </c>
       <c r="P205" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -15768,7 +16856,7 @@
         </is>
       </c>
       <c r="G206" t="n">
-        <v>1966</v>
+        <v>1963</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
@@ -15807,7 +16895,12 @@
       </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -15843,7 +16936,7 @@
         </is>
       </c>
       <c r="G207" t="n">
-        <v>1967</v>
+        <v>1964</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
@@ -15882,7 +16975,12 @@
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -15918,7 +17016,7 @@
         </is>
       </c>
       <c r="G208" t="n">
-        <v>1968</v>
+        <v>1965</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
@@ -15957,7 +17055,12 @@
       </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -15993,7 +17096,7 @@
         </is>
       </c>
       <c r="G209" t="n">
-        <v>1969</v>
+        <v>1966</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
@@ -16032,7 +17135,12 @@
       </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -16068,7 +17176,7 @@
         </is>
       </c>
       <c r="G210" t="n">
-        <v>1970</v>
+        <v>1967</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
@@ -16107,7 +17215,12 @@
       </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -16143,7 +17256,7 @@
         </is>
       </c>
       <c r="G211" t="n">
-        <v>1971</v>
+        <v>1968</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
@@ -16182,7 +17295,12 @@
       </c>
       <c r="P211" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -16218,7 +17336,7 @@
         </is>
       </c>
       <c r="G212" t="n">
-        <v>1972</v>
+        <v>1969</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
@@ -16257,7 +17375,12 @@
       </c>
       <c r="P212" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -16293,7 +17416,7 @@
         </is>
       </c>
       <c r="G213" t="n">
-        <v>1973</v>
+        <v>1970</v>
       </c>
       <c r="H213" t="inlineStr">
         <is>
@@ -16332,7 +17455,12 @@
       </c>
       <c r="P213" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -16368,7 +17496,7 @@
         </is>
       </c>
       <c r="G214" t="n">
-        <v>1974</v>
+        <v>1971</v>
       </c>
       <c r="H214" t="inlineStr">
         <is>
@@ -16407,7 +17535,12 @@
       </c>
       <c r="P214" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -16443,7 +17576,7 @@
         </is>
       </c>
       <c r="G215" t="n">
-        <v>1975</v>
+        <v>1972</v>
       </c>
       <c r="H215" t="inlineStr">
         <is>
@@ -16482,7 +17615,12 @@
       </c>
       <c r="P215" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -16518,7 +17656,7 @@
         </is>
       </c>
       <c r="G216" t="n">
-        <v>1976</v>
+        <v>1973</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
@@ -16557,7 +17695,12 @@
       </c>
       <c r="P216" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -16593,7 +17736,7 @@
         </is>
       </c>
       <c r="G217" t="n">
-        <v>1977</v>
+        <v>1974</v>
       </c>
       <c r="H217" t="inlineStr">
         <is>
@@ -16632,7 +17775,12 @@
       </c>
       <c r="P217" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -16668,7 +17816,7 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>1978</v>
+        <v>1975</v>
       </c>
       <c r="H218" t="inlineStr">
         <is>
@@ -16707,7 +17855,12 @@
       </c>
       <c r="P218" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -16743,7 +17896,7 @@
         </is>
       </c>
       <c r="G219" t="n">
-        <v>1979</v>
+        <v>1976</v>
       </c>
       <c r="H219" t="inlineStr">
         <is>
@@ -16782,7 +17935,12 @@
       </c>
       <c r="P219" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -16818,7 +17976,7 @@
         </is>
       </c>
       <c r="G220" t="n">
-        <v>1980</v>
+        <v>1977</v>
       </c>
       <c r="H220" t="inlineStr">
         <is>
@@ -16857,7 +18015,12 @@
       </c>
       <c r="P220" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -16893,7 +18056,7 @@
         </is>
       </c>
       <c r="G221" t="n">
-        <v>1981</v>
+        <v>1978</v>
       </c>
       <c r="H221" t="inlineStr">
         <is>
@@ -16932,7 +18095,12 @@
       </c>
       <c r="P221" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -16968,7 +18136,7 @@
         </is>
       </c>
       <c r="G222" t="n">
-        <v>1982</v>
+        <v>1979</v>
       </c>
       <c r="H222" t="inlineStr">
         <is>
@@ -17007,7 +18175,12 @@
       </c>
       <c r="P222" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -17043,7 +18216,7 @@
         </is>
       </c>
       <c r="G223" t="n">
-        <v>1983</v>
+        <v>1980</v>
       </c>
       <c r="H223" t="inlineStr">
         <is>
@@ -17082,7 +18255,12 @@
       </c>
       <c r="P223" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -17118,7 +18296,7 @@
         </is>
       </c>
       <c r="G224" t="n">
-        <v>1984</v>
+        <v>1981</v>
       </c>
       <c r="H224" t="inlineStr">
         <is>
@@ -17157,7 +18335,12 @@
       </c>
       <c r="P224" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -17193,7 +18376,7 @@
         </is>
       </c>
       <c r="G225" t="n">
-        <v>1985</v>
+        <v>1982</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
@@ -17232,7 +18415,12 @@
       </c>
       <c r="P225" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -17268,7 +18456,7 @@
         </is>
       </c>
       <c r="G226" t="n">
-        <v>1986</v>
+        <v>1983</v>
       </c>
       <c r="H226" t="inlineStr">
         <is>
@@ -17307,7 +18495,12 @@
       </c>
       <c r="P226" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -17343,7 +18536,7 @@
         </is>
       </c>
       <c r="G227" t="n">
-        <v>1987</v>
+        <v>1984</v>
       </c>
       <c r="H227" t="inlineStr">
         <is>
@@ -17382,7 +18575,12 @@
       </c>
       <c r="P227" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -17418,7 +18616,7 @@
         </is>
       </c>
       <c r="G228" t="n">
-        <v>1988</v>
+        <v>1985</v>
       </c>
       <c r="H228" t="inlineStr">
         <is>
@@ -17457,7 +18655,12 @@
       </c>
       <c r="P228" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -17493,7 +18696,7 @@
         </is>
       </c>
       <c r="G229" t="n">
-        <v>1989</v>
+        <v>1986</v>
       </c>
       <c r="H229" t="inlineStr">
         <is>
@@ -17532,7 +18735,12 @@
       </c>
       <c r="P229" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -17568,7 +18776,7 @@
         </is>
       </c>
       <c r="G230" t="n">
-        <v>1990</v>
+        <v>1987</v>
       </c>
       <c r="H230" t="inlineStr">
         <is>
@@ -17607,7 +18815,12 @@
       </c>
       <c r="P230" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -17643,7 +18856,7 @@
         </is>
       </c>
       <c r="G231" t="n">
-        <v>1991</v>
+        <v>1988</v>
       </c>
       <c r="H231" t="inlineStr">
         <is>
@@ -17682,7 +18895,12 @@
       </c>
       <c r="P231" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -17718,7 +18936,7 @@
         </is>
       </c>
       <c r="G232" t="n">
-        <v>1992</v>
+        <v>1989</v>
       </c>
       <c r="H232" t="inlineStr">
         <is>
@@ -17757,7 +18975,12 @@
       </c>
       <c r="P232" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -17793,7 +19016,7 @@
         </is>
       </c>
       <c r="G233" t="n">
-        <v>1993</v>
+        <v>1990</v>
       </c>
       <c r="H233" t="inlineStr">
         <is>
@@ -17832,7 +19055,12 @@
       </c>
       <c r="P233" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -17868,7 +19096,7 @@
         </is>
       </c>
       <c r="G234" t="n">
-        <v>1994</v>
+        <v>1991</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
@@ -17907,7 +19135,12 @@
       </c>
       <c r="P234" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -17943,7 +19176,7 @@
         </is>
       </c>
       <c r="G235" t="n">
-        <v>1995</v>
+        <v>1992</v>
       </c>
       <c r="H235" t="inlineStr">
         <is>
@@ -17982,7 +19215,12 @@
       </c>
       <c r="P235" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -18018,7 +19256,7 @@
         </is>
       </c>
       <c r="G236" t="n">
-        <v>1996</v>
+        <v>1993</v>
       </c>
       <c r="H236" t="inlineStr">
         <is>
@@ -18057,7 +19295,12 @@
       </c>
       <c r="P236" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q236" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -18093,7 +19336,7 @@
         </is>
       </c>
       <c r="G237" t="n">
-        <v>1997</v>
+        <v>1994</v>
       </c>
       <c r="H237" t="inlineStr">
         <is>
@@ -18132,7 +19375,12 @@
       </c>
       <c r="P237" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q237" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -18168,7 +19416,7 @@
         </is>
       </c>
       <c r="G238" t="n">
-        <v>1998</v>
+        <v>1995</v>
       </c>
       <c r="H238" t="inlineStr">
         <is>
@@ -18207,7 +19455,12 @@
       </c>
       <c r="P238" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q238" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -18243,7 +19496,7 @@
         </is>
       </c>
       <c r="G239" t="n">
-        <v>1999</v>
+        <v>1996</v>
       </c>
       <c r="H239" t="inlineStr">
         <is>
@@ -18282,7 +19535,12 @@
       </c>
       <c r="P239" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q239" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -18318,7 +19576,7 @@
         </is>
       </c>
       <c r="G240" t="n">
-        <v>2000</v>
+        <v>1997</v>
       </c>
       <c r="H240" t="inlineStr">
         <is>
@@ -18357,7 +19615,12 @@
       </c>
       <c r="P240" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q240" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -18393,7 +19656,7 @@
         </is>
       </c>
       <c r="G241" t="n">
-        <v>2001</v>
+        <v>1998</v>
       </c>
       <c r="H241" t="inlineStr">
         <is>
@@ -18432,7 +19695,12 @@
       </c>
       <c r="P241" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q241" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -18468,7 +19736,7 @@
         </is>
       </c>
       <c r="G242" t="n">
-        <v>2002</v>
+        <v>1999</v>
       </c>
       <c r="H242" t="inlineStr">
         <is>
@@ -18507,7 +19775,12 @@
       </c>
       <c r="P242" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q242" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -18543,7 +19816,7 @@
         </is>
       </c>
       <c r="G243" t="n">
-        <v>2003</v>
+        <v>2000</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
@@ -18582,7 +19855,12 @@
       </c>
       <c r="P243" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q243" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -18618,7 +19896,7 @@
         </is>
       </c>
       <c r="G244" t="n">
-        <v>2004</v>
+        <v>2001</v>
       </c>
       <c r="H244" t="inlineStr">
         <is>
@@ -18657,7 +19935,12 @@
       </c>
       <c r="P244" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q244" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -18693,7 +19976,7 @@
         </is>
       </c>
       <c r="G245" t="n">
-        <v>2005</v>
+        <v>2002</v>
       </c>
       <c r="H245" t="inlineStr">
         <is>
@@ -18732,7 +20015,12 @@
       </c>
       <c r="P245" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q245" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -18768,7 +20056,7 @@
         </is>
       </c>
       <c r="G246" t="n">
-        <v>2006</v>
+        <v>2003</v>
       </c>
       <c r="H246" t="inlineStr">
         <is>
@@ -18807,7 +20095,12 @@
       </c>
       <c r="P246" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q246" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -18843,7 +20136,7 @@
         </is>
       </c>
       <c r="G247" t="n">
-        <v>2007</v>
+        <v>2004</v>
       </c>
       <c r="H247" t="inlineStr">
         <is>
@@ -18882,7 +20175,12 @@
       </c>
       <c r="P247" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q247" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -18918,7 +20216,7 @@
         </is>
       </c>
       <c r="G248" t="n">
-        <v>2008</v>
+        <v>2005</v>
       </c>
       <c r="H248" t="inlineStr">
         <is>
@@ -18957,7 +20255,12 @@
       </c>
       <c r="P248" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q248" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -18993,7 +20296,7 @@
         </is>
       </c>
       <c r="G249" t="n">
-        <v>2009</v>
+        <v>2006</v>
       </c>
       <c r="H249" t="inlineStr">
         <is>
@@ -19032,7 +20335,12 @@
       </c>
       <c r="P249" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q249" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -19068,7 +20376,7 @@
         </is>
       </c>
       <c r="G250" t="n">
-        <v>2010</v>
+        <v>2007</v>
       </c>
       <c r="H250" t="inlineStr">
         <is>
@@ -19107,7 +20415,12 @@
       </c>
       <c r="P250" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q250" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -19143,7 +20456,7 @@
         </is>
       </c>
       <c r="G251" t="n">
-        <v>2011</v>
+        <v>2008</v>
       </c>
       <c r="H251" t="inlineStr">
         <is>
@@ -19182,7 +20495,12 @@
       </c>
       <c r="P251" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q251" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -19218,7 +20536,7 @@
         </is>
       </c>
       <c r="G252" t="n">
-        <v>2012</v>
+        <v>2009</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
@@ -19257,7 +20575,12 @@
       </c>
       <c r="P252" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q252" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -19293,7 +20616,7 @@
         </is>
       </c>
       <c r="G253" t="n">
-        <v>2013</v>
+        <v>2010</v>
       </c>
       <c r="H253" t="inlineStr">
         <is>
@@ -19332,7 +20655,12 @@
       </c>
       <c r="P253" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q253" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -19368,7 +20696,7 @@
         </is>
       </c>
       <c r="G254" t="n">
-        <v>2014</v>
+        <v>2011</v>
       </c>
       <c r="H254" t="inlineStr">
         <is>
@@ -19407,7 +20735,12 @@
       </c>
       <c r="P254" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q254" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -19443,7 +20776,7 @@
         </is>
       </c>
       <c r="G255" t="n">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="H255" t="inlineStr">
         <is>
@@ -19482,7 +20815,12 @@
       </c>
       <c r="P255" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q255" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -19518,7 +20856,7 @@
         </is>
       </c>
       <c r="G256" t="n">
-        <v>2016</v>
+        <v>2013</v>
       </c>
       <c r="H256" t="inlineStr">
         <is>
@@ -19557,7 +20895,12 @@
       </c>
       <c r="P256" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q256" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -19593,7 +20936,7 @@
         </is>
       </c>
       <c r="G257" t="n">
-        <v>2017</v>
+        <v>2014</v>
       </c>
       <c r="H257" t="inlineStr">
         <is>
@@ -19632,7 +20975,12 @@
       </c>
       <c r="P257" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q257" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -19668,7 +21016,7 @@
         </is>
       </c>
       <c r="G258" t="n">
-        <v>2018</v>
+        <v>2015</v>
       </c>
       <c r="H258" t="inlineStr">
         <is>
@@ -19707,7 +21055,12 @@
       </c>
       <c r="P258" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q258" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -19743,7 +21096,7 @@
         </is>
       </c>
       <c r="G259" t="n">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="H259" t="inlineStr">
         <is>
@@ -19782,7 +21135,12 @@
       </c>
       <c r="P259" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q259" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -19818,7 +21176,7 @@
         </is>
       </c>
       <c r="G260" t="n">
-        <v>2020</v>
+        <v>2017</v>
       </c>
       <c r="H260" t="inlineStr">
         <is>
@@ -19857,7 +21215,12 @@
       </c>
       <c r="P260" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q260" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -19893,7 +21256,7 @@
         </is>
       </c>
       <c r="G261" t="n">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
@@ -19932,7 +21295,12 @@
       </c>
       <c r="P261" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q261" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -19968,7 +21336,7 @@
         </is>
       </c>
       <c r="G262" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="H262" t="inlineStr">
         <is>
@@ -20007,7 +21375,12 @@
       </c>
       <c r="P262" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q262" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -20043,7 +21416,7 @@
         </is>
       </c>
       <c r="G263" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="H263" t="inlineStr">
         <is>
@@ -20082,7 +21455,12 @@
       </c>
       <c r="P263" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q263" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -20118,7 +21496,7 @@
         </is>
       </c>
       <c r="G264" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="H264" t="inlineStr">
         <is>
@@ -20157,7 +21535,12 @@
       </c>
       <c r="P264" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q264" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -20193,46 +21576,371 @@
         </is>
       </c>
       <c r="G265" t="n">
+        <v>2022</v>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>Sector público e instituciones</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>sector_publico_e_instituciones</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>Gasto público</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>gasto_publico</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>GC.XPN.TOTL.GD.ZS</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>Gasto público como porcentaje del PIB</t>
+        </is>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>Banco Mundial - World Development Indicators</t>
+        </is>
+      </c>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q265" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Venezuela, RB</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>Not classified</t>
+        </is>
+      </c>
+      <c r="G266" t="n">
+        <v>2023</v>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>Sector público e instituciones</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>sector_publico_e_instituciones</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>Gasto público</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>gasto_publico</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>GC.XPN.TOTL.GD.ZS</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>Gasto público como porcentaje del PIB</t>
+        </is>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>Banco Mundial - World Development Indicators</t>
+        </is>
+      </c>
+      <c r="P266" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q266" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Venezuela, RB</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Not classified</t>
+        </is>
+      </c>
+      <c r="G267" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>Sector público e instituciones</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>sector_publico_e_instituciones</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>Gasto público</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>gasto_publico</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>GC.XPN.TOTL.GD.ZS</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>Gasto público como porcentaje del PIB</t>
+        </is>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>Banco Mundial - World Development Indicators</t>
+        </is>
+      </c>
+      <c r="P267" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q267" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Venezuela, RB</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>Not classified</t>
+        </is>
+      </c>
+      <c r="G268" t="n">
         <v>2025</v>
       </c>
-      <c r="H265" t="inlineStr">
-        <is>
-          <t>Sector público e instituciones</t>
-        </is>
-      </c>
-      <c r="I265" t="inlineStr">
-        <is>
-          <t>sector_publico_e_instituciones</t>
-        </is>
-      </c>
-      <c r="J265" t="inlineStr">
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>Sector público e instituciones</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>sector_publico_e_instituciones</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
         <is>
           <t>Gasto público</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr">
+      <c r="K268" t="inlineStr">
         <is>
           <t>gasto_publico</t>
         </is>
       </c>
-      <c r="L265" t="inlineStr">
+      <c r="L268" t="inlineStr">
         <is>
           <t>GC.XPN.TOTL.GD.ZS</t>
         </is>
       </c>
-      <c r="M265" t="inlineStr">
+      <c r="M268" t="inlineStr">
         <is>
           <t>Gasto público como porcentaje del PIB</t>
         </is>
       </c>
-      <c r="O265" t="inlineStr">
-        <is>
-          <t>Banco Mundial - World Development Indicators</t>
-        </is>
-      </c>
-      <c r="P265" t="inlineStr">
-        <is>
-          <t>2026-07-08</t>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>Banco Mundial - World Development Indicators</t>
+        </is>
+      </c>
+      <c r="P268" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q268" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Venezuela, RB</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>Not classified</t>
+        </is>
+      </c>
+      <c r="G269" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>Sector público e instituciones</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>sector_publico_e_instituciones</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>Gasto público</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>gasto_publico</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>GC.XPN.TOTL.GD.ZS</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>Gasto público como porcentaje del PIB</t>
+        </is>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>Banco Mundial - World Development Indicators</t>
+        </is>
+      </c>
+      <c r="P269" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="Q269" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
         </is>
       </c>
     </row>
@@ -20282,7 +21990,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -20303,7 +22011,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
   </sheetData>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_sector_publico_e_instituciones.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_sector_publico_e_instituciones.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="[$-es-ES]#,##0"/>
+  </numFmts>
   <fonts count="5">
     <font>
       <name val="Calibri"/>
@@ -69,7 +71,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -83,6 +85,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -114,6 +119,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -144,6 +152,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -597,7 +608,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="G7" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -678,7 +689,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G8" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -759,7 +770,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="G9" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -840,7 +851,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="G10" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -921,7 +932,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="G11" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -1002,7 +1013,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="G12" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1083,7 +1094,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="G13" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1164,7 +1175,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="G14" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -1245,7 +1256,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="G15" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -1326,7 +1337,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="G16" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -1407,7 +1418,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="G17" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -1488,7 +1499,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="G18" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -1569,7 +1580,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="G19" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -1650,7 +1661,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="G20" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -1731,7 +1742,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="G21" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -1812,7 +1823,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G22" s="4" t="n">
+      <c r="G22" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -1893,7 +1904,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="G23" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -1974,7 +1985,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="G24" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -2055,7 +2066,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="G25" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -2136,7 +2147,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G26" s="4" t="n">
+      <c r="G26" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -2217,7 +2228,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="G27" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -2298,7 +2309,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G28" s="4" t="n">
+      <c r="G28" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -2379,7 +2390,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="G29" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -2460,7 +2471,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G30" s="4" t="n">
+      <c r="G30" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -2541,7 +2552,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G31" s="4" t="n">
+      <c r="G31" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -2622,7 +2633,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G32" s="4" t="n">
+      <c r="G32" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -2703,7 +2714,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G33" s="4" t="n">
+      <c r="G33" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -2784,7 +2795,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G34" s="4" t="n">
+      <c r="G34" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H34" s="4" t="inlineStr">
@@ -2865,7 +2876,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G35" s="4" t="n">
+      <c r="G35" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H35" s="4" t="inlineStr">
@@ -2946,7 +2957,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G36" s="4" t="n">
+      <c r="G36" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H36" s="4" t="inlineStr">
@@ -3027,7 +3038,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G37" s="4" t="n">
+      <c r="G37" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H37" s="4" t="inlineStr">
@@ -3108,7 +3119,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G38" s="4" t="n">
+      <c r="G38" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H38" s="4" t="inlineStr">
@@ -3189,7 +3200,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G39" s="4" t="n">
+      <c r="G39" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H39" s="4" t="inlineStr">
@@ -3270,7 +3281,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G40" s="4" t="n">
+      <c r="G40" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H40" s="4" t="inlineStr">
@@ -3351,7 +3362,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G41" s="4" t="n">
+      <c r="G41" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H41" s="4" t="inlineStr">
@@ -3432,7 +3443,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G42" s="4" t="n">
+      <c r="G42" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H42" s="4" t="inlineStr">
@@ -3513,7 +3524,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G43" s="4" t="n">
+      <c r="G43" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H43" s="4" t="inlineStr">
@@ -3594,7 +3605,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G44" s="4" t="n">
+      <c r="G44" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H44" s="4" t="inlineStr">
@@ -3675,7 +3686,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G45" s="4" t="n">
+      <c r="G45" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H45" s="4" t="inlineStr">
@@ -3756,7 +3767,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G46" s="4" t="n">
+      <c r="G46" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H46" s="4" t="inlineStr">
@@ -3837,7 +3848,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G47" s="4" t="n">
+      <c r="G47" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H47" s="4" t="inlineStr">
@@ -3918,7 +3929,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G48" s="4" t="n">
+      <c r="G48" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H48" s="4" t="inlineStr">
@@ -3999,7 +4010,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G49" s="4" t="n">
+      <c r="G49" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H49" s="4" t="inlineStr">
@@ -4080,7 +4091,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G50" s="4" t="n">
+      <c r="G50" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H50" s="4" t="inlineStr">
@@ -4161,7 +4172,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G51" s="4" t="n">
+      <c r="G51" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H51" s="4" t="inlineStr">
@@ -4242,7 +4253,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G52" s="4" t="n">
+      <c r="G52" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H52" s="4" t="inlineStr">
@@ -4323,7 +4334,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G53" s="4" t="n">
+      <c r="G53" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H53" s="4" t="inlineStr">
@@ -4404,7 +4415,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G54" s="4" t="n">
+      <c r="G54" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H54" s="4" t="inlineStr">
@@ -4485,7 +4496,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G55" s="4" t="n">
+      <c r="G55" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H55" s="4" t="inlineStr">
@@ -4566,7 +4577,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G56" s="4" t="n">
+      <c r="G56" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H56" s="4" t="inlineStr">
@@ -4647,7 +4658,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G57" s="4" t="n">
+      <c r="G57" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H57" s="4" t="inlineStr">
@@ -4728,7 +4739,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G58" s="4" t="n">
+      <c r="G58" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H58" s="4" t="inlineStr">
@@ -4809,7 +4820,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G59" s="4" t="n">
+      <c r="G59" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H59" s="4" t="inlineStr">
@@ -4890,7 +4901,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G60" s="4" t="n">
+      <c r="G60" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H60" s="4" t="inlineStr">
@@ -4971,7 +4982,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G61" s="4" t="n">
+      <c r="G61" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H61" s="4" t="inlineStr">
@@ -5052,7 +5063,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G62" s="4" t="n">
+      <c r="G62" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H62" s="4" t="inlineStr">
@@ -5133,7 +5144,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G63" s="4" t="n">
+      <c r="G63" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H63" s="4" t="inlineStr">
@@ -5214,7 +5225,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G64" s="4" t="n">
+      <c r="G64" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H64" s="4" t="inlineStr">
@@ -5295,7 +5306,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G65" s="4" t="n">
+      <c r="G65" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H65" s="4" t="inlineStr">
@@ -5376,7 +5387,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G66" s="4" t="n">
+      <c r="G66" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H66" s="4" t="inlineStr">
@@ -5457,7 +5468,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G67" s="4" t="n">
+      <c r="G67" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H67" s="4" t="inlineStr">
@@ -5538,7 +5549,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G68" s="4" t="n">
+      <c r="G68" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H68" s="4" t="inlineStr">
@@ -5619,7 +5630,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G69" s="4" t="n">
+      <c r="G69" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H69" s="4" t="inlineStr">
@@ -5700,7 +5711,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G70" s="4" t="n">
+      <c r="G70" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H70" s="4" t="inlineStr">
@@ -5781,7 +5792,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G71" s="4" t="n">
+      <c r="G71" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H71" s="4" t="inlineStr">
@@ -5862,7 +5873,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G72" s="4" t="n">
+      <c r="G72" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H72" s="4" t="inlineStr">
@@ -5943,7 +5954,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G73" s="4" t="n">
+      <c r="G73" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="H73" s="4" t="inlineStr">
@@ -6024,7 +6035,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G74" s="4" t="n">
+      <c r="G74" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H74" s="4" t="inlineStr">
@@ -6105,7 +6116,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G75" s="4" t="n">
+      <c r="G75" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H75" s="4" t="inlineStr">
@@ -6186,7 +6197,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G76" s="4" t="n">
+      <c r="G76" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H76" s="4" t="inlineStr">
@@ -6267,7 +6278,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G77" s="4" t="n">
+      <c r="G77" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H77" s="4" t="inlineStr">
@@ -6348,7 +6359,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G78" s="4" t="n">
+      <c r="G78" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H78" s="4" t="inlineStr">
@@ -6429,7 +6440,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G79" s="4" t="n">
+      <c r="G79" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H79" s="4" t="inlineStr">
@@ -6510,7 +6521,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G80" s="4" t="n">
+      <c r="G80" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H80" s="4" t="inlineStr">
@@ -6591,7 +6602,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G81" s="4" t="n">
+      <c r="G81" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H81" s="4" t="inlineStr">
@@ -6672,7 +6683,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G82" s="4" t="n">
+      <c r="G82" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H82" s="4" t="inlineStr">
@@ -6753,7 +6764,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G83" s="4" t="n">
+      <c r="G83" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H83" s="4" t="inlineStr">
@@ -6834,7 +6845,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G84" s="4" t="n">
+      <c r="G84" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H84" s="4" t="inlineStr">
@@ -6915,7 +6926,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G85" s="4" t="n">
+      <c r="G85" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H85" s="4" t="inlineStr">
@@ -6996,7 +7007,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G86" s="4" t="n">
+      <c r="G86" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H86" s="4" t="inlineStr">
@@ -7077,7 +7088,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G87" s="4" t="n">
+      <c r="G87" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H87" s="4" t="inlineStr">
@@ -7158,7 +7169,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G88" s="4" t="n">
+      <c r="G88" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H88" s="4" t="inlineStr">
@@ -7239,7 +7250,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G89" s="4" t="n">
+      <c r="G89" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H89" s="4" t="inlineStr">
@@ -7320,7 +7331,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G90" s="4" t="n">
+      <c r="G90" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H90" s="4" t="inlineStr">
@@ -7401,7 +7412,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G91" s="4" t="n">
+      <c r="G91" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H91" s="4" t="inlineStr">
@@ -7482,7 +7493,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G92" s="4" t="n">
+      <c r="G92" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H92" s="4" t="inlineStr">
@@ -7563,7 +7574,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G93" s="4" t="n">
+      <c r="G93" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H93" s="4" t="inlineStr">
@@ -7644,7 +7655,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G94" s="4" t="n">
+      <c r="G94" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H94" s="4" t="inlineStr">
@@ -7725,7 +7736,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G95" s="4" t="n">
+      <c r="G95" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H95" s="4" t="inlineStr">
@@ -7806,7 +7817,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G96" s="4" t="n">
+      <c r="G96" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H96" s="4" t="inlineStr">
@@ -7887,7 +7898,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G97" s="4" t="n">
+      <c r="G97" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H97" s="4" t="inlineStr">
@@ -7968,7 +7979,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G98" s="4" t="n">
+      <c r="G98" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H98" s="4" t="inlineStr">
@@ -8049,7 +8060,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G99" s="4" t="n">
+      <c r="G99" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H99" s="4" t="inlineStr">
@@ -8130,7 +8141,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G100" s="4" t="n">
+      <c r="G100" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H100" s="4" t="inlineStr">
@@ -8211,7 +8222,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G101" s="4" t="n">
+      <c r="G101" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H101" s="4" t="inlineStr">
@@ -8292,7 +8303,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G102" s="4" t="n">
+      <c r="G102" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H102" s="4" t="inlineStr">
@@ -8373,7 +8384,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G103" s="4" t="n">
+      <c r="G103" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H103" s="4" t="inlineStr">
@@ -8454,7 +8465,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G104" s="4" t="n">
+      <c r="G104" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H104" s="4" t="inlineStr">
@@ -8535,7 +8546,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G105" s="4" t="n">
+      <c r="G105" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H105" s="4" t="inlineStr">
@@ -8616,7 +8627,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G106" s="4" t="n">
+      <c r="G106" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H106" s="4" t="inlineStr">
@@ -8697,7 +8708,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G107" s="4" t="n">
+      <c r="G107" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H107" s="4" t="inlineStr">
@@ -8778,7 +8789,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G108" s="4" t="n">
+      <c r="G108" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H108" s="4" t="inlineStr">
@@ -8859,7 +8870,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G109" s="4" t="n">
+      <c r="G109" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H109" s="4" t="inlineStr">
@@ -8940,7 +8951,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G110" s="4" t="n">
+      <c r="G110" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H110" s="4" t="inlineStr">
@@ -9021,7 +9032,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G111" s="4" t="n">
+      <c r="G111" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H111" s="4" t="inlineStr">
@@ -9102,7 +9113,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G112" s="4" t="n">
+      <c r="G112" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H112" s="4" t="inlineStr">
@@ -9183,7 +9194,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G113" s="4" t="n">
+      <c r="G113" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H113" s="4" t="inlineStr">
@@ -9264,7 +9275,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G114" s="4" t="n">
+      <c r="G114" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H114" s="4" t="inlineStr">
@@ -9345,7 +9356,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G115" s="4" t="n">
+      <c r="G115" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H115" s="4" t="inlineStr">
@@ -9426,7 +9437,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G116" s="4" t="n">
+      <c r="G116" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H116" s="4" t="inlineStr">
@@ -9507,7 +9518,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G117" s="4" t="n">
+      <c r="G117" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H117" s="4" t="inlineStr">
@@ -9588,7 +9599,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G118" s="4" t="n">
+      <c r="G118" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H118" s="4" t="inlineStr">
@@ -9669,7 +9680,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G119" s="4" t="n">
+      <c r="G119" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H119" s="4" t="inlineStr">
@@ -9750,7 +9761,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G120" s="4" t="n">
+      <c r="G120" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H120" s="4" t="inlineStr">
@@ -9831,7 +9842,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G121" s="4" t="n">
+      <c r="G121" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H121" s="4" t="inlineStr">
@@ -9912,7 +9923,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G122" s="4" t="n">
+      <c r="G122" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H122" s="4" t="inlineStr">
@@ -9993,7 +10004,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G123" s="4" t="n">
+      <c r="G123" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H123" s="4" t="inlineStr">
@@ -10074,7 +10085,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G124" s="4" t="n">
+      <c r="G124" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H124" s="4" t="inlineStr">
@@ -10155,7 +10166,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G125" s="4" t="n">
+      <c r="G125" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H125" s="4" t="inlineStr">
@@ -10236,7 +10247,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G126" s="4" t="n">
+      <c r="G126" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H126" s="4" t="inlineStr">
@@ -10317,7 +10328,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G127" s="4" t="n">
+      <c r="G127" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H127" s="4" t="inlineStr">
@@ -10398,7 +10409,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G128" s="4" t="n">
+      <c r="G128" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H128" s="4" t="inlineStr">
@@ -10479,7 +10490,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G129" s="4" t="n">
+      <c r="G129" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H129" s="4" t="inlineStr">
@@ -10560,7 +10571,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G130" s="4" t="n">
+      <c r="G130" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H130" s="4" t="inlineStr">
@@ -10641,7 +10652,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G131" s="4" t="n">
+      <c r="G131" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H131" s="4" t="inlineStr">
@@ -10722,7 +10733,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G132" s="4" t="n">
+      <c r="G132" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H132" s="4" t="inlineStr">
@@ -10803,7 +10814,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G133" s="4" t="n">
+      <c r="G133" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H133" s="4" t="inlineStr">
@@ -10884,7 +10895,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G134" s="4" t="n">
+      <c r="G134" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H134" s="4" t="inlineStr">
@@ -10965,7 +10976,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G135" s="4" t="n">
+      <c r="G135" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H135" s="4" t="inlineStr">
@@ -11046,7 +11057,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G136" s="4" t="n">
+      <c r="G136" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H136" s="4" t="inlineStr">
@@ -11127,7 +11138,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G137" s="4" t="n">
+      <c r="G137" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H137" s="4" t="inlineStr">
@@ -11208,7 +11219,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G138" s="4" t="n">
+      <c r="G138" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H138" s="4" t="inlineStr">
@@ -11289,7 +11300,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G139" s="4" t="n">
+      <c r="G139" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H139" s="4" t="inlineStr">
@@ -11370,7 +11381,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G140" s="4" t="n">
+      <c r="G140" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="H140" s="4" t="inlineStr">
@@ -11451,7 +11462,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G141" s="4" t="n">
+      <c r="G141" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H141" s="4" t="inlineStr">
@@ -11532,7 +11543,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G142" s="4" t="n">
+      <c r="G142" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H142" s="4" t="inlineStr">
@@ -11613,7 +11624,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G143" s="4" t="n">
+      <c r="G143" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H143" s="4" t="inlineStr">
@@ -11694,7 +11705,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G144" s="4" t="n">
+      <c r="G144" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H144" s="4" t="inlineStr">
@@ -11775,7 +11786,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G145" s="4" t="n">
+      <c r="G145" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H145" s="4" t="inlineStr">
@@ -11856,7 +11867,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G146" s="4" t="n">
+      <c r="G146" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H146" s="4" t="inlineStr">
@@ -11937,7 +11948,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G147" s="4" t="n">
+      <c r="G147" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H147" s="4" t="inlineStr">
@@ -12018,7 +12029,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G148" s="4" t="n">
+      <c r="G148" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H148" s="4" t="inlineStr">
@@ -12099,7 +12110,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G149" s="4" t="n">
+      <c r="G149" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H149" s="4" t="inlineStr">
@@ -12180,7 +12191,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G150" s="4" t="n">
+      <c r="G150" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H150" s="4" t="inlineStr">
@@ -12261,7 +12272,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G151" s="4" t="n">
+      <c r="G151" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H151" s="4" t="inlineStr">
@@ -12342,7 +12353,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G152" s="4" t="n">
+      <c r="G152" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H152" s="4" t="inlineStr">
@@ -12423,7 +12434,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G153" s="4" t="n">
+      <c r="G153" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H153" s="4" t="inlineStr">
@@ -12504,7 +12515,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G154" s="4" t="n">
+      <c r="G154" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H154" s="4" t="inlineStr">
@@ -12585,7 +12596,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G155" s="4" t="n">
+      <c r="G155" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H155" s="4" t="inlineStr">
@@ -12666,7 +12677,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G156" s="4" t="n">
+      <c r="G156" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H156" s="4" t="inlineStr">
@@ -12747,7 +12758,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G157" s="4" t="n">
+      <c r="G157" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H157" s="4" t="inlineStr">
@@ -12828,7 +12839,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G158" s="4" t="n">
+      <c r="G158" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H158" s="4" t="inlineStr">
@@ -12909,7 +12920,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G159" s="4" t="n">
+      <c r="G159" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H159" s="4" t="inlineStr">
@@ -12990,7 +13001,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G160" s="4" t="n">
+      <c r="G160" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H160" s="4" t="inlineStr">
@@ -13071,7 +13082,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G161" s="4" t="n">
+      <c r="G161" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H161" s="4" t="inlineStr">
@@ -13152,7 +13163,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G162" s="4" t="n">
+      <c r="G162" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H162" s="4" t="inlineStr">
@@ -13233,7 +13244,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G163" s="4" t="n">
+      <c r="G163" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H163" s="4" t="inlineStr">
@@ -13314,7 +13325,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G164" s="4" t="n">
+      <c r="G164" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H164" s="4" t="inlineStr">
@@ -13395,7 +13406,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G165" s="4" t="n">
+      <c r="G165" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H165" s="4" t="inlineStr">
@@ -13476,7 +13487,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G166" s="4" t="n">
+      <c r="G166" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H166" s="4" t="inlineStr">
@@ -13557,7 +13568,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G167" s="4" t="n">
+      <c r="G167" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H167" s="4" t="inlineStr">
@@ -13638,7 +13649,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G168" s="4" t="n">
+      <c r="G168" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H168" s="4" t="inlineStr">
@@ -13719,7 +13730,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G169" s="4" t="n">
+      <c r="G169" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H169" s="4" t="inlineStr">
@@ -13800,7 +13811,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G170" s="4" t="n">
+      <c r="G170" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H170" s="4" t="inlineStr">
@@ -13881,7 +13892,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G171" s="4" t="n">
+      <c r="G171" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H171" s="4" t="inlineStr">
@@ -13962,7 +13973,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G172" s="4" t="n">
+      <c r="G172" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H172" s="4" t="inlineStr">
@@ -14043,7 +14054,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G173" s="4" t="n">
+      <c r="G173" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H173" s="4" t="inlineStr">
@@ -14124,7 +14135,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G174" s="4" t="n">
+      <c r="G174" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H174" s="4" t="inlineStr">
@@ -14205,7 +14216,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G175" s="4" t="n">
+      <c r="G175" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H175" s="4" t="inlineStr">
@@ -14286,7 +14297,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G176" s="4" t="n">
+      <c r="G176" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H176" s="4" t="inlineStr">
@@ -14367,7 +14378,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G177" s="4" t="n">
+      <c r="G177" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H177" s="4" t="inlineStr">
@@ -14448,7 +14459,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G178" s="4" t="n">
+      <c r="G178" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H178" s="4" t="inlineStr">
@@ -14529,7 +14540,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G179" s="4" t="n">
+      <c r="G179" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H179" s="4" t="inlineStr">
@@ -14610,7 +14621,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G180" s="4" t="n">
+      <c r="G180" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H180" s="4" t="inlineStr">
@@ -14691,7 +14702,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G181" s="4" t="n">
+      <c r="G181" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H181" s="4" t="inlineStr">
@@ -14772,7 +14783,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G182" s="4" t="n">
+      <c r="G182" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H182" s="4" t="inlineStr">
@@ -14853,7 +14864,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G183" s="4" t="n">
+      <c r="G183" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H183" s="4" t="inlineStr">
@@ -14934,7 +14945,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G184" s="4" t="n">
+      <c r="G184" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H184" s="4" t="inlineStr">
@@ -15015,7 +15026,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G185" s="4" t="n">
+      <c r="G185" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H185" s="4" t="inlineStr">
@@ -15096,7 +15107,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G186" s="4" t="n">
+      <c r="G186" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H186" s="4" t="inlineStr">
@@ -15177,7 +15188,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G187" s="4" t="n">
+      <c r="G187" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H187" s="4" t="inlineStr">
@@ -15258,7 +15269,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G188" s="4" t="n">
+      <c r="G188" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H188" s="4" t="inlineStr">
@@ -15339,7 +15350,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G189" s="4" t="n">
+      <c r="G189" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H189" s="4" t="inlineStr">
@@ -15420,7 +15431,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G190" s="4" t="n">
+      <c r="G190" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H190" s="4" t="inlineStr">
@@ -15501,7 +15512,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G191" s="4" t="n">
+      <c r="G191" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H191" s="4" t="inlineStr">
@@ -15582,7 +15593,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G192" s="4" t="n">
+      <c r="G192" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H192" s="4" t="inlineStr">
@@ -15663,7 +15674,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G193" s="4" t="n">
+      <c r="G193" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H193" s="4" t="inlineStr">
@@ -15744,7 +15755,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G194" s="4" t="n">
+      <c r="G194" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H194" s="4" t="inlineStr">
@@ -15825,7 +15836,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G195" s="4" t="n">
+      <c r="G195" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H195" s="4" t="inlineStr">
@@ -15906,7 +15917,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G196" s="4" t="n">
+      <c r="G196" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H196" s="4" t="inlineStr">
@@ -15987,7 +15998,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G197" s="4" t="n">
+      <c r="G197" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H197" s="4" t="inlineStr">
@@ -16068,7 +16079,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G198" s="4" t="n">
+      <c r="G198" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H198" s="4" t="inlineStr">
@@ -16149,7 +16160,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G199" s="4" t="n">
+      <c r="G199" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H199" s="4" t="inlineStr">
@@ -16230,7 +16241,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G200" s="4" t="n">
+      <c r="G200" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H200" s="4" t="inlineStr">
@@ -16311,7 +16322,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G201" s="4" t="n">
+      <c r="G201" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H201" s="4" t="inlineStr">
@@ -16392,7 +16403,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G202" s="4" t="n">
+      <c r="G202" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H202" s="4" t="inlineStr">
@@ -16473,7 +16484,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G203" s="4" t="n">
+      <c r="G203" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H203" s="4" t="inlineStr">
@@ -16554,7 +16565,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G204" s="4" t="n">
+      <c r="G204" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H204" s="4" t="inlineStr">
@@ -16635,7 +16646,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G205" s="4" t="n">
+      <c r="G205" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H205" s="4" t="inlineStr">
@@ -16716,7 +16727,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G206" s="4" t="n">
+      <c r="G206" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H206" s="4" t="inlineStr">
@@ -16797,7 +16808,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G207" s="4" t="n">
+      <c r="G207" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="H207" s="4" t="inlineStr">
@@ -16878,7 +16889,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G208" s="4" t="n">
+      <c r="G208" s="7" t="n">
         <v>1960</v>
       </c>
       <c r="H208" s="4" t="inlineStr">
@@ -16959,7 +16970,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G209" s="4" t="n">
+      <c r="G209" s="7" t="n">
         <v>1961</v>
       </c>
       <c r="H209" s="4" t="inlineStr">
@@ -17040,7 +17051,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G210" s="4" t="n">
+      <c r="G210" s="7" t="n">
         <v>1962</v>
       </c>
       <c r="H210" s="4" t="inlineStr">
@@ -17121,7 +17132,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G211" s="4" t="n">
+      <c r="G211" s="7" t="n">
         <v>1963</v>
       </c>
       <c r="H211" s="4" t="inlineStr">
@@ -17202,7 +17213,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G212" s="4" t="n">
+      <c r="G212" s="7" t="n">
         <v>1964</v>
       </c>
       <c r="H212" s="4" t="inlineStr">
@@ -17283,7 +17294,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G213" s="4" t="n">
+      <c r="G213" s="7" t="n">
         <v>1965</v>
       </c>
       <c r="H213" s="4" t="inlineStr">
@@ -17364,7 +17375,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G214" s="4" t="n">
+      <c r="G214" s="7" t="n">
         <v>1966</v>
       </c>
       <c r="H214" s="4" t="inlineStr">
@@ -17445,7 +17456,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G215" s="4" t="n">
+      <c r="G215" s="7" t="n">
         <v>1967</v>
       </c>
       <c r="H215" s="4" t="inlineStr">
@@ -17526,7 +17537,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G216" s="4" t="n">
+      <c r="G216" s="7" t="n">
         <v>1968</v>
       </c>
       <c r="H216" s="4" t="inlineStr">
@@ -17607,7 +17618,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G217" s="4" t="n">
+      <c r="G217" s="7" t="n">
         <v>1969</v>
       </c>
       <c r="H217" s="4" t="inlineStr">
@@ -17688,7 +17699,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G218" s="4" t="n">
+      <c r="G218" s="7" t="n">
         <v>1970</v>
       </c>
       <c r="H218" s="4" t="inlineStr">
@@ -17769,7 +17780,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G219" s="4" t="n">
+      <c r="G219" s="7" t="n">
         <v>1971</v>
       </c>
       <c r="H219" s="4" t="inlineStr">
@@ -17850,7 +17861,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G220" s="4" t="n">
+      <c r="G220" s="7" t="n">
         <v>1972</v>
       </c>
       <c r="H220" s="4" t="inlineStr">
@@ -17931,7 +17942,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G221" s="4" t="n">
+      <c r="G221" s="7" t="n">
         <v>1973</v>
       </c>
       <c r="H221" s="4" t="inlineStr">
@@ -18012,7 +18023,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G222" s="4" t="n">
+      <c r="G222" s="7" t="n">
         <v>1974</v>
       </c>
       <c r="H222" s="4" t="inlineStr">
@@ -18093,7 +18104,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G223" s="4" t="n">
+      <c r="G223" s="7" t="n">
         <v>1975</v>
       </c>
       <c r="H223" s="4" t="inlineStr">
@@ -18174,7 +18185,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G224" s="4" t="n">
+      <c r="G224" s="7" t="n">
         <v>1976</v>
       </c>
       <c r="H224" s="4" t="inlineStr">
@@ -18255,7 +18266,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G225" s="4" t="n">
+      <c r="G225" s="7" t="n">
         <v>1977</v>
       </c>
       <c r="H225" s="4" t="inlineStr">
@@ -18336,7 +18347,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G226" s="4" t="n">
+      <c r="G226" s="7" t="n">
         <v>1978</v>
       </c>
       <c r="H226" s="4" t="inlineStr">
@@ -18417,7 +18428,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G227" s="4" t="n">
+      <c r="G227" s="7" t="n">
         <v>1979</v>
       </c>
       <c r="H227" s="4" t="inlineStr">
@@ -18498,7 +18509,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G228" s="4" t="n">
+      <c r="G228" s="7" t="n">
         <v>1980</v>
       </c>
       <c r="H228" s="4" t="inlineStr">
@@ -18579,7 +18590,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G229" s="4" t="n">
+      <c r="G229" s="7" t="n">
         <v>1981</v>
       </c>
       <c r="H229" s="4" t="inlineStr">
@@ -18660,7 +18671,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G230" s="4" t="n">
+      <c r="G230" s="7" t="n">
         <v>1982</v>
       </c>
       <c r="H230" s="4" t="inlineStr">
@@ -18741,7 +18752,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G231" s="4" t="n">
+      <c r="G231" s="7" t="n">
         <v>1983</v>
       </c>
       <c r="H231" s="4" t="inlineStr">
@@ -18822,7 +18833,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G232" s="4" t="n">
+      <c r="G232" s="7" t="n">
         <v>1984</v>
       </c>
       <c r="H232" s="4" t="inlineStr">
@@ -18903,7 +18914,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G233" s="4" t="n">
+      <c r="G233" s="7" t="n">
         <v>1985</v>
       </c>
       <c r="H233" s="4" t="inlineStr">
@@ -18984,7 +18995,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G234" s="4" t="n">
+      <c r="G234" s="7" t="n">
         <v>1986</v>
       </c>
       <c r="H234" s="4" t="inlineStr">
@@ -19065,7 +19076,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G235" s="4" t="n">
+      <c r="G235" s="7" t="n">
         <v>1987</v>
       </c>
       <c r="H235" s="4" t="inlineStr">
@@ -19146,7 +19157,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G236" s="4" t="n">
+      <c r="G236" s="7" t="n">
         <v>1988</v>
       </c>
       <c r="H236" s="4" t="inlineStr">
@@ -19227,7 +19238,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G237" s="4" t="n">
+      <c r="G237" s="7" t="n">
         <v>1989</v>
       </c>
       <c r="H237" s="4" t="inlineStr">
@@ -19308,7 +19319,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G238" s="4" t="n">
+      <c r="G238" s="7" t="n">
         <v>1990</v>
       </c>
       <c r="H238" s="4" t="inlineStr">
@@ -19389,7 +19400,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G239" s="4" t="n">
+      <c r="G239" s="7" t="n">
         <v>1991</v>
       </c>
       <c r="H239" s="4" t="inlineStr">
@@ -19470,7 +19481,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G240" s="4" t="n">
+      <c r="G240" s="7" t="n">
         <v>1992</v>
       </c>
       <c r="H240" s="4" t="inlineStr">
@@ -19551,7 +19562,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G241" s="4" t="n">
+      <c r="G241" s="7" t="n">
         <v>1993</v>
       </c>
       <c r="H241" s="4" t="inlineStr">
@@ -19632,7 +19643,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G242" s="4" t="n">
+      <c r="G242" s="7" t="n">
         <v>1994</v>
       </c>
       <c r="H242" s="4" t="inlineStr">
@@ -19713,7 +19724,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G243" s="4" t="n">
+      <c r="G243" s="7" t="n">
         <v>1995</v>
       </c>
       <c r="H243" s="4" t="inlineStr">
@@ -19794,7 +19805,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G244" s="4" t="n">
+      <c r="G244" s="7" t="n">
         <v>1996</v>
       </c>
       <c r="H244" s="4" t="inlineStr">
@@ -19875,7 +19886,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G245" s="4" t="n">
+      <c r="G245" s="7" t="n">
         <v>1997</v>
       </c>
       <c r="H245" s="4" t="inlineStr">
@@ -19956,7 +19967,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G246" s="4" t="n">
+      <c r="G246" s="7" t="n">
         <v>1998</v>
       </c>
       <c r="H246" s="4" t="inlineStr">
@@ -20037,7 +20048,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G247" s="4" t="n">
+      <c r="G247" s="7" t="n">
         <v>1999</v>
       </c>
       <c r="H247" s="4" t="inlineStr">
@@ -20118,7 +20129,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G248" s="4" t="n">
+      <c r="G248" s="7" t="n">
         <v>2000</v>
       </c>
       <c r="H248" s="4" t="inlineStr">
@@ -20199,7 +20210,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G249" s="4" t="n">
+      <c r="G249" s="7" t="n">
         <v>2001</v>
       </c>
       <c r="H249" s="4" t="inlineStr">
@@ -20280,7 +20291,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G250" s="4" t="n">
+      <c r="G250" s="7" t="n">
         <v>2002</v>
       </c>
       <c r="H250" s="4" t="inlineStr">
@@ -20361,7 +20372,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G251" s="4" t="n">
+      <c r="G251" s="7" t="n">
         <v>2003</v>
       </c>
       <c r="H251" s="4" t="inlineStr">
@@ -20442,7 +20453,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G252" s="4" t="n">
+      <c r="G252" s="7" t="n">
         <v>2004</v>
       </c>
       <c r="H252" s="4" t="inlineStr">
@@ -20523,7 +20534,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G253" s="4" t="n">
+      <c r="G253" s="7" t="n">
         <v>2005</v>
       </c>
       <c r="H253" s="4" t="inlineStr">
@@ -20604,7 +20615,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G254" s="4" t="n">
+      <c r="G254" s="7" t="n">
         <v>2006</v>
       </c>
       <c r="H254" s="4" t="inlineStr">
@@ -20685,7 +20696,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G255" s="4" t="n">
+      <c r="G255" s="7" t="n">
         <v>2007</v>
       </c>
       <c r="H255" s="4" t="inlineStr">
@@ -20766,7 +20777,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G256" s="4" t="n">
+      <c r="G256" s="7" t="n">
         <v>2008</v>
       </c>
       <c r="H256" s="4" t="inlineStr">
@@ -20847,7 +20858,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G257" s="4" t="n">
+      <c r="G257" s="7" t="n">
         <v>2009</v>
       </c>
       <c r="H257" s="4" t="inlineStr">
@@ -20928,7 +20939,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G258" s="4" t="n">
+      <c r="G258" s="7" t="n">
         <v>2010</v>
       </c>
       <c r="H258" s="4" t="inlineStr">
@@ -21009,7 +21020,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G259" s="4" t="n">
+      <c r="G259" s="7" t="n">
         <v>2011</v>
       </c>
       <c r="H259" s="4" t="inlineStr">
@@ -21090,7 +21101,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G260" s="4" t="n">
+      <c r="G260" s="7" t="n">
         <v>2012</v>
       </c>
       <c r="H260" s="4" t="inlineStr">
@@ -21171,7 +21182,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G261" s="4" t="n">
+      <c r="G261" s="7" t="n">
         <v>2013</v>
       </c>
       <c r="H261" s="4" t="inlineStr">
@@ -21252,7 +21263,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G262" s="4" t="n">
+      <c r="G262" s="7" t="n">
         <v>2014</v>
       </c>
       <c r="H262" s="4" t="inlineStr">
@@ -21333,7 +21344,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G263" s="4" t="n">
+      <c r="G263" s="7" t="n">
         <v>2015</v>
       </c>
       <c r="H263" s="4" t="inlineStr">
@@ -21414,7 +21425,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G264" s="4" t="n">
+      <c r="G264" s="7" t="n">
         <v>2016</v>
       </c>
       <c r="H264" s="4" t="inlineStr">
@@ -21495,7 +21506,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G265" s="4" t="n">
+      <c r="G265" s="7" t="n">
         <v>2017</v>
       </c>
       <c r="H265" s="4" t="inlineStr">
@@ -21576,7 +21587,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G266" s="4" t="n">
+      <c r="G266" s="7" t="n">
         <v>2018</v>
       </c>
       <c r="H266" s="4" t="inlineStr">
@@ -21657,7 +21668,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G267" s="4" t="n">
+      <c r="G267" s="7" t="n">
         <v>2019</v>
       </c>
       <c r="H267" s="4" t="inlineStr">
@@ -21738,7 +21749,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G268" s="4" t="n">
+      <c r="G268" s="7" t="n">
         <v>2020</v>
       </c>
       <c r="H268" s="4" t="inlineStr">
@@ -21819,7 +21830,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G269" s="4" t="n">
+      <c r="G269" s="7" t="n">
         <v>2021</v>
       </c>
       <c r="H269" s="4" t="inlineStr">
@@ -21900,7 +21911,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G270" s="4" t="n">
+      <c r="G270" s="7" t="n">
         <v>2022</v>
       </c>
       <c r="H270" s="4" t="inlineStr">
@@ -21981,7 +21992,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G271" s="4" t="n">
+      <c r="G271" s="7" t="n">
         <v>2023</v>
       </c>
       <c r="H271" s="4" t="inlineStr">
@@ -22062,7 +22073,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G272" s="4" t="n">
+      <c r="G272" s="7" t="n">
         <v>2024</v>
       </c>
       <c r="H272" s="4" t="inlineStr">
@@ -22143,7 +22154,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G273" s="4" t="n">
+      <c r="G273" s="7" t="n">
         <v>2025</v>
       </c>
       <c r="H273" s="4" t="inlineStr">
@@ -22224,7 +22235,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G274" s="4" t="n">
+      <c r="G274" s="7" t="n">
         <v>2026</v>
       </c>
       <c r="H274" s="4" t="inlineStr">
@@ -22364,7 +22375,7 @@
           <t>Número de indicadores</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="7" t="n">
         <v>4</v>
       </c>
     </row>
@@ -22374,7 +22385,7 @@
           <t>Número de registros</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="7" t="n">
         <v>268</v>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_sector_publico_e_instituciones.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_sector_publico_e_instituciones.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="datos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metadatos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="datos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="metadatos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -81,23 +81,91 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -112,16 +180,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -130,7 +195,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -145,16 +210,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -451,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q274"/>
+  <dimension ref="A1:Q270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -476,14 +538,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Banco Mundial - Venezuela - Sector público e instituciones</t>
+          <t>Banco Mundial - Sector público e instituciones</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>World Development Indicators</t>
+          <t>Venezuela</t>
         </is>
       </c>
     </row>
@@ -608,7 +670,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G7" s="7" t="n">
+      <c r="G7" s="5" t="n">
         <v>1960</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
@@ -649,14 +711,10 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q7" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -689,7 +747,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G8" s="7" t="n">
+      <c r="G8" s="5" t="n">
         <v>1961</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -730,14 +788,10 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q8" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -770,7 +824,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G9" s="7" t="n">
+      <c r="G9" s="5" t="n">
         <v>1962</v>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -811,14 +865,10 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q9" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -851,7 +901,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G10" s="7" t="n">
+      <c r="G10" s="5" t="n">
         <v>1963</v>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -892,14 +942,10 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q10" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -932,7 +978,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G11" s="7" t="n">
+      <c r="G11" s="5" t="n">
         <v>1964</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -973,14 +1019,10 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q11" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -1013,7 +1055,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G12" s="7" t="n">
+      <c r="G12" s="5" t="n">
         <v>1965</v>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1054,14 +1096,10 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q12" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -1094,7 +1132,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G13" s="7" t="n">
+      <c r="G13" s="5" t="n">
         <v>1966</v>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1135,14 +1173,10 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q13" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -1175,7 +1209,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G14" s="7" t="n">
+      <c r="G14" s="5" t="n">
         <v>1967</v>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -1216,14 +1250,10 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q14" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -1256,7 +1286,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G15" s="7" t="n">
+      <c r="G15" s="5" t="n">
         <v>1968</v>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -1297,14 +1327,10 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q15" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -1337,7 +1363,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G16" s="7" t="n">
+      <c r="G16" s="5" t="n">
         <v>1969</v>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -1378,14 +1404,10 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q16" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -1418,7 +1440,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G17" s="7" t="n">
+      <c r="G17" s="5" t="n">
         <v>1970</v>
       </c>
       <c r="H17" s="4" t="inlineStr">
@@ -1459,14 +1481,10 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q17" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -1499,7 +1517,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G18" s="7" t="n">
+      <c r="G18" s="5" t="n">
         <v>1971</v>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -1540,14 +1558,10 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q18" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -1580,7 +1594,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G19" s="7" t="n">
+      <c r="G19" s="5" t="n">
         <v>1972</v>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -1621,14 +1635,10 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q19" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -1661,7 +1671,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G20" s="7" t="n">
+      <c r="G20" s="5" t="n">
         <v>1973</v>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -1702,14 +1712,10 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q20" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -1742,7 +1748,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G21" s="7" t="n">
+      <c r="G21" s="5" t="n">
         <v>1974</v>
       </c>
       <c r="H21" s="4" t="inlineStr">
@@ -1783,14 +1789,10 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q21" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -1823,7 +1825,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G22" s="7" t="n">
+      <c r="G22" s="5" t="n">
         <v>1975</v>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -1864,14 +1866,10 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q22" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -1904,7 +1902,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G23" s="7" t="n">
+      <c r="G23" s="5" t="n">
         <v>1976</v>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -1945,14 +1943,10 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q23" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q23" s="4" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -1985,7 +1979,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G24" s="7" t="n">
+      <c r="G24" s="5" t="n">
         <v>1977</v>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -2026,14 +2020,10 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q24" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -2066,7 +2056,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G25" s="7" t="n">
+      <c r="G25" s="5" t="n">
         <v>1978</v>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -2107,14 +2097,10 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q25" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -2147,7 +2133,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G26" s="7" t="n">
+      <c r="G26" s="5" t="n">
         <v>1979</v>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -2188,14 +2174,10 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q26" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -2228,7 +2210,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G27" s="7" t="n">
+      <c r="G27" s="5" t="n">
         <v>1980</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -2269,14 +2251,10 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q27" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -2309,7 +2287,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G28" s="7" t="n">
+      <c r="G28" s="5" t="n">
         <v>1981</v>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -2350,14 +2328,10 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q28" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -2390,7 +2364,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G29" s="7" t="n">
+      <c r="G29" s="5" t="n">
         <v>1982</v>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -2431,14 +2405,10 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q29" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q29" s="4" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -2471,7 +2441,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G30" s="7" t="n">
+      <c r="G30" s="5" t="n">
         <v>1983</v>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -2512,14 +2482,10 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q30" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q30" s="4" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -2552,7 +2518,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G31" s="7" t="n">
+      <c r="G31" s="5" t="n">
         <v>1984</v>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -2593,14 +2559,10 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q31" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -2633,7 +2595,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G32" s="7" t="n">
+      <c r="G32" s="5" t="n">
         <v>1985</v>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -2674,14 +2636,10 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q32" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q32" s="4" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -2714,7 +2672,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G33" s="7" t="n">
+      <c r="G33" s="5" t="n">
         <v>1986</v>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -2755,14 +2713,10 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q33" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -2795,7 +2749,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G34" s="7" t="n">
+      <c r="G34" s="5" t="n">
         <v>1987</v>
       </c>
       <c r="H34" s="4" t="inlineStr">
@@ -2836,14 +2790,10 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q34" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q34" s="4" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -2876,7 +2826,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G35" s="7" t="n">
+      <c r="G35" s="5" t="n">
         <v>1988</v>
       </c>
       <c r="H35" s="4" t="inlineStr">
@@ -2917,14 +2867,10 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q35" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q35" s="4" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -2957,7 +2903,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G36" s="7" t="n">
+      <c r="G36" s="5" t="n">
         <v>1989</v>
       </c>
       <c r="H36" s="4" t="inlineStr">
@@ -2998,14 +2944,10 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q36" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q36" s="4" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -3038,7 +2980,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G37" s="7" t="n">
+      <c r="G37" s="5" t="n">
         <v>1990</v>
       </c>
       <c r="H37" s="4" t="inlineStr">
@@ -3079,14 +3021,10 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q37" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q37" s="4" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -3119,7 +3057,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G38" s="7" t="n">
+      <c r="G38" s="5" t="n">
         <v>1991</v>
       </c>
       <c r="H38" s="4" t="inlineStr">
@@ -3160,14 +3098,10 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q38" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q38" s="4" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -3200,7 +3134,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G39" s="7" t="n">
+      <c r="G39" s="5" t="n">
         <v>1992</v>
       </c>
       <c r="H39" s="4" t="inlineStr">
@@ -3241,14 +3175,10 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q39" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -3281,7 +3211,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G40" s="7" t="n">
+      <c r="G40" s="5" t="n">
         <v>1993</v>
       </c>
       <c r="H40" s="4" t="inlineStr">
@@ -3322,14 +3252,10 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q40" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q40" s="4" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -3362,7 +3288,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G41" s="7" t="n">
+      <c r="G41" s="5" t="n">
         <v>1994</v>
       </c>
       <c r="H41" s="4" t="inlineStr">
@@ -3403,14 +3329,10 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q41" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q41" s="4" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -3443,7 +3365,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G42" s="7" t="n">
+      <c r="G42" s="5" t="n">
         <v>1995</v>
       </c>
       <c r="H42" s="4" t="inlineStr">
@@ -3484,14 +3406,10 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q42" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q42" s="4" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -3524,7 +3442,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G43" s="7" t="n">
+      <c r="G43" s="5" t="n">
         <v>1996</v>
       </c>
       <c r="H43" s="4" t="inlineStr">
@@ -3565,14 +3483,10 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q43" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q43" s="4" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -3605,7 +3519,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G44" s="7" t="n">
+      <c r="G44" s="5" t="n">
         <v>1997</v>
       </c>
       <c r="H44" s="4" t="inlineStr">
@@ -3646,14 +3560,10 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q44" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -3686,7 +3596,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G45" s="7" t="n">
+      <c r="G45" s="5" t="n">
         <v>1998</v>
       </c>
       <c r="H45" s="4" t="inlineStr">
@@ -3727,14 +3637,10 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q45" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q45" s="4" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -3767,7 +3673,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G46" s="7" t="n">
+      <c r="G46" s="5" t="n">
         <v>1999</v>
       </c>
       <c r="H46" s="4" t="inlineStr">
@@ -3808,14 +3714,10 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q46" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -3848,7 +3750,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G47" s="7" t="n">
+      <c r="G47" s="5" t="n">
         <v>2000</v>
       </c>
       <c r="H47" s="4" t="inlineStr">
@@ -3889,14 +3791,10 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q47" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q47" s="4" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
@@ -3929,7 +3827,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G48" s="7" t="n">
+      <c r="G48" s="5" t="n">
         <v>2001</v>
       </c>
       <c r="H48" s="4" t="inlineStr">
@@ -3970,14 +3868,10 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q48" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q48" s="4" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
@@ -4010,7 +3904,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G49" s="7" t="n">
+      <c r="G49" s="5" t="n">
         <v>2002</v>
       </c>
       <c r="H49" s="4" t="inlineStr">
@@ -4051,14 +3945,10 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q49" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q49" s="4" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
@@ -4091,7 +3981,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G50" s="7" t="n">
+      <c r="G50" s="5" t="n">
         <v>2003</v>
       </c>
       <c r="H50" s="4" t="inlineStr">
@@ -4132,14 +4022,10 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q50" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q50" s="4" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
@@ -4172,7 +4058,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G51" s="7" t="n">
+      <c r="G51" s="5" t="n">
         <v>2004</v>
       </c>
       <c r="H51" s="4" t="inlineStr">
@@ -4213,14 +4099,10 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q51" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
@@ -4253,7 +4135,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G52" s="7" t="n">
+      <c r="G52" s="5" t="n">
         <v>2005</v>
       </c>
       <c r="H52" s="4" t="inlineStr">
@@ -4294,14 +4176,10 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q52" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q52" s="4" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
@@ -4334,7 +4212,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G53" s="7" t="n">
+      <c r="G53" s="5" t="n">
         <v>2006</v>
       </c>
       <c r="H53" s="4" t="inlineStr">
@@ -4375,14 +4253,10 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q53" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
@@ -4415,7 +4289,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G54" s="7" t="n">
+      <c r="G54" s="5" t="n">
         <v>2007</v>
       </c>
       <c r="H54" s="4" t="inlineStr">
@@ -4456,14 +4330,10 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q54" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q54" s="4" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
@@ -4496,7 +4366,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G55" s="7" t="n">
+      <c r="G55" s="5" t="n">
         <v>2008</v>
       </c>
       <c r="H55" s="4" t="inlineStr">
@@ -4537,14 +4407,10 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q55" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
@@ -4577,7 +4443,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G56" s="7" t="n">
+      <c r="G56" s="5" t="n">
         <v>2009</v>
       </c>
       <c r="H56" s="4" t="inlineStr">
@@ -4618,14 +4484,10 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q56" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q56" s="4" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
@@ -4658,7 +4520,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G57" s="7" t="n">
+      <c r="G57" s="5" t="n">
         <v>2010</v>
       </c>
       <c r="H57" s="4" t="inlineStr">
@@ -4699,14 +4561,10 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q57" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q57" s="4" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
@@ -4739,7 +4597,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G58" s="7" t="n">
+      <c r="G58" s="5" t="n">
         <v>2011</v>
       </c>
       <c r="H58" s="4" t="inlineStr">
@@ -4780,14 +4638,10 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q58" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q58" s="4" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -4820,7 +4674,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G59" s="7" t="n">
+      <c r="G59" s="5" t="n">
         <v>2012</v>
       </c>
       <c r="H59" s="4" t="inlineStr">
@@ -4861,14 +4715,10 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q59" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q59" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
@@ -4901,7 +4751,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G60" s="7" t="n">
+      <c r="G60" s="5" t="n">
         <v>2013</v>
       </c>
       <c r="H60" s="4" t="inlineStr">
@@ -4942,14 +4792,10 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q60" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -4982,7 +4828,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G61" s="7" t="n">
+      <c r="G61" s="5" t="n">
         <v>2014</v>
       </c>
       <c r="H61" s="4" t="inlineStr">
@@ -5023,14 +4869,10 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q61" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q61" s="4" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
@@ -5063,7 +4905,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G62" s="7" t="n">
+      <c r="G62" s="5" t="n">
         <v>2015</v>
       </c>
       <c r="H62" s="4" t="inlineStr">
@@ -5104,14 +4946,10 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q62" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q62" s="4" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
@@ -5144,7 +4982,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G63" s="7" t="n">
+      <c r="G63" s="5" t="n">
         <v>2016</v>
       </c>
       <c r="H63" s="4" t="inlineStr">
@@ -5185,14 +5023,10 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q63" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q63" s="4" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
@@ -5225,7 +5059,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G64" s="7" t="n">
+      <c r="G64" s="5" t="n">
         <v>2017</v>
       </c>
       <c r="H64" s="4" t="inlineStr">
@@ -5266,14 +5100,10 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q64" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q64" s="4" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
@@ -5306,7 +5136,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G65" s="7" t="n">
+      <c r="G65" s="5" t="n">
         <v>2018</v>
       </c>
       <c r="H65" s="4" t="inlineStr">
@@ -5347,14 +5177,10 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q65" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q65" s="4" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
@@ -5387,7 +5213,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G66" s="7" t="n">
+      <c r="G66" s="5" t="n">
         <v>2019</v>
       </c>
       <c r="H66" s="4" t="inlineStr">
@@ -5428,14 +5254,10 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q66" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q66" s="4" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
@@ -5468,7 +5290,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G67" s="7" t="n">
+      <c r="G67" s="5" t="n">
         <v>2020</v>
       </c>
       <c r="H67" s="4" t="inlineStr">
@@ -5509,14 +5331,10 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q67" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q67" s="4" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
@@ -5549,7 +5367,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G68" s="7" t="n">
+      <c r="G68" s="5" t="n">
         <v>2021</v>
       </c>
       <c r="H68" s="4" t="inlineStr">
@@ -5590,14 +5408,10 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q68" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q68" s="4" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
@@ -5630,7 +5444,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G69" s="7" t="n">
+      <c r="G69" s="5" t="n">
         <v>2022</v>
       </c>
       <c r="H69" s="4" t="inlineStr">
@@ -5671,14 +5485,10 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q69" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q69" s="4" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
@@ -5711,7 +5521,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G70" s="7" t="n">
+      <c r="G70" s="5" t="n">
         <v>2023</v>
       </c>
       <c r="H70" s="4" t="inlineStr">
@@ -5752,14 +5562,10 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q70" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q70" s="4" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
@@ -5792,7 +5598,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G71" s="7" t="n">
+      <c r="G71" s="5" t="n">
         <v>2024</v>
       </c>
       <c r="H71" s="4" t="inlineStr">
@@ -5833,14 +5639,10 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q71" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q71" s="4" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
@@ -5873,7 +5675,7 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G72" s="7" t="n">
+      <c r="G72" s="5" t="n">
         <v>2025</v>
       </c>
       <c r="H72" s="4" t="inlineStr">
@@ -5914,14 +5716,10 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q72" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q72" s="4" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
@@ -5954,8 +5752,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G73" s="7" t="n">
-        <v>2026</v>
+      <c r="G73" s="5" t="n">
+        <v>1960</v>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
@@ -5969,22 +5767,22 @@
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>Deuda pública</t>
+          <t>Ingresos públicos</t>
         </is>
       </c>
       <c r="K73" s="4" t="inlineStr">
         <is>
-          <t>deuda_publica</t>
+          <t>ingresos_publicos</t>
         </is>
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
-          <t>GC.DOD.TOTL.GD.ZS</t>
+          <t>GC.REV.XGRT.GD.ZS</t>
         </is>
       </c>
       <c r="M73" s="4" t="inlineStr">
         <is>
-          <t>Deuda del gobierno central como porcentaje del PIB</t>
+          <t>Ingresos públicos excluidas donaciones como porcentaje del PIB</t>
         </is>
       </c>
       <c r="N73" s="4" t="n"/>
@@ -5995,14 +5793,10 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q73" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q73" s="4" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
@@ -6035,8 +5829,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G74" s="7" t="n">
-        <v>1960</v>
+      <c r="G74" s="5" t="n">
+        <v>1961</v>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
@@ -6076,14 +5870,10 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q74" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q74" s="4" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
@@ -6116,8 +5906,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G75" s="7" t="n">
-        <v>1961</v>
+      <c r="G75" s="5" t="n">
+        <v>1962</v>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
@@ -6157,14 +5947,10 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q75" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q75" s="4" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
@@ -6197,8 +5983,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G76" s="7" t="n">
-        <v>1962</v>
+      <c r="G76" s="5" t="n">
+        <v>1963</v>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
@@ -6238,14 +6024,10 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q76" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q76" s="4" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
@@ -6278,8 +6060,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G77" s="7" t="n">
-        <v>1963</v>
+      <c r="G77" s="5" t="n">
+        <v>1964</v>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
@@ -6319,14 +6101,10 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q77" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q77" s="4" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
@@ -6359,8 +6137,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G78" s="7" t="n">
-        <v>1964</v>
+      <c r="G78" s="5" t="n">
+        <v>1965</v>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
@@ -6400,14 +6178,10 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q78" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q78" s="4" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
@@ -6440,8 +6214,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G79" s="7" t="n">
-        <v>1965</v>
+      <c r="G79" s="5" t="n">
+        <v>1966</v>
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
@@ -6481,14 +6255,10 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q79" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q79" s="4" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
@@ -6521,8 +6291,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G80" s="7" t="n">
-        <v>1966</v>
+      <c r="G80" s="5" t="n">
+        <v>1967</v>
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
@@ -6562,14 +6332,10 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q80" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q80" s="4" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
@@ -6602,8 +6368,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G81" s="7" t="n">
-        <v>1967</v>
+      <c r="G81" s="5" t="n">
+        <v>1968</v>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
@@ -6643,14 +6409,10 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q81" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q81" s="4" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
@@ -6683,8 +6445,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G82" s="7" t="n">
-        <v>1968</v>
+      <c r="G82" s="5" t="n">
+        <v>1969</v>
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
@@ -6724,14 +6486,10 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q82" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q82" s="4" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
@@ -6764,8 +6522,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G83" s="7" t="n">
-        <v>1969</v>
+      <c r="G83" s="5" t="n">
+        <v>1970</v>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
@@ -6805,14 +6563,10 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q83" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q83" s="4" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
@@ -6845,8 +6599,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G84" s="7" t="n">
-        <v>1970</v>
+      <c r="G84" s="5" t="n">
+        <v>1971</v>
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
@@ -6886,14 +6640,10 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q84" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q84" s="4" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
@@ -6926,8 +6676,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G85" s="7" t="n">
-        <v>1971</v>
+      <c r="G85" s="5" t="n">
+        <v>1972</v>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
@@ -6967,14 +6717,10 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q85" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q85" s="4" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
@@ -7007,8 +6753,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G86" s="7" t="n">
-        <v>1972</v>
+      <c r="G86" s="5" t="n">
+        <v>1973</v>
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
@@ -7048,14 +6794,10 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q86" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q86" s="4" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
@@ -7088,8 +6830,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G87" s="7" t="n">
-        <v>1973</v>
+      <c r="G87" s="5" t="n">
+        <v>1974</v>
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
@@ -7129,14 +6871,10 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q87" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q87" s="4" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
@@ -7169,8 +6907,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G88" s="7" t="n">
-        <v>1974</v>
+      <c r="G88" s="5" t="n">
+        <v>1975</v>
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
@@ -7210,14 +6948,10 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q88" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q88" s="4" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
@@ -7250,8 +6984,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G89" s="7" t="n">
-        <v>1975</v>
+      <c r="G89" s="5" t="n">
+        <v>1976</v>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
@@ -7291,14 +7025,10 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q89" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q89" s="4" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
@@ -7331,8 +7061,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G90" s="7" t="n">
-        <v>1976</v>
+      <c r="G90" s="5" t="n">
+        <v>1977</v>
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
@@ -7372,14 +7102,10 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q90" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q90" s="4" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
@@ -7412,8 +7138,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G91" s="7" t="n">
-        <v>1977</v>
+      <c r="G91" s="5" t="n">
+        <v>1978</v>
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
@@ -7453,14 +7179,10 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q91" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q91" s="4" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
@@ -7493,8 +7215,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G92" s="7" t="n">
-        <v>1978</v>
+      <c r="G92" s="5" t="n">
+        <v>1979</v>
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
@@ -7534,14 +7256,10 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q92" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q92" s="4" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
@@ -7574,8 +7292,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G93" s="7" t="n">
-        <v>1979</v>
+      <c r="G93" s="5" t="n">
+        <v>1980</v>
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
@@ -7615,14 +7333,10 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q93" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q93" s="4" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
@@ -7655,8 +7369,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G94" s="7" t="n">
-        <v>1980</v>
+      <c r="G94" s="5" t="n">
+        <v>1981</v>
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
@@ -7696,14 +7410,10 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q94" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q94" s="4" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
@@ -7736,8 +7446,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G95" s="7" t="n">
-        <v>1981</v>
+      <c r="G95" s="5" t="n">
+        <v>1982</v>
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
@@ -7777,14 +7487,10 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q95" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q95" s="4" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
@@ -7817,8 +7523,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G96" s="7" t="n">
-        <v>1982</v>
+      <c r="G96" s="5" t="n">
+        <v>1983</v>
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
@@ -7858,14 +7564,10 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q96" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q96" s="4" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
@@ -7898,8 +7600,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G97" s="7" t="n">
-        <v>1983</v>
+      <c r="G97" s="5" t="n">
+        <v>1984</v>
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
@@ -7939,14 +7641,10 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q97" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q97" s="4" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
@@ -7979,8 +7677,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G98" s="7" t="n">
-        <v>1984</v>
+      <c r="G98" s="5" t="n">
+        <v>1985</v>
       </c>
       <c r="H98" s="4" t="inlineStr">
         <is>
@@ -8020,14 +7718,10 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q98" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q98" s="4" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
@@ -8060,8 +7754,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G99" s="7" t="n">
-        <v>1985</v>
+      <c r="G99" s="5" t="n">
+        <v>1986</v>
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
@@ -8101,14 +7795,10 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q99" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q99" s="4" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
@@ -8141,8 +7831,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G100" s="7" t="n">
-        <v>1986</v>
+      <c r="G100" s="5" t="n">
+        <v>1987</v>
       </c>
       <c r="H100" s="4" t="inlineStr">
         <is>
@@ -8182,14 +7872,10 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q100" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q100" s="4" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
@@ -8222,8 +7908,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G101" s="7" t="n">
-        <v>1987</v>
+      <c r="G101" s="5" t="n">
+        <v>1988</v>
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
@@ -8263,14 +7949,10 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q101" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q101" s="4" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
@@ -8303,8 +7985,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G102" s="7" t="n">
-        <v>1988</v>
+      <c r="G102" s="5" t="n">
+        <v>1989</v>
       </c>
       <c r="H102" s="4" t="inlineStr">
         <is>
@@ -8344,14 +8026,10 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q102" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q102" s="4" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
@@ -8384,8 +8062,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G103" s="7" t="n">
-        <v>1989</v>
+      <c r="G103" s="5" t="n">
+        <v>1990</v>
       </c>
       <c r="H103" s="4" t="inlineStr">
         <is>
@@ -8425,14 +8103,10 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q103" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q103" s="4" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
@@ -8465,8 +8139,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G104" s="7" t="n">
-        <v>1990</v>
+      <c r="G104" s="5" t="n">
+        <v>1991</v>
       </c>
       <c r="H104" s="4" t="inlineStr">
         <is>
@@ -8506,14 +8180,10 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q104" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q104" s="4" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
@@ -8546,8 +8216,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G105" s="7" t="n">
-        <v>1991</v>
+      <c r="G105" s="5" t="n">
+        <v>1992</v>
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
@@ -8587,14 +8257,10 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q105" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q105" s="4" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
@@ -8627,8 +8293,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G106" s="7" t="n">
-        <v>1992</v>
+      <c r="G106" s="5" t="n">
+        <v>1993</v>
       </c>
       <c r="H106" s="4" t="inlineStr">
         <is>
@@ -8668,14 +8334,10 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q106" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q106" s="4" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
@@ -8708,8 +8370,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G107" s="7" t="n">
-        <v>1993</v>
+      <c r="G107" s="5" t="n">
+        <v>1994</v>
       </c>
       <c r="H107" s="4" t="inlineStr">
         <is>
@@ -8749,14 +8411,10 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q107" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q107" s="4" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
@@ -8789,8 +8447,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G108" s="7" t="n">
-        <v>1994</v>
+      <c r="G108" s="5" t="n">
+        <v>1995</v>
       </c>
       <c r="H108" s="4" t="inlineStr">
         <is>
@@ -8830,14 +8488,10 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q108" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q108" s="4" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
@@ -8870,8 +8524,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G109" s="7" t="n">
-        <v>1995</v>
+      <c r="G109" s="5" t="n">
+        <v>1996</v>
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
@@ -8911,14 +8565,10 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q109" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q109" s="4" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
@@ -8951,8 +8601,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G110" s="7" t="n">
-        <v>1996</v>
+      <c r="G110" s="5" t="n">
+        <v>1997</v>
       </c>
       <c r="H110" s="4" t="inlineStr">
         <is>
@@ -8992,14 +8642,10 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q110" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q110" s="4" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
@@ -9032,8 +8678,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G111" s="7" t="n">
-        <v>1997</v>
+      <c r="G111" s="5" t="n">
+        <v>1998</v>
       </c>
       <c r="H111" s="4" t="inlineStr">
         <is>
@@ -9073,14 +8719,10 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q111" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q111" s="4" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
@@ -9113,8 +8755,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G112" s="7" t="n">
-        <v>1998</v>
+      <c r="G112" s="5" t="n">
+        <v>1999</v>
       </c>
       <c r="H112" s="4" t="inlineStr">
         <is>
@@ -9154,14 +8796,10 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q112" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q112" s="4" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
@@ -9194,8 +8832,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G113" s="7" t="n">
-        <v>1999</v>
+      <c r="G113" s="5" t="n">
+        <v>2000</v>
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
@@ -9235,14 +8873,10 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q113" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q113" s="4" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
@@ -9275,8 +8909,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G114" s="7" t="n">
-        <v>2000</v>
+      <c r="G114" s="5" t="n">
+        <v>2001</v>
       </c>
       <c r="H114" s="4" t="inlineStr">
         <is>
@@ -9316,14 +8950,10 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q114" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q114" s="4" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
@@ -9356,8 +8986,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G115" s="7" t="n">
-        <v>2001</v>
+      <c r="G115" s="5" t="n">
+        <v>2002</v>
       </c>
       <c r="H115" s="4" t="inlineStr">
         <is>
@@ -9397,14 +9027,10 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q115" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q115" s="4" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
@@ -9437,8 +9063,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G116" s="7" t="n">
-        <v>2002</v>
+      <c r="G116" s="5" t="n">
+        <v>2003</v>
       </c>
       <c r="H116" s="4" t="inlineStr">
         <is>
@@ -9478,14 +9104,10 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q116" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q116" s="4" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
@@ -9518,8 +9140,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G117" s="7" t="n">
-        <v>2003</v>
+      <c r="G117" s="5" t="n">
+        <v>2004</v>
       </c>
       <c r="H117" s="4" t="inlineStr">
         <is>
@@ -9559,14 +9181,10 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q117" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q117" s="4" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
@@ -9599,8 +9217,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G118" s="7" t="n">
-        <v>2004</v>
+      <c r="G118" s="5" t="n">
+        <v>2005</v>
       </c>
       <c r="H118" s="4" t="inlineStr">
         <is>
@@ -9640,14 +9258,10 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q118" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q118" s="4" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
@@ -9680,8 +9294,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G119" s="7" t="n">
-        <v>2005</v>
+      <c r="G119" s="5" t="n">
+        <v>2006</v>
       </c>
       <c r="H119" s="4" t="inlineStr">
         <is>
@@ -9721,14 +9335,10 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q119" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q119" s="4" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
@@ -9761,8 +9371,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G120" s="7" t="n">
-        <v>2006</v>
+      <c r="G120" s="5" t="n">
+        <v>2007</v>
       </c>
       <c r="H120" s="4" t="inlineStr">
         <is>
@@ -9802,14 +9412,10 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q120" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q120" s="4" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
@@ -9842,8 +9448,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G121" s="7" t="n">
-        <v>2007</v>
+      <c r="G121" s="5" t="n">
+        <v>2008</v>
       </c>
       <c r="H121" s="4" t="inlineStr">
         <is>
@@ -9883,14 +9489,10 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q121" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q121" s="4" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
@@ -9923,8 +9525,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G122" s="7" t="n">
-        <v>2008</v>
+      <c r="G122" s="5" t="n">
+        <v>2009</v>
       </c>
       <c r="H122" s="4" t="inlineStr">
         <is>
@@ -9964,14 +9566,10 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q122" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q122" s="4" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
@@ -10004,8 +9602,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G123" s="7" t="n">
-        <v>2009</v>
+      <c r="G123" s="5" t="n">
+        <v>2010</v>
       </c>
       <c r="H123" s="4" t="inlineStr">
         <is>
@@ -10045,14 +9643,10 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q123" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q123" s="4" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
@@ -10085,8 +9679,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G124" s="7" t="n">
-        <v>2010</v>
+      <c r="G124" s="5" t="n">
+        <v>2011</v>
       </c>
       <c r="H124" s="4" t="inlineStr">
         <is>
@@ -10126,14 +9720,10 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q124" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q124" s="4" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
@@ -10166,8 +9756,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G125" s="7" t="n">
-        <v>2011</v>
+      <c r="G125" s="5" t="n">
+        <v>2012</v>
       </c>
       <c r="H125" s="4" t="inlineStr">
         <is>
@@ -10207,14 +9797,10 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q125" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q125" s="4" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
@@ -10247,8 +9833,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G126" s="7" t="n">
-        <v>2012</v>
+      <c r="G126" s="5" t="n">
+        <v>2013</v>
       </c>
       <c r="H126" s="4" t="inlineStr">
         <is>
@@ -10288,14 +9874,10 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q126" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q126" s="4" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
@@ -10328,8 +9910,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G127" s="7" t="n">
-        <v>2013</v>
+      <c r="G127" s="5" t="n">
+        <v>2014</v>
       </c>
       <c r="H127" s="4" t="inlineStr">
         <is>
@@ -10369,14 +9951,10 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q127" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q127" s="4" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
@@ -10409,8 +9987,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G128" s="7" t="n">
-        <v>2014</v>
+      <c r="G128" s="5" t="n">
+        <v>2015</v>
       </c>
       <c r="H128" s="4" t="inlineStr">
         <is>
@@ -10450,14 +10028,10 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q128" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q128" s="4" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
@@ -10490,8 +10064,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G129" s="7" t="n">
-        <v>2015</v>
+      <c r="G129" s="5" t="n">
+        <v>2016</v>
       </c>
       <c r="H129" s="4" t="inlineStr">
         <is>
@@ -10531,14 +10105,10 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q129" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q129" s="4" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
@@ -10571,8 +10141,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G130" s="7" t="n">
-        <v>2016</v>
+      <c r="G130" s="5" t="n">
+        <v>2017</v>
       </c>
       <c r="H130" s="4" t="inlineStr">
         <is>
@@ -10612,14 +10182,10 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q130" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q130" s="4" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
@@ -10652,8 +10218,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G131" s="7" t="n">
-        <v>2017</v>
+      <c r="G131" s="5" t="n">
+        <v>2018</v>
       </c>
       <c r="H131" s="4" t="inlineStr">
         <is>
@@ -10693,14 +10259,10 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q131" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q131" s="4" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
@@ -10733,8 +10295,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G132" s="7" t="n">
-        <v>2018</v>
+      <c r="G132" s="5" t="n">
+        <v>2019</v>
       </c>
       <c r="H132" s="4" t="inlineStr">
         <is>
@@ -10774,14 +10336,10 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q132" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q132" s="4" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
@@ -10814,8 +10372,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G133" s="7" t="n">
-        <v>2019</v>
+      <c r="G133" s="5" t="n">
+        <v>2020</v>
       </c>
       <c r="H133" s="4" t="inlineStr">
         <is>
@@ -10855,14 +10413,10 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q133" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q133" s="4" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
@@ -10895,8 +10449,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G134" s="7" t="n">
-        <v>2020</v>
+      <c r="G134" s="5" t="n">
+        <v>2021</v>
       </c>
       <c r="H134" s="4" t="inlineStr">
         <is>
@@ -10936,14 +10490,10 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q134" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q134" s="4" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
@@ -10976,8 +10526,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G135" s="7" t="n">
-        <v>2021</v>
+      <c r="G135" s="5" t="n">
+        <v>2022</v>
       </c>
       <c r="H135" s="4" t="inlineStr">
         <is>
@@ -11017,14 +10567,10 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q135" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q135" s="4" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
@@ -11057,8 +10603,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G136" s="7" t="n">
-        <v>2022</v>
+      <c r="G136" s="5" t="n">
+        <v>2023</v>
       </c>
       <c r="H136" s="4" t="inlineStr">
         <is>
@@ -11098,14 +10644,10 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q136" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q136" s="4" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
@@ -11138,8 +10680,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G137" s="7" t="n">
-        <v>2023</v>
+      <c r="G137" s="5" t="n">
+        <v>2024</v>
       </c>
       <c r="H137" s="4" t="inlineStr">
         <is>
@@ -11179,14 +10721,10 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q137" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q137" s="4" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
@@ -11219,8 +10757,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G138" s="7" t="n">
-        <v>2024</v>
+      <c r="G138" s="5" t="n">
+        <v>2025</v>
       </c>
       <c r="H138" s="4" t="inlineStr">
         <is>
@@ -11260,14 +10798,10 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q138" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q138" s="4" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
@@ -11300,8 +10834,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G139" s="7" t="n">
-        <v>2025</v>
+      <c r="G139" s="5" t="n">
+        <v>1960</v>
       </c>
       <c r="H139" s="4" t="inlineStr">
         <is>
@@ -11315,22 +10849,22 @@
       </c>
       <c r="J139" s="4" t="inlineStr">
         <is>
-          <t>Ingresos públicos</t>
+          <t>Fiscalidad</t>
         </is>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>ingresos_publicos</t>
+          <t>fiscalidad</t>
         </is>
       </c>
       <c r="L139" s="4" t="inlineStr">
         <is>
-          <t>GC.REV.XGRT.GD.ZS</t>
+          <t>GC.TAX.TOTL.GD.ZS</t>
         </is>
       </c>
       <c r="M139" s="4" t="inlineStr">
         <is>
-          <t>Ingresos públicos excluidas donaciones como porcentaje del PIB</t>
+          <t>Ingresos tributarios como porcentaje del PIB</t>
         </is>
       </c>
       <c r="N139" s="4" t="n"/>
@@ -11341,14 +10875,10 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q139" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q139" s="4" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
@@ -11381,8 +10911,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G140" s="7" t="n">
-        <v>2026</v>
+      <c r="G140" s="5" t="n">
+        <v>1961</v>
       </c>
       <c r="H140" s="4" t="inlineStr">
         <is>
@@ -11396,22 +10926,22 @@
       </c>
       <c r="J140" s="4" t="inlineStr">
         <is>
-          <t>Ingresos públicos</t>
+          <t>Fiscalidad</t>
         </is>
       </c>
       <c r="K140" s="4" t="inlineStr">
         <is>
-          <t>ingresos_publicos</t>
+          <t>fiscalidad</t>
         </is>
       </c>
       <c r="L140" s="4" t="inlineStr">
         <is>
-          <t>GC.REV.XGRT.GD.ZS</t>
+          <t>GC.TAX.TOTL.GD.ZS</t>
         </is>
       </c>
       <c r="M140" s="4" t="inlineStr">
         <is>
-          <t>Ingresos públicos excluidas donaciones como porcentaje del PIB</t>
+          <t>Ingresos tributarios como porcentaje del PIB</t>
         </is>
       </c>
       <c r="N140" s="4" t="n"/>
@@ -11422,14 +10952,10 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q140" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q140" s="4" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
@@ -11462,8 +10988,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G141" s="7" t="n">
-        <v>1960</v>
+      <c r="G141" s="5" t="n">
+        <v>1962</v>
       </c>
       <c r="H141" s="4" t="inlineStr">
         <is>
@@ -11503,14 +11029,10 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q141" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q141" s="4" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
@@ -11543,8 +11065,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G142" s="7" t="n">
-        <v>1961</v>
+      <c r="G142" s="5" t="n">
+        <v>1963</v>
       </c>
       <c r="H142" s="4" t="inlineStr">
         <is>
@@ -11584,14 +11106,10 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q142" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q142" s="4" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
@@ -11624,8 +11142,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G143" s="7" t="n">
-        <v>1962</v>
+      <c r="G143" s="5" t="n">
+        <v>1964</v>
       </c>
       <c r="H143" s="4" t="inlineStr">
         <is>
@@ -11665,14 +11183,10 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q143" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q143" s="4" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
@@ -11705,8 +11219,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G144" s="7" t="n">
-        <v>1963</v>
+      <c r="G144" s="5" t="n">
+        <v>1965</v>
       </c>
       <c r="H144" s="4" t="inlineStr">
         <is>
@@ -11746,14 +11260,10 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q144" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q144" s="4" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
@@ -11786,8 +11296,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G145" s="7" t="n">
-        <v>1964</v>
+      <c r="G145" s="5" t="n">
+        <v>1966</v>
       </c>
       <c r="H145" s="4" t="inlineStr">
         <is>
@@ -11827,14 +11337,10 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q145" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q145" s="4" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
@@ -11867,8 +11373,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G146" s="7" t="n">
-        <v>1965</v>
+      <c r="G146" s="5" t="n">
+        <v>1967</v>
       </c>
       <c r="H146" s="4" t="inlineStr">
         <is>
@@ -11908,14 +11414,10 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q146" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q146" s="4" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
@@ -11948,8 +11450,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G147" s="7" t="n">
-        <v>1966</v>
+      <c r="G147" s="5" t="n">
+        <v>1968</v>
       </c>
       <c r="H147" s="4" t="inlineStr">
         <is>
@@ -11989,14 +11491,10 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q147" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q147" s="4" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
@@ -12029,8 +11527,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G148" s="7" t="n">
-        <v>1967</v>
+      <c r="G148" s="5" t="n">
+        <v>1969</v>
       </c>
       <c r="H148" s="4" t="inlineStr">
         <is>
@@ -12070,14 +11568,10 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q148" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q148" s="4" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
@@ -12110,8 +11604,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G149" s="7" t="n">
-        <v>1968</v>
+      <c r="G149" s="5" t="n">
+        <v>1970</v>
       </c>
       <c r="H149" s="4" t="inlineStr">
         <is>
@@ -12151,14 +11645,10 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q149" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q149" s="4" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
@@ -12191,8 +11681,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G150" s="7" t="n">
-        <v>1969</v>
+      <c r="G150" s="5" t="n">
+        <v>1971</v>
       </c>
       <c r="H150" s="4" t="inlineStr">
         <is>
@@ -12232,14 +11722,10 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q150" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q150" s="4" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
@@ -12272,8 +11758,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G151" s="7" t="n">
-        <v>1970</v>
+      <c r="G151" s="5" t="n">
+        <v>1972</v>
       </c>
       <c r="H151" s="4" t="inlineStr">
         <is>
@@ -12313,14 +11799,10 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q151" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q151" s="4" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
@@ -12353,8 +11835,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G152" s="7" t="n">
-        <v>1971</v>
+      <c r="G152" s="5" t="n">
+        <v>1973</v>
       </c>
       <c r="H152" s="4" t="inlineStr">
         <is>
@@ -12394,14 +11876,10 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q152" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q152" s="4" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
@@ -12434,8 +11912,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G153" s="7" t="n">
-        <v>1972</v>
+      <c r="G153" s="5" t="n">
+        <v>1974</v>
       </c>
       <c r="H153" s="4" t="inlineStr">
         <is>
@@ -12475,14 +11953,10 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q153" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q153" s="4" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
@@ -12515,8 +11989,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G154" s="7" t="n">
-        <v>1973</v>
+      <c r="G154" s="5" t="n">
+        <v>1975</v>
       </c>
       <c r="H154" s="4" t="inlineStr">
         <is>
@@ -12556,14 +12030,10 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q154" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q154" s="4" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
@@ -12596,8 +12066,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G155" s="7" t="n">
-        <v>1974</v>
+      <c r="G155" s="5" t="n">
+        <v>1976</v>
       </c>
       <c r="H155" s="4" t="inlineStr">
         <is>
@@ -12637,14 +12107,10 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q155" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q155" s="4" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
@@ -12677,8 +12143,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G156" s="7" t="n">
-        <v>1975</v>
+      <c r="G156" s="5" t="n">
+        <v>1977</v>
       </c>
       <c r="H156" s="4" t="inlineStr">
         <is>
@@ -12718,14 +12184,10 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q156" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q156" s="4" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
@@ -12758,8 +12220,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G157" s="7" t="n">
-        <v>1976</v>
+      <c r="G157" s="5" t="n">
+        <v>1978</v>
       </c>
       <c r="H157" s="4" t="inlineStr">
         <is>
@@ -12799,14 +12261,10 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q157" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q157" s="4" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
@@ -12839,8 +12297,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G158" s="7" t="n">
-        <v>1977</v>
+      <c r="G158" s="5" t="n">
+        <v>1979</v>
       </c>
       <c r="H158" s="4" t="inlineStr">
         <is>
@@ -12880,14 +12338,10 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q158" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q158" s="4" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
@@ -12920,8 +12374,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G159" s="7" t="n">
-        <v>1978</v>
+      <c r="G159" s="5" t="n">
+        <v>1980</v>
       </c>
       <c r="H159" s="4" t="inlineStr">
         <is>
@@ -12961,14 +12415,10 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q159" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q159" s="4" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
@@ -13001,8 +12451,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G160" s="7" t="n">
-        <v>1979</v>
+      <c r="G160" s="5" t="n">
+        <v>1981</v>
       </c>
       <c r="H160" s="4" t="inlineStr">
         <is>
@@ -13042,14 +12492,10 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q160" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q160" s="4" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
@@ -13082,8 +12528,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G161" s="7" t="n">
-        <v>1980</v>
+      <c r="G161" s="5" t="n">
+        <v>1982</v>
       </c>
       <c r="H161" s="4" t="inlineStr">
         <is>
@@ -13123,14 +12569,10 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q161" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q161" s="4" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
@@ -13163,8 +12605,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G162" s="7" t="n">
-        <v>1981</v>
+      <c r="G162" s="5" t="n">
+        <v>1983</v>
       </c>
       <c r="H162" s="4" t="inlineStr">
         <is>
@@ -13204,14 +12646,10 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q162" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q162" s="4" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
@@ -13244,8 +12682,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G163" s="7" t="n">
-        <v>1982</v>
+      <c r="G163" s="5" t="n">
+        <v>1984</v>
       </c>
       <c r="H163" s="4" t="inlineStr">
         <is>
@@ -13285,14 +12723,10 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q163" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q163" s="4" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
@@ -13325,8 +12759,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G164" s="7" t="n">
-        <v>1983</v>
+      <c r="G164" s="5" t="n">
+        <v>1985</v>
       </c>
       <c r="H164" s="4" t="inlineStr">
         <is>
@@ -13366,14 +12800,10 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q164" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q164" s="4" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
@@ -13406,8 +12836,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G165" s="7" t="n">
-        <v>1984</v>
+      <c r="G165" s="5" t="n">
+        <v>1986</v>
       </c>
       <c r="H165" s="4" t="inlineStr">
         <is>
@@ -13447,14 +12877,10 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q165" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q165" s="4" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
@@ -13487,8 +12913,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G166" s="7" t="n">
-        <v>1985</v>
+      <c r="G166" s="5" t="n">
+        <v>1987</v>
       </c>
       <c r="H166" s="4" t="inlineStr">
         <is>
@@ -13528,14 +12954,10 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q166" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q166" s="4" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
@@ -13568,8 +12990,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G167" s="7" t="n">
-        <v>1986</v>
+      <c r="G167" s="5" t="n">
+        <v>1988</v>
       </c>
       <c r="H167" s="4" t="inlineStr">
         <is>
@@ -13609,14 +13031,10 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q167" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q167" s="4" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
@@ -13649,8 +13067,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G168" s="7" t="n">
-        <v>1987</v>
+      <c r="G168" s="5" t="n">
+        <v>1989</v>
       </c>
       <c r="H168" s="4" t="inlineStr">
         <is>
@@ -13690,14 +13108,10 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q168" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q168" s="4" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
@@ -13730,8 +13144,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G169" s="7" t="n">
-        <v>1988</v>
+      <c r="G169" s="5" t="n">
+        <v>1990</v>
       </c>
       <c r="H169" s="4" t="inlineStr">
         <is>
@@ -13771,14 +13185,10 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q169" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q169" s="4" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
@@ -13811,8 +13221,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G170" s="7" t="n">
-        <v>1989</v>
+      <c r="G170" s="5" t="n">
+        <v>1991</v>
       </c>
       <c r="H170" s="4" t="inlineStr">
         <is>
@@ -13852,14 +13262,10 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q170" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q170" s="4" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
@@ -13892,8 +13298,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G171" s="7" t="n">
-        <v>1990</v>
+      <c r="G171" s="5" t="n">
+        <v>1992</v>
       </c>
       <c r="H171" s="4" t="inlineStr">
         <is>
@@ -13933,14 +13339,10 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q171" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q171" s="4" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
@@ -13973,8 +13375,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G172" s="7" t="n">
-        <v>1991</v>
+      <c r="G172" s="5" t="n">
+        <v>1993</v>
       </c>
       <c r="H172" s="4" t="inlineStr">
         <is>
@@ -14014,14 +13416,10 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q172" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q172" s="4" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
@@ -14054,8 +13452,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G173" s="7" t="n">
-        <v>1992</v>
+      <c r="G173" s="5" t="n">
+        <v>1994</v>
       </c>
       <c r="H173" s="4" t="inlineStr">
         <is>
@@ -14095,14 +13493,10 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q173" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q173" s="4" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
@@ -14135,8 +13529,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G174" s="7" t="n">
-        <v>1993</v>
+      <c r="G174" s="5" t="n">
+        <v>1995</v>
       </c>
       <c r="H174" s="4" t="inlineStr">
         <is>
@@ -14176,14 +13570,10 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q174" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q174" s="4" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
@@ -14216,8 +13606,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G175" s="7" t="n">
-        <v>1994</v>
+      <c r="G175" s="5" t="n">
+        <v>1996</v>
       </c>
       <c r="H175" s="4" t="inlineStr">
         <is>
@@ -14257,14 +13647,10 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q175" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q175" s="4" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="4" t="inlineStr">
@@ -14297,8 +13683,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G176" s="7" t="n">
-        <v>1995</v>
+      <c r="G176" s="5" t="n">
+        <v>1997</v>
       </c>
       <c r="H176" s="4" t="inlineStr">
         <is>
@@ -14338,14 +13724,10 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q176" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q176" s="4" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
@@ -14378,8 +13760,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G177" s="7" t="n">
-        <v>1996</v>
+      <c r="G177" s="5" t="n">
+        <v>1998</v>
       </c>
       <c r="H177" s="4" t="inlineStr">
         <is>
@@ -14419,14 +13801,10 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q177" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q177" s="4" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
@@ -14459,8 +13837,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G178" s="7" t="n">
-        <v>1997</v>
+      <c r="G178" s="5" t="n">
+        <v>1999</v>
       </c>
       <c r="H178" s="4" t="inlineStr">
         <is>
@@ -14500,14 +13878,10 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q178" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q178" s="4" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
@@ -14540,8 +13914,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G179" s="7" t="n">
-        <v>1998</v>
+      <c r="G179" s="5" t="n">
+        <v>2000</v>
       </c>
       <c r="H179" s="4" t="inlineStr">
         <is>
@@ -14581,14 +13955,10 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q179" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q179" s="4" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="4" t="inlineStr">
@@ -14621,8 +13991,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G180" s="7" t="n">
-        <v>1999</v>
+      <c r="G180" s="5" t="n">
+        <v>2001</v>
       </c>
       <c r="H180" s="4" t="inlineStr">
         <is>
@@ -14662,14 +14032,10 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q180" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q180" s="4" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
@@ -14702,8 +14068,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G181" s="7" t="n">
-        <v>2000</v>
+      <c r="G181" s="5" t="n">
+        <v>2002</v>
       </c>
       <c r="H181" s="4" t="inlineStr">
         <is>
@@ -14743,14 +14109,10 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q181" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q181" s="4" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
@@ -14783,8 +14145,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G182" s="7" t="n">
-        <v>2001</v>
+      <c r="G182" s="5" t="n">
+        <v>2003</v>
       </c>
       <c r="H182" s="4" t="inlineStr">
         <is>
@@ -14824,14 +14186,10 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q182" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q182" s="4" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
@@ -14864,8 +14222,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G183" s="7" t="n">
-        <v>2002</v>
+      <c r="G183" s="5" t="n">
+        <v>2004</v>
       </c>
       <c r="H183" s="4" t="inlineStr">
         <is>
@@ -14905,14 +14263,10 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q183" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q183" s="4" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
@@ -14945,8 +14299,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G184" s="7" t="n">
-        <v>2003</v>
+      <c r="G184" s="5" t="n">
+        <v>2005</v>
       </c>
       <c r="H184" s="4" t="inlineStr">
         <is>
@@ -14986,14 +14340,10 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q184" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q184" s="4" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
@@ -15026,8 +14376,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G185" s="7" t="n">
-        <v>2004</v>
+      <c r="G185" s="5" t="n">
+        <v>2006</v>
       </c>
       <c r="H185" s="4" t="inlineStr">
         <is>
@@ -15067,14 +14417,10 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q185" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q185" s="4" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
@@ -15107,8 +14453,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G186" s="7" t="n">
-        <v>2005</v>
+      <c r="G186" s="5" t="n">
+        <v>2007</v>
       </c>
       <c r="H186" s="4" t="inlineStr">
         <is>
@@ -15148,14 +14494,10 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q186" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q186" s="4" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
@@ -15188,8 +14530,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G187" s="7" t="n">
-        <v>2006</v>
+      <c r="G187" s="5" t="n">
+        <v>2008</v>
       </c>
       <c r="H187" s="4" t="inlineStr">
         <is>
@@ -15229,14 +14571,10 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q187" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q187" s="4" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="4" t="inlineStr">
@@ -15269,8 +14607,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G188" s="7" t="n">
-        <v>2007</v>
+      <c r="G188" s="5" t="n">
+        <v>2009</v>
       </c>
       <c r="H188" s="4" t="inlineStr">
         <is>
@@ -15310,14 +14648,10 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q188" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q188" s="4" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
@@ -15350,8 +14684,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G189" s="7" t="n">
-        <v>2008</v>
+      <c r="G189" s="5" t="n">
+        <v>2010</v>
       </c>
       <c r="H189" s="4" t="inlineStr">
         <is>
@@ -15391,14 +14725,10 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q189" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q189" s="4" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="4" t="inlineStr">
@@ -15431,8 +14761,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G190" s="7" t="n">
-        <v>2009</v>
+      <c r="G190" s="5" t="n">
+        <v>2011</v>
       </c>
       <c r="H190" s="4" t="inlineStr">
         <is>
@@ -15472,14 +14802,10 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q190" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q190" s="4" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
@@ -15512,8 +14838,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G191" s="7" t="n">
-        <v>2010</v>
+      <c r="G191" s="5" t="n">
+        <v>2012</v>
       </c>
       <c r="H191" s="4" t="inlineStr">
         <is>
@@ -15553,14 +14879,10 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q191" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q191" s="4" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
@@ -15593,8 +14915,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G192" s="7" t="n">
-        <v>2011</v>
+      <c r="G192" s="5" t="n">
+        <v>2013</v>
       </c>
       <c r="H192" s="4" t="inlineStr">
         <is>
@@ -15634,14 +14956,10 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q192" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q192" s="4" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
@@ -15674,8 +14992,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G193" s="7" t="n">
-        <v>2012</v>
+      <c r="G193" s="5" t="n">
+        <v>2014</v>
       </c>
       <c r="H193" s="4" t="inlineStr">
         <is>
@@ -15715,14 +15033,10 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q193" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q193" s="4" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="4" t="inlineStr">
@@ -15755,8 +15069,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G194" s="7" t="n">
-        <v>2013</v>
+      <c r="G194" s="5" t="n">
+        <v>2015</v>
       </c>
       <c r="H194" s="4" t="inlineStr">
         <is>
@@ -15796,14 +15110,10 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q194" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q194" s="4" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
@@ -15836,8 +15146,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G195" s="7" t="n">
-        <v>2014</v>
+      <c r="G195" s="5" t="n">
+        <v>2016</v>
       </c>
       <c r="H195" s="4" t="inlineStr">
         <is>
@@ -15877,14 +15187,10 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q195" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q195" s="4" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="4" t="inlineStr">
@@ -15917,8 +15223,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G196" s="7" t="n">
-        <v>2015</v>
+      <c r="G196" s="5" t="n">
+        <v>2017</v>
       </c>
       <c r="H196" s="4" t="inlineStr">
         <is>
@@ -15958,14 +15264,10 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q196" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q196" s="4" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="4" t="inlineStr">
@@ -15998,8 +15300,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G197" s="7" t="n">
-        <v>2016</v>
+      <c r="G197" s="5" t="n">
+        <v>2018</v>
       </c>
       <c r="H197" s="4" t="inlineStr">
         <is>
@@ -16039,14 +15341,10 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q197" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q197" s="4" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="4" t="inlineStr">
@@ -16079,8 +15377,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G198" s="7" t="n">
-        <v>2017</v>
+      <c r="G198" s="5" t="n">
+        <v>2019</v>
       </c>
       <c r="H198" s="4" t="inlineStr">
         <is>
@@ -16120,14 +15418,10 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q198" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q198" s="4" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="4" t="inlineStr">
@@ -16160,8 +15454,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G199" s="7" t="n">
-        <v>2018</v>
+      <c r="G199" s="5" t="n">
+        <v>2020</v>
       </c>
       <c r="H199" s="4" t="inlineStr">
         <is>
@@ -16201,14 +15495,10 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q199" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q199" s="4" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="4" t="inlineStr">
@@ -16241,8 +15531,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G200" s="7" t="n">
-        <v>2019</v>
+      <c r="G200" s="5" t="n">
+        <v>2021</v>
       </c>
       <c r="H200" s="4" t="inlineStr">
         <is>
@@ -16282,14 +15572,10 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q200" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q200" s="4" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="4" t="inlineStr">
@@ -16322,8 +15608,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G201" s="7" t="n">
-        <v>2020</v>
+      <c r="G201" s="5" t="n">
+        <v>2022</v>
       </c>
       <c r="H201" s="4" t="inlineStr">
         <is>
@@ -16363,14 +15649,10 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q201" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q201" s="4" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="4" t="inlineStr">
@@ -16403,8 +15685,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G202" s="7" t="n">
-        <v>2021</v>
+      <c r="G202" s="5" t="n">
+        <v>2023</v>
       </c>
       <c r="H202" s="4" t="inlineStr">
         <is>
@@ -16444,14 +15726,10 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q202" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q202" s="4" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
@@ -16484,8 +15762,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G203" s="7" t="n">
-        <v>2022</v>
+      <c r="G203" s="5" t="n">
+        <v>2024</v>
       </c>
       <c r="H203" s="4" t="inlineStr">
         <is>
@@ -16525,14 +15803,10 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q203" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q203" s="4" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="4" t="inlineStr">
@@ -16565,8 +15839,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G204" s="7" t="n">
-        <v>2023</v>
+      <c r="G204" s="5" t="n">
+        <v>2025</v>
       </c>
       <c r="H204" s="4" t="inlineStr">
         <is>
@@ -16606,14 +15880,10 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q204" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q204" s="4" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
@@ -16646,8 +15916,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G205" s="7" t="n">
-        <v>2024</v>
+      <c r="G205" s="5" t="n">
+        <v>1960</v>
       </c>
       <c r="H205" s="4" t="inlineStr">
         <is>
@@ -16661,22 +15931,22 @@
       </c>
       <c r="J205" s="4" t="inlineStr">
         <is>
-          <t>Fiscalidad</t>
+          <t>Gasto público</t>
         </is>
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>fiscalidad</t>
+          <t>gasto_publico</t>
         </is>
       </c>
       <c r="L205" s="4" t="inlineStr">
         <is>
-          <t>GC.TAX.TOTL.GD.ZS</t>
+          <t>GC.XPN.TOTL.GD.ZS</t>
         </is>
       </c>
       <c r="M205" s="4" t="inlineStr">
         <is>
-          <t>Ingresos tributarios como porcentaje del PIB</t>
+          <t>Gasto público como porcentaje del PIB</t>
         </is>
       </c>
       <c r="N205" s="4" t="n"/>
@@ -16687,14 +15957,10 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q205" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q205" s="4" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="4" t="inlineStr">
@@ -16727,8 +15993,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G206" s="7" t="n">
-        <v>2025</v>
+      <c r="G206" s="5" t="n">
+        <v>1961</v>
       </c>
       <c r="H206" s="4" t="inlineStr">
         <is>
@@ -16742,22 +16008,22 @@
       </c>
       <c r="J206" s="4" t="inlineStr">
         <is>
-          <t>Fiscalidad</t>
+          <t>Gasto público</t>
         </is>
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>fiscalidad</t>
+          <t>gasto_publico</t>
         </is>
       </c>
       <c r="L206" s="4" t="inlineStr">
         <is>
-          <t>GC.TAX.TOTL.GD.ZS</t>
+          <t>GC.XPN.TOTL.GD.ZS</t>
         </is>
       </c>
       <c r="M206" s="4" t="inlineStr">
         <is>
-          <t>Ingresos tributarios como porcentaje del PIB</t>
+          <t>Gasto público como porcentaje del PIB</t>
         </is>
       </c>
       <c r="N206" s="4" t="n"/>
@@ -16768,14 +16034,10 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q206" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q206" s="4" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
@@ -16808,8 +16070,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G207" s="7" t="n">
-        <v>2026</v>
+      <c r="G207" s="5" t="n">
+        <v>1962</v>
       </c>
       <c r="H207" s="4" t="inlineStr">
         <is>
@@ -16823,22 +16085,22 @@
       </c>
       <c r="J207" s="4" t="inlineStr">
         <is>
-          <t>Fiscalidad</t>
+          <t>Gasto público</t>
         </is>
       </c>
       <c r="K207" s="4" t="inlineStr">
         <is>
-          <t>fiscalidad</t>
+          <t>gasto_publico</t>
         </is>
       </c>
       <c r="L207" s="4" t="inlineStr">
         <is>
-          <t>GC.TAX.TOTL.GD.ZS</t>
+          <t>GC.XPN.TOTL.GD.ZS</t>
         </is>
       </c>
       <c r="M207" s="4" t="inlineStr">
         <is>
-          <t>Ingresos tributarios como porcentaje del PIB</t>
+          <t>Gasto público como porcentaje del PIB</t>
         </is>
       </c>
       <c r="N207" s="4" t="n"/>
@@ -16849,14 +16111,10 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q207" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q207" s="4" t="n"/>
     </row>
     <row r="208">
       <c r="A208" s="4" t="inlineStr">
@@ -16889,8 +16147,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G208" s="7" t="n">
-        <v>1960</v>
+      <c r="G208" s="5" t="n">
+        <v>1963</v>
       </c>
       <c r="H208" s="4" t="inlineStr">
         <is>
@@ -16930,14 +16188,10 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q208" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q208" s="4" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
@@ -16970,8 +16224,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G209" s="7" t="n">
-        <v>1961</v>
+      <c r="G209" s="5" t="n">
+        <v>1964</v>
       </c>
       <c r="H209" s="4" t="inlineStr">
         <is>
@@ -17011,14 +16265,10 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q209" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q209" s="4" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="4" t="inlineStr">
@@ -17051,8 +16301,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G210" s="7" t="n">
-        <v>1962</v>
+      <c r="G210" s="5" t="n">
+        <v>1965</v>
       </c>
       <c r="H210" s="4" t="inlineStr">
         <is>
@@ -17092,14 +16342,10 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q210" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q210" s="4" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="4" t="inlineStr">
@@ -17132,8 +16378,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G211" s="7" t="n">
-        <v>1963</v>
+      <c r="G211" s="5" t="n">
+        <v>1966</v>
       </c>
       <c r="H211" s="4" t="inlineStr">
         <is>
@@ -17173,14 +16419,10 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q211" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q211" s="4" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="4" t="inlineStr">
@@ -17213,8 +16455,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G212" s="7" t="n">
-        <v>1964</v>
+      <c r="G212" s="5" t="n">
+        <v>1967</v>
       </c>
       <c r="H212" s="4" t="inlineStr">
         <is>
@@ -17254,14 +16496,10 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q212" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q212" s="4" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="4" t="inlineStr">
@@ -17294,8 +16532,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G213" s="7" t="n">
-        <v>1965</v>
+      <c r="G213" s="5" t="n">
+        <v>1968</v>
       </c>
       <c r="H213" s="4" t="inlineStr">
         <is>
@@ -17335,14 +16573,10 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q213" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q213" s="4" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="4" t="inlineStr">
@@ -17375,8 +16609,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G214" s="7" t="n">
-        <v>1966</v>
+      <c r="G214" s="5" t="n">
+        <v>1969</v>
       </c>
       <c r="H214" s="4" t="inlineStr">
         <is>
@@ -17416,14 +16650,10 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q214" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q214" s="4" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="4" t="inlineStr">
@@ -17456,8 +16686,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G215" s="7" t="n">
-        <v>1967</v>
+      <c r="G215" s="5" t="n">
+        <v>1970</v>
       </c>
       <c r="H215" s="4" t="inlineStr">
         <is>
@@ -17497,14 +16727,10 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q215" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q215" s="4" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="4" t="inlineStr">
@@ -17537,8 +16763,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G216" s="7" t="n">
-        <v>1968</v>
+      <c r="G216" s="5" t="n">
+        <v>1971</v>
       </c>
       <c r="H216" s="4" t="inlineStr">
         <is>
@@ -17578,14 +16804,10 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q216" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q216" s="4" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="4" t="inlineStr">
@@ -17618,8 +16840,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G217" s="7" t="n">
-        <v>1969</v>
+      <c r="G217" s="5" t="n">
+        <v>1972</v>
       </c>
       <c r="H217" s="4" t="inlineStr">
         <is>
@@ -17659,14 +16881,10 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q217" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q217" s="4" t="n"/>
     </row>
     <row r="218">
       <c r="A218" s="4" t="inlineStr">
@@ -17699,8 +16917,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G218" s="7" t="n">
-        <v>1970</v>
+      <c r="G218" s="5" t="n">
+        <v>1973</v>
       </c>
       <c r="H218" s="4" t="inlineStr">
         <is>
@@ -17740,14 +16958,10 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q218" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q218" s="4" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="4" t="inlineStr">
@@ -17780,8 +16994,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G219" s="7" t="n">
-        <v>1971</v>
+      <c r="G219" s="5" t="n">
+        <v>1974</v>
       </c>
       <c r="H219" s="4" t="inlineStr">
         <is>
@@ -17821,14 +17035,10 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q219" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q219" s="4" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="4" t="inlineStr">
@@ -17861,8 +17071,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G220" s="7" t="n">
-        <v>1972</v>
+      <c r="G220" s="5" t="n">
+        <v>1975</v>
       </c>
       <c r="H220" s="4" t="inlineStr">
         <is>
@@ -17902,14 +17112,10 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q220" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q220" s="4" t="n"/>
     </row>
     <row r="221">
       <c r="A221" s="4" t="inlineStr">
@@ -17942,8 +17148,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G221" s="7" t="n">
-        <v>1973</v>
+      <c r="G221" s="5" t="n">
+        <v>1976</v>
       </c>
       <c r="H221" s="4" t="inlineStr">
         <is>
@@ -17983,14 +17189,10 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q221" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q221" s="4" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="4" t="inlineStr">
@@ -18023,8 +17225,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G222" s="7" t="n">
-        <v>1974</v>
+      <c r="G222" s="5" t="n">
+        <v>1977</v>
       </c>
       <c r="H222" s="4" t="inlineStr">
         <is>
@@ -18064,14 +17266,10 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q222" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q222" s="4" t="n"/>
     </row>
     <row r="223">
       <c r="A223" s="4" t="inlineStr">
@@ -18104,8 +17302,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G223" s="7" t="n">
-        <v>1975</v>
+      <c r="G223" s="5" t="n">
+        <v>1978</v>
       </c>
       <c r="H223" s="4" t="inlineStr">
         <is>
@@ -18145,14 +17343,10 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q223" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q223" s="4" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="4" t="inlineStr">
@@ -18185,8 +17379,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G224" s="7" t="n">
-        <v>1976</v>
+      <c r="G224" s="5" t="n">
+        <v>1979</v>
       </c>
       <c r="H224" s="4" t="inlineStr">
         <is>
@@ -18226,14 +17420,10 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q224" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q224" s="4" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="4" t="inlineStr">
@@ -18266,8 +17456,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G225" s="7" t="n">
-        <v>1977</v>
+      <c r="G225" s="5" t="n">
+        <v>1980</v>
       </c>
       <c r="H225" s="4" t="inlineStr">
         <is>
@@ -18307,14 +17497,10 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q225" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q225" s="4" t="n"/>
     </row>
     <row r="226">
       <c r="A226" s="4" t="inlineStr">
@@ -18347,8 +17533,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G226" s="7" t="n">
-        <v>1978</v>
+      <c r="G226" s="5" t="n">
+        <v>1981</v>
       </c>
       <c r="H226" s="4" t="inlineStr">
         <is>
@@ -18388,14 +17574,10 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q226" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q226" s="4" t="n"/>
     </row>
     <row r="227">
       <c r="A227" s="4" t="inlineStr">
@@ -18428,8 +17610,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G227" s="7" t="n">
-        <v>1979</v>
+      <c r="G227" s="5" t="n">
+        <v>1982</v>
       </c>
       <c r="H227" s="4" t="inlineStr">
         <is>
@@ -18469,14 +17651,10 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q227" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q227" s="4" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="4" t="inlineStr">
@@ -18509,8 +17687,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G228" s="7" t="n">
-        <v>1980</v>
+      <c r="G228" s="5" t="n">
+        <v>1983</v>
       </c>
       <c r="H228" s="4" t="inlineStr">
         <is>
@@ -18550,14 +17728,10 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q228" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q228" s="4" t="n"/>
     </row>
     <row r="229">
       <c r="A229" s="4" t="inlineStr">
@@ -18590,8 +17764,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G229" s="7" t="n">
-        <v>1981</v>
+      <c r="G229" s="5" t="n">
+        <v>1984</v>
       </c>
       <c r="H229" s="4" t="inlineStr">
         <is>
@@ -18631,14 +17805,10 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q229" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q229" s="4" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="4" t="inlineStr">
@@ -18671,8 +17841,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G230" s="7" t="n">
-        <v>1982</v>
+      <c r="G230" s="5" t="n">
+        <v>1985</v>
       </c>
       <c r="H230" s="4" t="inlineStr">
         <is>
@@ -18712,14 +17882,10 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q230" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q230" s="4" t="n"/>
     </row>
     <row r="231">
       <c r="A231" s="4" t="inlineStr">
@@ -18752,8 +17918,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G231" s="7" t="n">
-        <v>1983</v>
+      <c r="G231" s="5" t="n">
+        <v>1986</v>
       </c>
       <c r="H231" s="4" t="inlineStr">
         <is>
@@ -18793,14 +17959,10 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q231" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q231" s="4" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="4" t="inlineStr">
@@ -18833,8 +17995,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G232" s="7" t="n">
-        <v>1984</v>
+      <c r="G232" s="5" t="n">
+        <v>1987</v>
       </c>
       <c r="H232" s="4" t="inlineStr">
         <is>
@@ -18874,14 +18036,10 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q232" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q232" s="4" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="4" t="inlineStr">
@@ -18914,8 +18072,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G233" s="7" t="n">
-        <v>1985</v>
+      <c r="G233" s="5" t="n">
+        <v>1988</v>
       </c>
       <c r="H233" s="4" t="inlineStr">
         <is>
@@ -18955,14 +18113,10 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q233" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q233" s="4" t="n"/>
     </row>
     <row r="234">
       <c r="A234" s="4" t="inlineStr">
@@ -18995,8 +18149,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G234" s="7" t="n">
-        <v>1986</v>
+      <c r="G234" s="5" t="n">
+        <v>1989</v>
       </c>
       <c r="H234" s="4" t="inlineStr">
         <is>
@@ -19036,14 +18190,10 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q234" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q234" s="4" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="4" t="inlineStr">
@@ -19076,8 +18226,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G235" s="7" t="n">
-        <v>1987</v>
+      <c r="G235" s="5" t="n">
+        <v>1990</v>
       </c>
       <c r="H235" s="4" t="inlineStr">
         <is>
@@ -19117,14 +18267,10 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q235" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q235" s="4" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="4" t="inlineStr">
@@ -19157,8 +18303,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G236" s="7" t="n">
-        <v>1988</v>
+      <c r="G236" s="5" t="n">
+        <v>1991</v>
       </c>
       <c r="H236" s="4" t="inlineStr">
         <is>
@@ -19198,14 +18344,10 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q236" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q236" s="4" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="4" t="inlineStr">
@@ -19238,8 +18380,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G237" s="7" t="n">
-        <v>1989</v>
+      <c r="G237" s="5" t="n">
+        <v>1992</v>
       </c>
       <c r="H237" s="4" t="inlineStr">
         <is>
@@ -19279,14 +18421,10 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q237" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q237" s="4" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="4" t="inlineStr">
@@ -19319,8 +18457,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G238" s="7" t="n">
-        <v>1990</v>
+      <c r="G238" s="5" t="n">
+        <v>1993</v>
       </c>
       <c r="H238" s="4" t="inlineStr">
         <is>
@@ -19360,14 +18498,10 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q238" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q238" s="4" t="n"/>
     </row>
     <row r="239">
       <c r="A239" s="4" t="inlineStr">
@@ -19400,8 +18534,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G239" s="7" t="n">
-        <v>1991</v>
+      <c r="G239" s="5" t="n">
+        <v>1994</v>
       </c>
       <c r="H239" s="4" t="inlineStr">
         <is>
@@ -19441,14 +18575,10 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q239" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q239" s="4" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="4" t="inlineStr">
@@ -19481,8 +18611,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G240" s="7" t="n">
-        <v>1992</v>
+      <c r="G240" s="5" t="n">
+        <v>1995</v>
       </c>
       <c r="H240" s="4" t="inlineStr">
         <is>
@@ -19522,14 +18652,10 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q240" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q240" s="4" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="4" t="inlineStr">
@@ -19562,8 +18688,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G241" s="7" t="n">
-        <v>1993</v>
+      <c r="G241" s="5" t="n">
+        <v>1996</v>
       </c>
       <c r="H241" s="4" t="inlineStr">
         <is>
@@ -19603,14 +18729,10 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q241" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q241" s="4" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="4" t="inlineStr">
@@ -19643,8 +18765,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G242" s="7" t="n">
-        <v>1994</v>
+      <c r="G242" s="5" t="n">
+        <v>1997</v>
       </c>
       <c r="H242" s="4" t="inlineStr">
         <is>
@@ -19684,14 +18806,10 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q242" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q242" s="4" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="4" t="inlineStr">
@@ -19724,8 +18842,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G243" s="7" t="n">
-        <v>1995</v>
+      <c r="G243" s="5" t="n">
+        <v>1998</v>
       </c>
       <c r="H243" s="4" t="inlineStr">
         <is>
@@ -19765,14 +18883,10 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q243" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q243" s="4" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="4" t="inlineStr">
@@ -19805,8 +18919,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G244" s="7" t="n">
-        <v>1996</v>
+      <c r="G244" s="5" t="n">
+        <v>1999</v>
       </c>
       <c r="H244" s="4" t="inlineStr">
         <is>
@@ -19846,14 +18960,10 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q244" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q244" s="4" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="4" t="inlineStr">
@@ -19886,8 +18996,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G245" s="7" t="n">
-        <v>1997</v>
+      <c r="G245" s="5" t="n">
+        <v>2000</v>
       </c>
       <c r="H245" s="4" t="inlineStr">
         <is>
@@ -19927,14 +19037,10 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q245" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q245" s="4" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="4" t="inlineStr">
@@ -19967,8 +19073,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G246" s="7" t="n">
-        <v>1998</v>
+      <c r="G246" s="5" t="n">
+        <v>2001</v>
       </c>
       <c r="H246" s="4" t="inlineStr">
         <is>
@@ -20008,14 +19114,10 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q246" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q246" s="4" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="4" t="inlineStr">
@@ -20048,8 +19150,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G247" s="7" t="n">
-        <v>1999</v>
+      <c r="G247" s="5" t="n">
+        <v>2002</v>
       </c>
       <c r="H247" s="4" t="inlineStr">
         <is>
@@ -20089,14 +19191,10 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q247" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q247" s="4" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="4" t="inlineStr">
@@ -20129,8 +19227,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G248" s="7" t="n">
-        <v>2000</v>
+      <c r="G248" s="5" t="n">
+        <v>2003</v>
       </c>
       <c r="H248" s="4" t="inlineStr">
         <is>
@@ -20170,14 +19268,10 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q248" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q248" s="4" t="n"/>
     </row>
     <row r="249">
       <c r="A249" s="4" t="inlineStr">
@@ -20210,8 +19304,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G249" s="7" t="n">
-        <v>2001</v>
+      <c r="G249" s="5" t="n">
+        <v>2004</v>
       </c>
       <c r="H249" s="4" t="inlineStr">
         <is>
@@ -20251,14 +19345,10 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q249" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q249" s="4" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="4" t="inlineStr">
@@ -20291,8 +19381,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G250" s="7" t="n">
-        <v>2002</v>
+      <c r="G250" s="5" t="n">
+        <v>2005</v>
       </c>
       <c r="H250" s="4" t="inlineStr">
         <is>
@@ -20332,14 +19422,10 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q250" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q250" s="4" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="4" t="inlineStr">
@@ -20372,8 +19458,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G251" s="7" t="n">
-        <v>2003</v>
+      <c r="G251" s="5" t="n">
+        <v>2006</v>
       </c>
       <c r="H251" s="4" t="inlineStr">
         <is>
@@ -20413,14 +19499,10 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q251" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q251" s="4" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="4" t="inlineStr">
@@ -20453,8 +19535,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G252" s="7" t="n">
-        <v>2004</v>
+      <c r="G252" s="5" t="n">
+        <v>2007</v>
       </c>
       <c r="H252" s="4" t="inlineStr">
         <is>
@@ -20494,14 +19576,10 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q252" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q252" s="4" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="4" t="inlineStr">
@@ -20534,8 +19612,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G253" s="7" t="n">
-        <v>2005</v>
+      <c r="G253" s="5" t="n">
+        <v>2008</v>
       </c>
       <c r="H253" s="4" t="inlineStr">
         <is>
@@ -20575,14 +19653,10 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q253" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q253" s="4" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="4" t="inlineStr">
@@ -20615,8 +19689,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G254" s="7" t="n">
-        <v>2006</v>
+      <c r="G254" s="5" t="n">
+        <v>2009</v>
       </c>
       <c r="H254" s="4" t="inlineStr">
         <is>
@@ -20656,14 +19730,10 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q254" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q254" s="4" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="4" t="inlineStr">
@@ -20696,8 +19766,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G255" s="7" t="n">
-        <v>2007</v>
+      <c r="G255" s="5" t="n">
+        <v>2010</v>
       </c>
       <c r="H255" s="4" t="inlineStr">
         <is>
@@ -20737,14 +19807,10 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q255" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q255" s="4" t="n"/>
     </row>
     <row r="256">
       <c r="A256" s="4" t="inlineStr">
@@ -20777,8 +19843,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G256" s="7" t="n">
-        <v>2008</v>
+      <c r="G256" s="5" t="n">
+        <v>2011</v>
       </c>
       <c r="H256" s="4" t="inlineStr">
         <is>
@@ -20818,14 +19884,10 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q256" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q256" s="4" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="4" t="inlineStr">
@@ -20858,8 +19920,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G257" s="7" t="n">
-        <v>2009</v>
+      <c r="G257" s="5" t="n">
+        <v>2012</v>
       </c>
       <c r="H257" s="4" t="inlineStr">
         <is>
@@ -20899,14 +19961,10 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q257" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q257" s="4" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="4" t="inlineStr">
@@ -20939,8 +19997,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G258" s="7" t="n">
-        <v>2010</v>
+      <c r="G258" s="5" t="n">
+        <v>2013</v>
       </c>
       <c r="H258" s="4" t="inlineStr">
         <is>
@@ -20980,14 +20038,10 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q258" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q258" s="4" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="4" t="inlineStr">
@@ -21020,8 +20074,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G259" s="7" t="n">
-        <v>2011</v>
+      <c r="G259" s="5" t="n">
+        <v>2014</v>
       </c>
       <c r="H259" s="4" t="inlineStr">
         <is>
@@ -21061,14 +20115,10 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q259" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q259" s="4" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="4" t="inlineStr">
@@ -21101,8 +20151,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G260" s="7" t="n">
-        <v>2012</v>
+      <c r="G260" s="5" t="n">
+        <v>2015</v>
       </c>
       <c r="H260" s="4" t="inlineStr">
         <is>
@@ -21142,14 +20192,10 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q260" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q260" s="4" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="4" t="inlineStr">
@@ -21182,8 +20228,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G261" s="7" t="n">
-        <v>2013</v>
+      <c r="G261" s="5" t="n">
+        <v>2016</v>
       </c>
       <c r="H261" s="4" t="inlineStr">
         <is>
@@ -21223,14 +20269,10 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q261" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q261" s="4" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="4" t="inlineStr">
@@ -21263,8 +20305,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G262" s="7" t="n">
-        <v>2014</v>
+      <c r="G262" s="5" t="n">
+        <v>2017</v>
       </c>
       <c r="H262" s="4" t="inlineStr">
         <is>
@@ -21304,14 +20346,10 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q262" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q262" s="4" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="4" t="inlineStr">
@@ -21344,8 +20382,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G263" s="7" t="n">
-        <v>2015</v>
+      <c r="G263" s="5" t="n">
+        <v>2018</v>
       </c>
       <c r="H263" s="4" t="inlineStr">
         <is>
@@ -21385,14 +20423,10 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q263" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q263" s="4" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="4" t="inlineStr">
@@ -21425,8 +20459,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G264" s="7" t="n">
-        <v>2016</v>
+      <c r="G264" s="5" t="n">
+        <v>2019</v>
       </c>
       <c r="H264" s="4" t="inlineStr">
         <is>
@@ -21466,14 +20500,10 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q264" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q264" s="4" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="4" t="inlineStr">
@@ -21506,8 +20536,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G265" s="7" t="n">
-        <v>2017</v>
+      <c r="G265" s="5" t="n">
+        <v>2020</v>
       </c>
       <c r="H265" s="4" t="inlineStr">
         <is>
@@ -21547,14 +20577,10 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q265" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q265" s="4" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="4" t="inlineStr">
@@ -21587,8 +20613,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G266" s="7" t="n">
-        <v>2018</v>
+      <c r="G266" s="5" t="n">
+        <v>2021</v>
       </c>
       <c r="H266" s="4" t="inlineStr">
         <is>
@@ -21628,14 +20654,10 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q266" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q266" s="4" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="4" t="inlineStr">
@@ -21668,8 +20690,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G267" s="7" t="n">
-        <v>2019</v>
+      <c r="G267" s="5" t="n">
+        <v>2022</v>
       </c>
       <c r="H267" s="4" t="inlineStr">
         <is>
@@ -21709,14 +20731,10 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q267" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q267" s="4" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="4" t="inlineStr">
@@ -21749,8 +20767,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G268" s="7" t="n">
-        <v>2020</v>
+      <c r="G268" s="5" t="n">
+        <v>2023</v>
       </c>
       <c r="H268" s="4" t="inlineStr">
         <is>
@@ -21790,14 +20808,10 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q268" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q268" s="4" t="n"/>
     </row>
     <row r="269">
       <c r="A269" s="4" t="inlineStr">
@@ -21830,8 +20844,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G269" s="7" t="n">
-        <v>2021</v>
+      <c r="G269" s="5" t="n">
+        <v>2024</v>
       </c>
       <c r="H269" s="4" t="inlineStr">
         <is>
@@ -21871,14 +20885,10 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q269" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q269" s="4" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="4" t="inlineStr">
@@ -21911,8 +20921,8 @@
           <t>Not classified</t>
         </is>
       </c>
-      <c r="G270" s="7" t="n">
-        <v>2022</v>
+      <c r="G270" s="5" t="n">
+        <v>2025</v>
       </c>
       <c r="H270" s="4" t="inlineStr">
         <is>
@@ -21952,338 +20962,10 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q270" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" s="4" t="inlineStr">
-        <is>
-          <t>Venezuela</t>
-        </is>
-      </c>
-      <c r="B271" s="4" t="inlineStr">
-        <is>
-          <t>Venezuela, RB</t>
-        </is>
-      </c>
-      <c r="C271" s="4" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D271" s="4" t="inlineStr">
-        <is>
-          <t>VEN</t>
-        </is>
-      </c>
-      <c r="E271" s="4" t="inlineStr">
-        <is>
-          <t>Latin America &amp; Caribbean</t>
-        </is>
-      </c>
-      <c r="F271" s="4" t="inlineStr">
-        <is>
-          <t>Not classified</t>
-        </is>
-      </c>
-      <c r="G271" s="7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="H271" s="4" t="inlineStr">
-        <is>
-          <t>Sector público e instituciones</t>
-        </is>
-      </c>
-      <c r="I271" s="4" t="inlineStr">
-        <is>
-          <t>sector_publico_e_instituciones</t>
-        </is>
-      </c>
-      <c r="J271" s="4" t="inlineStr">
-        <is>
-          <t>Gasto público</t>
-        </is>
-      </c>
-      <c r="K271" s="4" t="inlineStr">
-        <is>
-          <t>gasto_publico</t>
-        </is>
-      </c>
-      <c r="L271" s="4" t="inlineStr">
-        <is>
-          <t>GC.XPN.TOTL.GD.ZS</t>
-        </is>
-      </c>
-      <c r="M271" s="4" t="inlineStr">
-        <is>
-          <t>Gasto público como porcentaje del PIB</t>
-        </is>
-      </c>
-      <c r="N271" s="4" t="n"/>
-      <c r="O271" s="4" t="inlineStr">
-        <is>
-          <t>Banco Mundial - World Development Indicators</t>
-        </is>
-      </c>
-      <c r="P271" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q271" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" s="4" t="inlineStr">
-        <is>
-          <t>Venezuela</t>
-        </is>
-      </c>
-      <c r="B272" s="4" t="inlineStr">
-        <is>
-          <t>Venezuela, RB</t>
-        </is>
-      </c>
-      <c r="C272" s="4" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D272" s="4" t="inlineStr">
-        <is>
-          <t>VEN</t>
-        </is>
-      </c>
-      <c r="E272" s="4" t="inlineStr">
-        <is>
-          <t>Latin America &amp; Caribbean</t>
-        </is>
-      </c>
-      <c r="F272" s="4" t="inlineStr">
-        <is>
-          <t>Not classified</t>
-        </is>
-      </c>
-      <c r="G272" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H272" s="4" t="inlineStr">
-        <is>
-          <t>Sector público e instituciones</t>
-        </is>
-      </c>
-      <c r="I272" s="4" t="inlineStr">
-        <is>
-          <t>sector_publico_e_instituciones</t>
-        </is>
-      </c>
-      <c r="J272" s="4" t="inlineStr">
-        <is>
-          <t>Gasto público</t>
-        </is>
-      </c>
-      <c r="K272" s="4" t="inlineStr">
-        <is>
-          <t>gasto_publico</t>
-        </is>
-      </c>
-      <c r="L272" s="4" t="inlineStr">
-        <is>
-          <t>GC.XPN.TOTL.GD.ZS</t>
-        </is>
-      </c>
-      <c r="M272" s="4" t="inlineStr">
-        <is>
-          <t>Gasto público como porcentaje del PIB</t>
-        </is>
-      </c>
-      <c r="N272" s="4" t="n"/>
-      <c r="O272" s="4" t="inlineStr">
-        <is>
-          <t>Banco Mundial - World Development Indicators</t>
-        </is>
-      </c>
-      <c r="P272" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q272" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" s="4" t="inlineStr">
-        <is>
-          <t>Venezuela</t>
-        </is>
-      </c>
-      <c r="B273" s="4" t="inlineStr">
-        <is>
-          <t>Venezuela, RB</t>
-        </is>
-      </c>
-      <c r="C273" s="4" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D273" s="4" t="inlineStr">
-        <is>
-          <t>VEN</t>
-        </is>
-      </c>
-      <c r="E273" s="4" t="inlineStr">
-        <is>
-          <t>Latin America &amp; Caribbean</t>
-        </is>
-      </c>
-      <c r="F273" s="4" t="inlineStr">
-        <is>
-          <t>Not classified</t>
-        </is>
-      </c>
-      <c r="G273" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="H273" s="4" t="inlineStr">
-        <is>
-          <t>Sector público e instituciones</t>
-        </is>
-      </c>
-      <c r="I273" s="4" t="inlineStr">
-        <is>
-          <t>sector_publico_e_instituciones</t>
-        </is>
-      </c>
-      <c r="J273" s="4" t="inlineStr">
-        <is>
-          <t>Gasto público</t>
-        </is>
-      </c>
-      <c r="K273" s="4" t="inlineStr">
-        <is>
-          <t>gasto_publico</t>
-        </is>
-      </c>
-      <c r="L273" s="4" t="inlineStr">
-        <is>
-          <t>GC.XPN.TOTL.GD.ZS</t>
-        </is>
-      </c>
-      <c r="M273" s="4" t="inlineStr">
-        <is>
-          <t>Gasto público como porcentaje del PIB</t>
-        </is>
-      </c>
-      <c r="N273" s="4" t="n"/>
-      <c r="O273" s="4" t="inlineStr">
-        <is>
-          <t>Banco Mundial - World Development Indicators</t>
-        </is>
-      </c>
-      <c r="P273" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q273" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" s="4" t="inlineStr">
-        <is>
-          <t>Venezuela</t>
-        </is>
-      </c>
-      <c r="B274" s="4" t="inlineStr">
-        <is>
-          <t>Venezuela, RB</t>
-        </is>
-      </c>
-      <c r="C274" s="4" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D274" s="4" t="inlineStr">
-        <is>
-          <t>VEN</t>
-        </is>
-      </c>
-      <c r="E274" s="4" t="inlineStr">
-        <is>
-          <t>Latin America &amp; Caribbean</t>
-        </is>
-      </c>
-      <c r="F274" s="4" t="inlineStr">
-        <is>
-          <t>Not classified</t>
-        </is>
-      </c>
-      <c r="G274" s="7" t="n">
-        <v>2026</v>
-      </c>
-      <c r="H274" s="4" t="inlineStr">
-        <is>
-          <t>Sector público e instituciones</t>
-        </is>
-      </c>
-      <c r="I274" s="4" t="inlineStr">
-        <is>
-          <t>sector_publico_e_instituciones</t>
-        </is>
-      </c>
-      <c r="J274" s="4" t="inlineStr">
-        <is>
-          <t>Gasto público</t>
-        </is>
-      </c>
-      <c r="K274" s="4" t="inlineStr">
-        <is>
-          <t>gasto_publico</t>
-        </is>
-      </c>
-      <c r="L274" s="4" t="inlineStr">
-        <is>
-          <t>GC.XPN.TOTL.GD.ZS</t>
-        </is>
-      </c>
-      <c r="M274" s="4" t="inlineStr">
-        <is>
-          <t>Gasto público como porcentaje del PIB</t>
-        </is>
-      </c>
-      <c r="N274" s="4" t="n"/>
-      <c r="O274" s="4" t="inlineStr">
-        <is>
-          <t>Banco Mundial - World Development Indicators</t>
-        </is>
-      </c>
-      <c r="P274" s="4" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="Q274" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="Q270" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -22314,7 +20996,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Banco Mundial - Venezuela - Sector público e instituciones</t>
+          <t>Banco Mundial - Sector público e instituciones</t>
         </is>
       </c>
     </row>
@@ -22322,19 +21004,19 @@
     <row r="4" ht="16" customHeight="1"/>
     <row r="5" ht="8" customHeight="1"/>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Campo</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Organización</t>
         </is>
@@ -22346,7 +21028,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Dataset</t>
         </is>
@@ -22358,35 +21040,35 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Fecha generación</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Número de indicadores</t>
         </is>
       </c>
-      <c r="B10" s="7" t="n">
+      <c r="B10" s="5" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>Número de registros</t>
         </is>
       </c>
-      <c r="B11" s="7" t="n">
-        <v>268</v>
+      <c r="B11" s="5" t="n">
+        <v>264</v>
       </c>
     </row>
   </sheetData>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_sector_publico_e_instituciones.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_sector_publico_e_instituciones.xlsx
@@ -513,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q270"/>
+  <dimension ref="A1:Q272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -711,7 +711,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -865,7 +865,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -942,7 +942,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3483,7 +3483,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3868,7 +3868,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4099,7 +4099,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4253,7 +4253,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4407,7 +4407,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4484,7 +4484,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4792,7 +4792,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4869,7 +4869,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -4946,7 +4946,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5023,7 +5023,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5177,7 +5177,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5331,7 +5331,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5408,7 +5408,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5485,7 +5485,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5716,7 +5716,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5793,10 +5793,14 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q73" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q73" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
@@ -5870,10 +5874,14 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q74" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q74" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
@@ -5947,10 +5955,14 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q75" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q75" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
@@ -6024,10 +6036,14 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q76" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q76" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
@@ -6101,10 +6117,14 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q77" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q77" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
@@ -6178,10 +6198,14 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q78" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q78" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
@@ -6255,10 +6279,14 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q79" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q79" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
@@ -6332,10 +6360,14 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q80" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q80" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
@@ -6409,10 +6441,14 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q81" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q81" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
@@ -6486,10 +6522,14 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q82" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q82" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
@@ -6563,10 +6603,14 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q83" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q83" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
@@ -6640,10 +6684,14 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q84" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q84" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
@@ -6717,10 +6765,14 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q85" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q85" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
@@ -6794,10 +6846,14 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q86" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q86" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
@@ -6871,10 +6927,14 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q87" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q87" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
@@ -6948,10 +7008,14 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q88" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q88" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
@@ -7025,10 +7089,14 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q89" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q89" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
@@ -7102,10 +7170,14 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q90" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q90" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
@@ -7179,10 +7251,14 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q91" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q91" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
@@ -7256,10 +7332,14 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q92" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q92" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
@@ -7333,10 +7413,14 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q93" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q93" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
@@ -7410,10 +7494,14 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q94" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q94" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
@@ -7487,10 +7575,14 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q95" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q95" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
@@ -7564,10 +7656,14 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q96" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q96" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
@@ -7641,10 +7737,14 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q97" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q97" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
@@ -7718,10 +7818,14 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q98" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q98" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
@@ -7795,10 +7899,14 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q99" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q99" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
@@ -7872,10 +7980,14 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q100" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q100" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
@@ -7949,10 +8061,14 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q101" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q101" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
@@ -8026,10 +8142,14 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q102" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q102" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
@@ -8103,10 +8223,14 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q103" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q103" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
@@ -8180,10 +8304,14 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q104" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q104" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
@@ -8257,10 +8385,14 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q105" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q105" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
@@ -8334,10 +8466,14 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q106" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q106" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
@@ -8411,10 +8547,14 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q107" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q107" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
@@ -8488,10 +8628,14 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q108" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q108" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
@@ -8565,10 +8709,14 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q109" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q109" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
@@ -8642,10 +8790,14 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q110" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q110" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
@@ -8719,10 +8871,14 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q111" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q111" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
@@ -8796,10 +8952,14 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q112" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q112" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
@@ -8873,10 +9033,14 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q113" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q113" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
@@ -8950,10 +9114,14 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q114" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q114" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
@@ -9027,10 +9195,14 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q115" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q115" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
@@ -9104,10 +9276,14 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q116" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q116" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
@@ -9181,10 +9357,14 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q117" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q117" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
@@ -9258,10 +9438,14 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q118" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q118" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
@@ -9335,10 +9519,14 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q119" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q119" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
@@ -9412,10 +9600,14 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q120" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q120" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
@@ -9489,10 +9681,14 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q121" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q121" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
@@ -9566,10 +9762,14 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q122" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q122" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
@@ -9643,10 +9843,14 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q123" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q123" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
@@ -9720,10 +9924,14 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q124" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q124" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
@@ -9797,10 +10005,14 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q125" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q125" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
@@ -9874,10 +10086,14 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q126" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q126" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
@@ -9951,10 +10167,14 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q127" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q127" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
@@ -10028,10 +10248,14 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q128" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q128" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
@@ -10105,10 +10329,14 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q129" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q129" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
@@ -10182,10 +10410,14 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q130" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q130" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
@@ -10259,10 +10491,14 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q131" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q131" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
@@ -10336,10 +10572,14 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q132" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q132" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
@@ -10413,10 +10653,14 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q133" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q133" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
@@ -10490,10 +10734,14 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q134" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q134" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
@@ -10567,10 +10815,14 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q135" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q135" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
@@ -10644,10 +10896,14 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q136" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q136" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
@@ -10721,10 +10977,14 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q137" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q137" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
@@ -10798,10 +11058,14 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q138" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q138" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
@@ -10835,7 +11099,7 @@
         </is>
       </c>
       <c r="G139" s="5" t="n">
-        <v>1960</v>
+        <v>2026</v>
       </c>
       <c r="H139" s="4" t="inlineStr">
         <is>
@@ -10849,22 +11113,22 @@
       </c>
       <c r="J139" s="4" t="inlineStr">
         <is>
-          <t>Fiscalidad</t>
+          <t>Ingresos públicos</t>
         </is>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>fiscalidad</t>
+          <t>ingresos_publicos</t>
         </is>
       </c>
       <c r="L139" s="4" t="inlineStr">
         <is>
-          <t>GC.TAX.TOTL.GD.ZS</t>
+          <t>GC.REV.XGRT.GD.ZS</t>
         </is>
       </c>
       <c r="M139" s="4" t="inlineStr">
         <is>
-          <t>Ingresos tributarios como porcentaje del PIB</t>
+          <t>Ingresos públicos excluidas donaciones como porcentaje del PIB</t>
         </is>
       </c>
       <c r="N139" s="4" t="n"/>
@@ -10875,10 +11139,14 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q139" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q139" s="4" t="inlineStr">
+        <is>
+          <t>HTTP Error 400: Bad Request</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
@@ -10912,7 +11180,7 @@
         </is>
       </c>
       <c r="G140" s="5" t="n">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="H140" s="4" t="inlineStr">
         <is>
@@ -10952,10 +11220,14 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q140" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q140" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
@@ -10989,7 +11261,7 @@
         </is>
       </c>
       <c r="G141" s="5" t="n">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="H141" s="4" t="inlineStr">
         <is>
@@ -11029,10 +11301,14 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q141" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q141" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
@@ -11066,7 +11342,7 @@
         </is>
       </c>
       <c r="G142" s="5" t="n">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="H142" s="4" t="inlineStr">
         <is>
@@ -11106,10 +11382,14 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q142" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q142" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
@@ -11143,7 +11423,7 @@
         </is>
       </c>
       <c r="G143" s="5" t="n">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="H143" s="4" t="inlineStr">
         <is>
@@ -11183,10 +11463,14 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q143" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q143" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
@@ -11220,7 +11504,7 @@
         </is>
       </c>
       <c r="G144" s="5" t="n">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="H144" s="4" t="inlineStr">
         <is>
@@ -11260,10 +11544,14 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q144" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q144" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
@@ -11297,7 +11585,7 @@
         </is>
       </c>
       <c r="G145" s="5" t="n">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="H145" s="4" t="inlineStr">
         <is>
@@ -11337,10 +11625,14 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q145" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q145" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
@@ -11374,7 +11666,7 @@
         </is>
       </c>
       <c r="G146" s="5" t="n">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="H146" s="4" t="inlineStr">
         <is>
@@ -11414,10 +11706,14 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q146" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q146" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
@@ -11451,7 +11747,7 @@
         </is>
       </c>
       <c r="G147" s="5" t="n">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="H147" s="4" t="inlineStr">
         <is>
@@ -11491,10 +11787,14 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q147" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q147" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
@@ -11528,7 +11828,7 @@
         </is>
       </c>
       <c r="G148" s="5" t="n">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="H148" s="4" t="inlineStr">
         <is>
@@ -11568,10 +11868,14 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q148" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q148" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
@@ -11605,7 +11909,7 @@
         </is>
       </c>
       <c r="G149" s="5" t="n">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="H149" s="4" t="inlineStr">
         <is>
@@ -11645,10 +11949,14 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q149" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q149" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
@@ -11682,7 +11990,7 @@
         </is>
       </c>
       <c r="G150" s="5" t="n">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="H150" s="4" t="inlineStr">
         <is>
@@ -11722,10 +12030,14 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q150" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q150" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
@@ -11759,7 +12071,7 @@
         </is>
       </c>
       <c r="G151" s="5" t="n">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="H151" s="4" t="inlineStr">
         <is>
@@ -11799,10 +12111,14 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q151" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q151" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
@@ -11836,7 +12152,7 @@
         </is>
       </c>
       <c r="G152" s="5" t="n">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="H152" s="4" t="inlineStr">
         <is>
@@ -11876,10 +12192,14 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q152" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q152" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
@@ -11913,7 +12233,7 @@
         </is>
       </c>
       <c r="G153" s="5" t="n">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="H153" s="4" t="inlineStr">
         <is>
@@ -11953,10 +12273,14 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q153" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q153" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
@@ -11990,7 +12314,7 @@
         </is>
       </c>
       <c r="G154" s="5" t="n">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="H154" s="4" t="inlineStr">
         <is>
@@ -12030,10 +12354,14 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q154" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q154" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
@@ -12067,7 +12395,7 @@
         </is>
       </c>
       <c r="G155" s="5" t="n">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="H155" s="4" t="inlineStr">
         <is>
@@ -12107,10 +12435,14 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q155" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q155" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
@@ -12144,7 +12476,7 @@
         </is>
       </c>
       <c r="G156" s="5" t="n">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="H156" s="4" t="inlineStr">
         <is>
@@ -12184,10 +12516,14 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q156" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q156" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
@@ -12221,7 +12557,7 @@
         </is>
       </c>
       <c r="G157" s="5" t="n">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="H157" s="4" t="inlineStr">
         <is>
@@ -12261,10 +12597,14 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q157" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q157" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
@@ -12298,7 +12638,7 @@
         </is>
       </c>
       <c r="G158" s="5" t="n">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="H158" s="4" t="inlineStr">
         <is>
@@ -12338,10 +12678,14 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q158" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q158" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
@@ -12375,7 +12719,7 @@
         </is>
       </c>
       <c r="G159" s="5" t="n">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="H159" s="4" t="inlineStr">
         <is>
@@ -12415,10 +12759,14 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q159" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q159" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
@@ -12452,7 +12800,7 @@
         </is>
       </c>
       <c r="G160" s="5" t="n">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="H160" s="4" t="inlineStr">
         <is>
@@ -12492,10 +12840,14 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q160" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q160" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
@@ -12529,7 +12881,7 @@
         </is>
       </c>
       <c r="G161" s="5" t="n">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="H161" s="4" t="inlineStr">
         <is>
@@ -12569,10 +12921,14 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q161" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q161" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
@@ -12606,7 +12962,7 @@
         </is>
       </c>
       <c r="G162" s="5" t="n">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="H162" s="4" t="inlineStr">
         <is>
@@ -12646,10 +13002,14 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q162" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q162" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
@@ -12683,7 +13043,7 @@
         </is>
       </c>
       <c r="G163" s="5" t="n">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="H163" s="4" t="inlineStr">
         <is>
@@ -12723,10 +13083,14 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q163" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q163" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
@@ -12760,7 +13124,7 @@
         </is>
       </c>
       <c r="G164" s="5" t="n">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="H164" s="4" t="inlineStr">
         <is>
@@ -12800,10 +13164,14 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q164" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q164" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
@@ -12837,7 +13205,7 @@
         </is>
       </c>
       <c r="G165" s="5" t="n">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="H165" s="4" t="inlineStr">
         <is>
@@ -12877,10 +13245,14 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q165" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q165" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
@@ -12914,7 +13286,7 @@
         </is>
       </c>
       <c r="G166" s="5" t="n">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="H166" s="4" t="inlineStr">
         <is>
@@ -12954,10 +13326,14 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q166" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q166" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
@@ -12991,7 +13367,7 @@
         </is>
       </c>
       <c r="G167" s="5" t="n">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="H167" s="4" t="inlineStr">
         <is>
@@ -13031,10 +13407,14 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q167" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q167" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
@@ -13068,7 +13448,7 @@
         </is>
       </c>
       <c r="G168" s="5" t="n">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="H168" s="4" t="inlineStr">
         <is>
@@ -13108,10 +13488,14 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q168" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q168" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
@@ -13145,7 +13529,7 @@
         </is>
       </c>
       <c r="G169" s="5" t="n">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="H169" s="4" t="inlineStr">
         <is>
@@ -13185,10 +13569,14 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q169" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q169" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
@@ -13222,7 +13610,7 @@
         </is>
       </c>
       <c r="G170" s="5" t="n">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="H170" s="4" t="inlineStr">
         <is>
@@ -13262,10 +13650,14 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q170" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q170" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
@@ -13299,7 +13691,7 @@
         </is>
       </c>
       <c r="G171" s="5" t="n">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="H171" s="4" t="inlineStr">
         <is>
@@ -13339,10 +13731,14 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q171" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q171" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
@@ -13376,7 +13772,7 @@
         </is>
       </c>
       <c r="G172" s="5" t="n">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="H172" s="4" t="inlineStr">
         <is>
@@ -13416,10 +13812,14 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q172" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q172" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
@@ -13453,7 +13853,7 @@
         </is>
       </c>
       <c r="G173" s="5" t="n">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="H173" s="4" t="inlineStr">
         <is>
@@ -13493,10 +13893,14 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q173" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q173" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
@@ -13530,7 +13934,7 @@
         </is>
       </c>
       <c r="G174" s="5" t="n">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="H174" s="4" t="inlineStr">
         <is>
@@ -13570,10 +13974,14 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q174" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q174" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
@@ -13607,7 +14015,7 @@
         </is>
       </c>
       <c r="G175" s="5" t="n">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="H175" s="4" t="inlineStr">
         <is>
@@ -13647,10 +14055,14 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q175" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q175" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="4" t="inlineStr">
@@ -13684,7 +14096,7 @@
         </is>
       </c>
       <c r="G176" s="5" t="n">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="H176" s="4" t="inlineStr">
         <is>
@@ -13724,10 +14136,14 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q176" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q176" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
@@ -13761,7 +14177,7 @@
         </is>
       </c>
       <c r="G177" s="5" t="n">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="H177" s="4" t="inlineStr">
         <is>
@@ -13801,10 +14217,14 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q177" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q177" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
@@ -13838,7 +14258,7 @@
         </is>
       </c>
       <c r="G178" s="5" t="n">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="H178" s="4" t="inlineStr">
         <is>
@@ -13878,10 +14298,14 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q178" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q178" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
@@ -13915,7 +14339,7 @@
         </is>
       </c>
       <c r="G179" s="5" t="n">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="H179" s="4" t="inlineStr">
         <is>
@@ -13955,10 +14379,14 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q179" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q179" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="4" t="inlineStr">
@@ -13992,7 +14420,7 @@
         </is>
       </c>
       <c r="G180" s="5" t="n">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="H180" s="4" t="inlineStr">
         <is>
@@ -14032,10 +14460,14 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q180" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q180" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
@@ -14069,7 +14501,7 @@
         </is>
       </c>
       <c r="G181" s="5" t="n">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="H181" s="4" t="inlineStr">
         <is>
@@ -14109,10 +14541,14 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q181" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q181" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
@@ -14146,7 +14582,7 @@
         </is>
       </c>
       <c r="G182" s="5" t="n">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="H182" s="4" t="inlineStr">
         <is>
@@ -14186,10 +14622,14 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q182" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q182" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
@@ -14223,7 +14663,7 @@
         </is>
       </c>
       <c r="G183" s="5" t="n">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="H183" s="4" t="inlineStr">
         <is>
@@ -14263,10 +14703,14 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q183" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q183" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
@@ -14300,7 +14744,7 @@
         </is>
       </c>
       <c r="G184" s="5" t="n">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="H184" s="4" t="inlineStr">
         <is>
@@ -14340,10 +14784,14 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q184" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q184" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
@@ -14377,7 +14825,7 @@
         </is>
       </c>
       <c r="G185" s="5" t="n">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="H185" s="4" t="inlineStr">
         <is>
@@ -14417,10 +14865,14 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q185" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q185" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
@@ -14454,7 +14906,7 @@
         </is>
       </c>
       <c r="G186" s="5" t="n">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="H186" s="4" t="inlineStr">
         <is>
@@ -14494,10 +14946,14 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q186" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q186" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
@@ -14531,7 +14987,7 @@
         </is>
       </c>
       <c r="G187" s="5" t="n">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="H187" s="4" t="inlineStr">
         <is>
@@ -14571,10 +15027,14 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q187" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q187" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="4" t="inlineStr">
@@ -14608,7 +15068,7 @@
         </is>
       </c>
       <c r="G188" s="5" t="n">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="H188" s="4" t="inlineStr">
         <is>
@@ -14648,10 +15108,14 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q188" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q188" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
@@ -14685,7 +15149,7 @@
         </is>
       </c>
       <c r="G189" s="5" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="H189" s="4" t="inlineStr">
         <is>
@@ -14725,10 +15189,14 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q189" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q189" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="4" t="inlineStr">
@@ -14762,7 +15230,7 @@
         </is>
       </c>
       <c r="G190" s="5" t="n">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="H190" s="4" t="inlineStr">
         <is>
@@ -14802,10 +15270,14 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q190" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q190" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
@@ -14839,7 +15311,7 @@
         </is>
       </c>
       <c r="G191" s="5" t="n">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="H191" s="4" t="inlineStr">
         <is>
@@ -14879,10 +15351,14 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q191" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q191" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
@@ -14916,7 +15392,7 @@
         </is>
       </c>
       <c r="G192" s="5" t="n">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="H192" s="4" t="inlineStr">
         <is>
@@ -14956,10 +15432,14 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q192" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q192" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
@@ -14993,7 +15473,7 @@
         </is>
       </c>
       <c r="G193" s="5" t="n">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="H193" s="4" t="inlineStr">
         <is>
@@ -15033,10 +15513,14 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q193" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q193" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="4" t="inlineStr">
@@ -15070,7 +15554,7 @@
         </is>
       </c>
       <c r="G194" s="5" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="H194" s="4" t="inlineStr">
         <is>
@@ -15110,10 +15594,14 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q194" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q194" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
@@ -15147,7 +15635,7 @@
         </is>
       </c>
       <c r="G195" s="5" t="n">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="H195" s="4" t="inlineStr">
         <is>
@@ -15187,10 +15675,14 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q195" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q195" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="4" t="inlineStr">
@@ -15224,7 +15716,7 @@
         </is>
       </c>
       <c r="G196" s="5" t="n">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="H196" s="4" t="inlineStr">
         <is>
@@ -15264,10 +15756,14 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q196" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q196" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="4" t="inlineStr">
@@ -15301,7 +15797,7 @@
         </is>
       </c>
       <c r="G197" s="5" t="n">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="H197" s="4" t="inlineStr">
         <is>
@@ -15341,10 +15837,14 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q197" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q197" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="4" t="inlineStr">
@@ -15378,7 +15878,7 @@
         </is>
       </c>
       <c r="G198" s="5" t="n">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="H198" s="4" t="inlineStr">
         <is>
@@ -15418,10 +15918,14 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q198" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q198" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="4" t="inlineStr">
@@ -15455,7 +15959,7 @@
         </is>
       </c>
       <c r="G199" s="5" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="H199" s="4" t="inlineStr">
         <is>
@@ -15495,10 +15999,14 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q199" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q199" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="4" t="inlineStr">
@@ -15532,7 +16040,7 @@
         </is>
       </c>
       <c r="G200" s="5" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="H200" s="4" t="inlineStr">
         <is>
@@ -15572,10 +16080,14 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q200" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q200" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="4" t="inlineStr">
@@ -15609,7 +16121,7 @@
         </is>
       </c>
       <c r="G201" s="5" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="H201" s="4" t="inlineStr">
         <is>
@@ -15649,10 +16161,14 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q201" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q201" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="4" t="inlineStr">
@@ -15686,7 +16202,7 @@
         </is>
       </c>
       <c r="G202" s="5" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="H202" s="4" t="inlineStr">
         <is>
@@ -15726,10 +16242,14 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q202" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q202" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
@@ -15763,7 +16283,7 @@
         </is>
       </c>
       <c r="G203" s="5" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="H203" s="4" t="inlineStr">
         <is>
@@ -15803,10 +16323,14 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q203" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q203" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="4" t="inlineStr">
@@ -15840,7 +16364,7 @@
         </is>
       </c>
       <c r="G204" s="5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="H204" s="4" t="inlineStr">
         <is>
@@ -15880,10 +16404,14 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q204" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q204" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
@@ -15917,7 +16445,7 @@
         </is>
       </c>
       <c r="G205" s="5" t="n">
-        <v>1960</v>
+        <v>2025</v>
       </c>
       <c r="H205" s="4" t="inlineStr">
         <is>
@@ -15931,22 +16459,22 @@
       </c>
       <c r="J205" s="4" t="inlineStr">
         <is>
-          <t>Gasto público</t>
+          <t>Fiscalidad</t>
         </is>
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>gasto_publico</t>
+          <t>fiscalidad</t>
         </is>
       </c>
       <c r="L205" s="4" t="inlineStr">
         <is>
-          <t>GC.XPN.TOTL.GD.ZS</t>
+          <t>GC.TAX.TOTL.GD.ZS</t>
         </is>
       </c>
       <c r="M205" s="4" t="inlineStr">
         <is>
-          <t>Gasto público como porcentaje del PIB</t>
+          <t>Ingresos tributarios como porcentaje del PIB</t>
         </is>
       </c>
       <c r="N205" s="4" t="n"/>
@@ -15957,10 +16485,14 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q205" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q205" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="4" t="inlineStr">
@@ -15994,7 +16526,7 @@
         </is>
       </c>
       <c r="G206" s="5" t="n">
-        <v>1961</v>
+        <v>2026</v>
       </c>
       <c r="H206" s="4" t="inlineStr">
         <is>
@@ -16008,22 +16540,22 @@
       </c>
       <c r="J206" s="4" t="inlineStr">
         <is>
-          <t>Gasto público</t>
+          <t>Fiscalidad</t>
         </is>
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>gasto_publico</t>
+          <t>fiscalidad</t>
         </is>
       </c>
       <c r="L206" s="4" t="inlineStr">
         <is>
-          <t>GC.XPN.TOTL.GD.ZS</t>
+          <t>GC.TAX.TOTL.GD.ZS</t>
         </is>
       </c>
       <c r="M206" s="4" t="inlineStr">
         <is>
-          <t>Gasto público como porcentaje del PIB</t>
+          <t>Ingresos tributarios como porcentaje del PIB</t>
         </is>
       </c>
       <c r="N206" s="4" t="n"/>
@@ -16034,10 +16566,14 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="Q206" s="4" t="n"/>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q206" s="4" t="inlineStr">
+        <is>
+          <t>The read operation timed out</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
@@ -16071,7 +16607,7 @@
         </is>
       </c>
       <c r="G207" s="5" t="n">
-        <v>1962</v>
+        <v>1960</v>
       </c>
       <c r="H207" s="4" t="inlineStr">
         <is>
@@ -16111,7 +16647,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16148,7 +16684,7 @@
         </is>
       </c>
       <c r="G208" s="5" t="n">
-        <v>1963</v>
+        <v>1961</v>
       </c>
       <c r="H208" s="4" t="inlineStr">
         <is>
@@ -16188,7 +16724,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16225,7 +16761,7 @@
         </is>
       </c>
       <c r="G209" s="5" t="n">
-        <v>1964</v>
+        <v>1962</v>
       </c>
       <c r="H209" s="4" t="inlineStr">
         <is>
@@ -16265,7 +16801,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16302,7 +16838,7 @@
         </is>
       </c>
       <c r="G210" s="5" t="n">
-        <v>1965</v>
+        <v>1963</v>
       </c>
       <c r="H210" s="4" t="inlineStr">
         <is>
@@ -16342,7 +16878,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16379,7 +16915,7 @@
         </is>
       </c>
       <c r="G211" s="5" t="n">
-        <v>1966</v>
+        <v>1964</v>
       </c>
       <c r="H211" s="4" t="inlineStr">
         <is>
@@ -16419,7 +16955,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16456,7 +16992,7 @@
         </is>
       </c>
       <c r="G212" s="5" t="n">
-        <v>1967</v>
+        <v>1965</v>
       </c>
       <c r="H212" s="4" t="inlineStr">
         <is>
@@ -16496,7 +17032,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16533,7 +17069,7 @@
         </is>
       </c>
       <c r="G213" s="5" t="n">
-        <v>1968</v>
+        <v>1966</v>
       </c>
       <c r="H213" s="4" t="inlineStr">
         <is>
@@ -16573,7 +17109,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16610,7 +17146,7 @@
         </is>
       </c>
       <c r="G214" s="5" t="n">
-        <v>1969</v>
+        <v>1967</v>
       </c>
       <c r="H214" s="4" t="inlineStr">
         <is>
@@ -16650,7 +17186,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16687,7 +17223,7 @@
         </is>
       </c>
       <c r="G215" s="5" t="n">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="H215" s="4" t="inlineStr">
         <is>
@@ -16727,7 +17263,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -16764,7 +17300,7 @@
         </is>
       </c>
       <c r="G216" s="5" t="n">
-        <v>1971</v>
+        <v>1969</v>
       </c>
       <c r="H216" s="4" t="inlineStr">
         <is>
@@ -16804,7 +17340,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -16841,7 +17377,7 @@
         </is>
       </c>
       <c r="G217" s="5" t="n">
-        <v>1972</v>
+        <v>1970</v>
       </c>
       <c r="H217" s="4" t="inlineStr">
         <is>
@@ -16881,7 +17417,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -16918,7 +17454,7 @@
         </is>
       </c>
       <c r="G218" s="5" t="n">
-        <v>1973</v>
+        <v>1971</v>
       </c>
       <c r="H218" s="4" t="inlineStr">
         <is>
@@ -16958,7 +17494,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -16995,7 +17531,7 @@
         </is>
       </c>
       <c r="G219" s="5" t="n">
-        <v>1974</v>
+        <v>1972</v>
       </c>
       <c r="H219" s="4" t="inlineStr">
         <is>
@@ -17035,7 +17571,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17072,7 +17608,7 @@
         </is>
       </c>
       <c r="G220" s="5" t="n">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="H220" s="4" t="inlineStr">
         <is>
@@ -17112,7 +17648,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17149,7 +17685,7 @@
         </is>
       </c>
       <c r="G221" s="5" t="n">
-        <v>1976</v>
+        <v>1974</v>
       </c>
       <c r="H221" s="4" t="inlineStr">
         <is>
@@ -17189,7 +17725,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17226,7 +17762,7 @@
         </is>
       </c>
       <c r="G222" s="5" t="n">
-        <v>1977</v>
+        <v>1975</v>
       </c>
       <c r="H222" s="4" t="inlineStr">
         <is>
@@ -17266,7 +17802,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17303,7 +17839,7 @@
         </is>
       </c>
       <c r="G223" s="5" t="n">
-        <v>1978</v>
+        <v>1976</v>
       </c>
       <c r="H223" s="4" t="inlineStr">
         <is>
@@ -17343,7 +17879,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17380,7 +17916,7 @@
         </is>
       </c>
       <c r="G224" s="5" t="n">
-        <v>1979</v>
+        <v>1977</v>
       </c>
       <c r="H224" s="4" t="inlineStr">
         <is>
@@ -17420,7 +17956,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17457,7 +17993,7 @@
         </is>
       </c>
       <c r="G225" s="5" t="n">
-        <v>1980</v>
+        <v>1978</v>
       </c>
       <c r="H225" s="4" t="inlineStr">
         <is>
@@ -17497,7 +18033,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17534,7 +18070,7 @@
         </is>
       </c>
       <c r="G226" s="5" t="n">
-        <v>1981</v>
+        <v>1979</v>
       </c>
       <c r="H226" s="4" t="inlineStr">
         <is>
@@ -17574,7 +18110,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17611,7 +18147,7 @@
         </is>
       </c>
       <c r="G227" s="5" t="n">
-        <v>1982</v>
+        <v>1980</v>
       </c>
       <c r="H227" s="4" t="inlineStr">
         <is>
@@ -17651,7 +18187,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17688,7 +18224,7 @@
         </is>
       </c>
       <c r="G228" s="5" t="n">
-        <v>1983</v>
+        <v>1981</v>
       </c>
       <c r="H228" s="4" t="inlineStr">
         <is>
@@ -17728,7 +18264,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -17765,7 +18301,7 @@
         </is>
       </c>
       <c r="G229" s="5" t="n">
-        <v>1984</v>
+        <v>1982</v>
       </c>
       <c r="H229" s="4" t="inlineStr">
         <is>
@@ -17805,7 +18341,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -17842,7 +18378,7 @@
         </is>
       </c>
       <c r="G230" s="5" t="n">
-        <v>1985</v>
+        <v>1983</v>
       </c>
       <c r="H230" s="4" t="inlineStr">
         <is>
@@ -17882,7 +18418,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -17919,7 +18455,7 @@
         </is>
       </c>
       <c r="G231" s="5" t="n">
-        <v>1986</v>
+        <v>1984</v>
       </c>
       <c r="H231" s="4" t="inlineStr">
         <is>
@@ -17959,7 +18495,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -17996,7 +18532,7 @@
         </is>
       </c>
       <c r="G232" s="5" t="n">
-        <v>1987</v>
+        <v>1985</v>
       </c>
       <c r="H232" s="4" t="inlineStr">
         <is>
@@ -18036,7 +18572,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18073,7 +18609,7 @@
         </is>
       </c>
       <c r="G233" s="5" t="n">
-        <v>1988</v>
+        <v>1986</v>
       </c>
       <c r="H233" s="4" t="inlineStr">
         <is>
@@ -18113,7 +18649,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18150,7 +18686,7 @@
         </is>
       </c>
       <c r="G234" s="5" t="n">
-        <v>1989</v>
+        <v>1987</v>
       </c>
       <c r="H234" s="4" t="inlineStr">
         <is>
@@ -18190,7 +18726,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18227,7 +18763,7 @@
         </is>
       </c>
       <c r="G235" s="5" t="n">
-        <v>1990</v>
+        <v>1988</v>
       </c>
       <c r="H235" s="4" t="inlineStr">
         <is>
@@ -18267,7 +18803,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18304,7 +18840,7 @@
         </is>
       </c>
       <c r="G236" s="5" t="n">
-        <v>1991</v>
+        <v>1989</v>
       </c>
       <c r="H236" s="4" t="inlineStr">
         <is>
@@ -18344,7 +18880,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18381,7 +18917,7 @@
         </is>
       </c>
       <c r="G237" s="5" t="n">
-        <v>1992</v>
+        <v>1990</v>
       </c>
       <c r="H237" s="4" t="inlineStr">
         <is>
@@ -18421,7 +18957,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18458,7 +18994,7 @@
         </is>
       </c>
       <c r="G238" s="5" t="n">
-        <v>1993</v>
+        <v>1991</v>
       </c>
       <c r="H238" s="4" t="inlineStr">
         <is>
@@ -18498,7 +19034,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18535,7 +19071,7 @@
         </is>
       </c>
       <c r="G239" s="5" t="n">
-        <v>1994</v>
+        <v>1992</v>
       </c>
       <c r="H239" s="4" t="inlineStr">
         <is>
@@ -18575,7 +19111,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18612,7 +19148,7 @@
         </is>
       </c>
       <c r="G240" s="5" t="n">
-        <v>1995</v>
+        <v>1993</v>
       </c>
       <c r="H240" s="4" t="inlineStr">
         <is>
@@ -18652,7 +19188,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18689,7 +19225,7 @@
         </is>
       </c>
       <c r="G241" s="5" t="n">
-        <v>1996</v>
+        <v>1994</v>
       </c>
       <c r="H241" s="4" t="inlineStr">
         <is>
@@ -18729,7 +19265,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -18766,7 +19302,7 @@
         </is>
       </c>
       <c r="G242" s="5" t="n">
-        <v>1997</v>
+        <v>1995</v>
       </c>
       <c r="H242" s="4" t="inlineStr">
         <is>
@@ -18806,7 +19342,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -18843,7 +19379,7 @@
         </is>
       </c>
       <c r="G243" s="5" t="n">
-        <v>1998</v>
+        <v>1996</v>
       </c>
       <c r="H243" s="4" t="inlineStr">
         <is>
@@ -18883,7 +19419,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -18920,7 +19456,7 @@
         </is>
       </c>
       <c r="G244" s="5" t="n">
-        <v>1999</v>
+        <v>1997</v>
       </c>
       <c r="H244" s="4" t="inlineStr">
         <is>
@@ -18960,7 +19496,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -18997,7 +19533,7 @@
         </is>
       </c>
       <c r="G245" s="5" t="n">
-        <v>2000</v>
+        <v>1998</v>
       </c>
       <c r="H245" s="4" t="inlineStr">
         <is>
@@ -19037,7 +19573,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19074,7 +19610,7 @@
         </is>
       </c>
       <c r="G246" s="5" t="n">
-        <v>2001</v>
+        <v>1999</v>
       </c>
       <c r="H246" s="4" t="inlineStr">
         <is>
@@ -19114,7 +19650,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19151,7 +19687,7 @@
         </is>
       </c>
       <c r="G247" s="5" t="n">
-        <v>2002</v>
+        <v>2000</v>
       </c>
       <c r="H247" s="4" t="inlineStr">
         <is>
@@ -19191,7 +19727,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19228,7 +19764,7 @@
         </is>
       </c>
       <c r="G248" s="5" t="n">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="H248" s="4" t="inlineStr">
         <is>
@@ -19268,7 +19804,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19305,7 +19841,7 @@
         </is>
       </c>
       <c r="G249" s="5" t="n">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="H249" s="4" t="inlineStr">
         <is>
@@ -19345,7 +19881,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19382,7 +19918,7 @@
         </is>
       </c>
       <c r="G250" s="5" t="n">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="H250" s="4" t="inlineStr">
         <is>
@@ -19422,7 +19958,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19459,7 +19995,7 @@
         </is>
       </c>
       <c r="G251" s="5" t="n">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="H251" s="4" t="inlineStr">
         <is>
@@ -19499,7 +20035,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19536,7 +20072,7 @@
         </is>
       </c>
       <c r="G252" s="5" t="n">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="H252" s="4" t="inlineStr">
         <is>
@@ -19576,7 +20112,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19613,7 +20149,7 @@
         </is>
       </c>
       <c r="G253" s="5" t="n">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="H253" s="4" t="inlineStr">
         <is>
@@ -19653,7 +20189,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -19690,7 +20226,7 @@
         </is>
       </c>
       <c r="G254" s="5" t="n">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="H254" s="4" t="inlineStr">
         <is>
@@ -19730,7 +20266,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -19767,7 +20303,7 @@
         </is>
       </c>
       <c r="G255" s="5" t="n">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="H255" s="4" t="inlineStr">
         <is>
@@ -19807,7 +20343,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -19844,7 +20380,7 @@
         </is>
       </c>
       <c r="G256" s="5" t="n">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="H256" s="4" t="inlineStr">
         <is>
@@ -19884,7 +20420,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -19921,7 +20457,7 @@
         </is>
       </c>
       <c r="G257" s="5" t="n">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="H257" s="4" t="inlineStr">
         <is>
@@ -19961,7 +20497,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -19998,7 +20534,7 @@
         </is>
       </c>
       <c r="G258" s="5" t="n">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="H258" s="4" t="inlineStr">
         <is>
@@ -20038,7 +20574,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20075,7 +20611,7 @@
         </is>
       </c>
       <c r="G259" s="5" t="n">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="H259" s="4" t="inlineStr">
         <is>
@@ -20115,7 +20651,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20152,7 +20688,7 @@
         </is>
       </c>
       <c r="G260" s="5" t="n">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="H260" s="4" t="inlineStr">
         <is>
@@ -20192,7 +20728,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20229,7 +20765,7 @@
         </is>
       </c>
       <c r="G261" s="5" t="n">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="H261" s="4" t="inlineStr">
         <is>
@@ -20269,7 +20805,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20306,7 +20842,7 @@
         </is>
       </c>
       <c r="G262" s="5" t="n">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="H262" s="4" t="inlineStr">
         <is>
@@ -20346,7 +20882,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20383,7 +20919,7 @@
         </is>
       </c>
       <c r="G263" s="5" t="n">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="H263" s="4" t="inlineStr">
         <is>
@@ -20423,7 +20959,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20460,7 +20996,7 @@
         </is>
       </c>
       <c r="G264" s="5" t="n">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="H264" s="4" t="inlineStr">
         <is>
@@ -20500,7 +21036,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20537,7 +21073,7 @@
         </is>
       </c>
       <c r="G265" s="5" t="n">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="H265" s="4" t="inlineStr">
         <is>
@@ -20577,7 +21113,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20614,7 +21150,7 @@
         </is>
       </c>
       <c r="G266" s="5" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="H266" s="4" t="inlineStr">
         <is>
@@ -20654,7 +21190,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -20691,7 +21227,7 @@
         </is>
       </c>
       <c r="G267" s="5" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="H267" s="4" t="inlineStr">
         <is>
@@ -20731,7 +21267,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -20768,7 +21304,7 @@
         </is>
       </c>
       <c r="G268" s="5" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="H268" s="4" t="inlineStr">
         <is>
@@ -20808,7 +21344,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -20845,7 +21381,7 @@
         </is>
       </c>
       <c r="G269" s="5" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="H269" s="4" t="inlineStr">
         <is>
@@ -20885,7 +21421,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -20922,7 +21458,7 @@
         </is>
       </c>
       <c r="G270" s="5" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="H270" s="4" t="inlineStr">
         <is>
@@ -20962,10 +21498,164 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="4" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="B271" s="4" t="inlineStr">
+        <is>
+          <t>Venezuela, RB</t>
+        </is>
+      </c>
+      <c r="C271" s="4" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="D271" s="4" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="E271" s="4" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="F271" s="4" t="inlineStr">
+        <is>
+          <t>Not classified</t>
+        </is>
+      </c>
+      <c r="G271" s="5" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H271" s="4" t="inlineStr">
+        <is>
+          <t>Sector público e instituciones</t>
+        </is>
+      </c>
+      <c r="I271" s="4" t="inlineStr">
+        <is>
+          <t>sector_publico_e_instituciones</t>
+        </is>
+      </c>
+      <c r="J271" s="4" t="inlineStr">
+        <is>
+          <t>Gasto público</t>
+        </is>
+      </c>
+      <c r="K271" s="4" t="inlineStr">
+        <is>
+          <t>gasto_publico</t>
+        </is>
+      </c>
+      <c r="L271" s="4" t="inlineStr">
+        <is>
+          <t>GC.XPN.TOTL.GD.ZS</t>
+        </is>
+      </c>
+      <c r="M271" s="4" t="inlineStr">
+        <is>
+          <t>Gasto público como porcentaje del PIB</t>
+        </is>
+      </c>
+      <c r="N271" s="4" t="n"/>
+      <c r="O271" s="4" t="inlineStr">
+        <is>
+          <t>Banco Mundial - World Development Indicators</t>
+        </is>
+      </c>
+      <c r="P271" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q271" s="4" t="n"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="4" t="inlineStr">
+        <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="B272" s="4" t="inlineStr">
+        <is>
+          <t>Venezuela, RB</t>
+        </is>
+      </c>
+      <c r="C272" s="4" t="inlineStr">
+        <is>
+          <t>VE</t>
+        </is>
+      </c>
+      <c r="D272" s="4" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="E272" s="4" t="inlineStr">
+        <is>
+          <t>Latin America &amp; Caribbean</t>
+        </is>
+      </c>
+      <c r="F272" s="4" t="inlineStr">
+        <is>
+          <t>Not classified</t>
+        </is>
+      </c>
+      <c r="G272" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H272" s="4" t="inlineStr">
+        <is>
+          <t>Sector público e instituciones</t>
+        </is>
+      </c>
+      <c r="I272" s="4" t="inlineStr">
+        <is>
+          <t>sector_publico_e_instituciones</t>
+        </is>
+      </c>
+      <c r="J272" s="4" t="inlineStr">
+        <is>
+          <t>Gasto público</t>
+        </is>
+      </c>
+      <c r="K272" s="4" t="inlineStr">
+        <is>
+          <t>gasto_publico</t>
+        </is>
+      </c>
+      <c r="L272" s="4" t="inlineStr">
+        <is>
+          <t>GC.XPN.TOTL.GD.ZS</t>
+        </is>
+      </c>
+      <c r="M272" s="4" t="inlineStr">
+        <is>
+          <t>Gasto público como porcentaje del PIB</t>
+        </is>
+      </c>
+      <c r="N272" s="4" t="n"/>
+      <c r="O272" s="4" t="inlineStr">
+        <is>
+          <t>Banco Mundial - World Development Indicators</t>
+        </is>
+      </c>
+      <c r="P272" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="Q272" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -21047,7 +21737,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
@@ -21068,7 +21758,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
   </sheetData>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_sector_publico_e_instituciones.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_sector_publico_e_instituciones.xlsx
@@ -513,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q272"/>
+  <dimension ref="A1:Q270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -711,7 +711,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -865,7 +865,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -942,7 +942,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3483,7 +3483,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3868,7 +3868,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4099,7 +4099,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4253,7 +4253,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4407,7 +4407,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4484,7 +4484,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4792,7 +4792,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4869,7 +4869,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -4946,7 +4946,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5023,7 +5023,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5177,7 +5177,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5331,7 +5331,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5408,7 +5408,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5485,7 +5485,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5716,7 +5716,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5793,14 +5793,10 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q73" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q73" s="4" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
@@ -5874,14 +5870,10 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q74" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q74" s="4" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
@@ -5955,14 +5947,10 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q75" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q75" s="4" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
@@ -6036,14 +6024,10 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q76" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q76" s="4" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
@@ -6117,14 +6101,10 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q77" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q77" s="4" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
@@ -6198,14 +6178,10 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q78" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q78" s="4" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
@@ -6279,14 +6255,10 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q79" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q79" s="4" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
@@ -6360,14 +6332,10 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q80" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q80" s="4" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
@@ -6441,14 +6409,10 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q81" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q81" s="4" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
@@ -6522,14 +6486,10 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q82" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q82" s="4" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
@@ -6603,14 +6563,10 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q83" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q83" s="4" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
@@ -6684,14 +6640,10 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q84" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q84" s="4" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
@@ -6765,14 +6717,10 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q85" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q85" s="4" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
@@ -6846,14 +6794,10 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q86" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q86" s="4" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
@@ -6927,14 +6871,10 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q87" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q87" s="4" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
@@ -7008,14 +6948,10 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q88" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q88" s="4" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
@@ -7089,14 +7025,10 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q89" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q89" s="4" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
@@ -7170,14 +7102,10 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q90" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q90" s="4" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
@@ -7251,14 +7179,10 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q91" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q91" s="4" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
@@ -7332,14 +7256,10 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q92" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q92" s="4" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
@@ -7413,14 +7333,10 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q93" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q93" s="4" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
@@ -7494,14 +7410,10 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q94" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q94" s="4" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
@@ -7575,14 +7487,10 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q95" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q95" s="4" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
@@ -7656,14 +7564,10 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q96" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q96" s="4" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
@@ -7737,14 +7641,10 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q97" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q97" s="4" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
@@ -7818,14 +7718,10 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q98" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q98" s="4" t="n"/>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
@@ -7899,14 +7795,10 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q99" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q99" s="4" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
@@ -7980,14 +7872,10 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q100" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q100" s="4" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
@@ -8061,14 +7949,10 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q101" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q101" s="4" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
@@ -8142,14 +8026,10 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q102" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q102" s="4" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
@@ -8223,14 +8103,10 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q103" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q103" s="4" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
@@ -8304,14 +8180,10 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q104" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q104" s="4" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
@@ -8385,14 +8257,10 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q105" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q105" s="4" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
@@ -8466,14 +8334,10 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q106" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q106" s="4" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
@@ -8547,14 +8411,10 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q107" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q107" s="4" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
@@ -8628,14 +8488,10 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q108" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q108" s="4" t="n"/>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
@@ -8709,14 +8565,10 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q109" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q109" s="4" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
@@ -8790,14 +8642,10 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q110" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q110" s="4" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
@@ -8871,14 +8719,10 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q111" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q111" s="4" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
@@ -8952,14 +8796,10 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q112" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q112" s="4" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
@@ -9033,14 +8873,10 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q113" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q113" s="4" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
@@ -9114,14 +8950,10 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q114" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q114" s="4" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
@@ -9195,14 +9027,10 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q115" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q115" s="4" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
@@ -9276,14 +9104,10 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q116" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q116" s="4" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
@@ -9357,14 +9181,10 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q117" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q117" s="4" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
@@ -9438,14 +9258,10 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q118" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q118" s="4" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
@@ -9519,14 +9335,10 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q119" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q119" s="4" t="n"/>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
@@ -9600,14 +9412,10 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q120" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q120" s="4" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
@@ -9681,14 +9489,10 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q121" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q121" s="4" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
@@ -9762,14 +9566,10 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q122" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q122" s="4" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
@@ -9843,14 +9643,10 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q123" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q123" s="4" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
@@ -9924,14 +9720,10 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q124" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q124" s="4" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
@@ -10005,14 +9797,10 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q125" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q125" s="4" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
@@ -10086,14 +9874,10 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q126" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q126" s="4" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
@@ -10167,14 +9951,10 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q127" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q127" s="4" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
@@ -10248,14 +10028,10 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q128" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q128" s="4" t="n"/>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
@@ -10329,14 +10105,10 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q129" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q129" s="4" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
@@ -10410,14 +10182,10 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q130" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q130" s="4" t="n"/>
     </row>
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
@@ -10491,14 +10259,10 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q131" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q131" s="4" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
@@ -10572,14 +10336,10 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q132" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q132" s="4" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
@@ -10653,14 +10413,10 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q133" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q133" s="4" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
@@ -10734,14 +10490,10 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q134" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q134" s="4" t="n"/>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
@@ -10815,14 +10567,10 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q135" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q135" s="4" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
@@ -10896,14 +10644,10 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q136" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q136" s="4" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
@@ -10977,14 +10721,10 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q137" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q137" s="4" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
@@ -11058,14 +10798,10 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q138" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q138" s="4" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
@@ -11099,7 +10835,7 @@
         </is>
       </c>
       <c r="G139" s="5" t="n">
-        <v>2026</v>
+        <v>1960</v>
       </c>
       <c r="H139" s="4" t="inlineStr">
         <is>
@@ -11113,22 +10849,22 @@
       </c>
       <c r="J139" s="4" t="inlineStr">
         <is>
-          <t>Ingresos públicos</t>
+          <t>Fiscalidad</t>
         </is>
       </c>
       <c r="K139" s="4" t="inlineStr">
         <is>
-          <t>ingresos_publicos</t>
+          <t>fiscalidad</t>
         </is>
       </c>
       <c r="L139" s="4" t="inlineStr">
         <is>
-          <t>GC.REV.XGRT.GD.ZS</t>
+          <t>GC.TAX.TOTL.GD.ZS</t>
         </is>
       </c>
       <c r="M139" s="4" t="inlineStr">
         <is>
-          <t>Ingresos públicos excluidas donaciones como porcentaje del PIB</t>
+          <t>Ingresos tributarios como porcentaje del PIB</t>
         </is>
       </c>
       <c r="N139" s="4" t="n"/>
@@ -11139,14 +10875,10 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q139" s="4" t="inlineStr">
-        <is>
-          <t>HTTP Error 400: Bad Request</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q139" s="4" t="n"/>
     </row>
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
@@ -11180,7 +10912,7 @@
         </is>
       </c>
       <c r="G140" s="5" t="n">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="H140" s="4" t="inlineStr">
         <is>
@@ -11220,14 +10952,10 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q140" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q140" s="4" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
@@ -11261,7 +10989,7 @@
         </is>
       </c>
       <c r="G141" s="5" t="n">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="H141" s="4" t="inlineStr">
         <is>
@@ -11301,14 +11029,10 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q141" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q141" s="4" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
@@ -11342,7 +11066,7 @@
         </is>
       </c>
       <c r="G142" s="5" t="n">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="H142" s="4" t="inlineStr">
         <is>
@@ -11382,14 +11106,10 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q142" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q142" s="4" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
@@ -11423,7 +11143,7 @@
         </is>
       </c>
       <c r="G143" s="5" t="n">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="H143" s="4" t="inlineStr">
         <is>
@@ -11463,14 +11183,10 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q143" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q143" s="4" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
@@ -11504,7 +11220,7 @@
         </is>
       </c>
       <c r="G144" s="5" t="n">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="H144" s="4" t="inlineStr">
         <is>
@@ -11544,14 +11260,10 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q144" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q144" s="4" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
@@ -11585,7 +11297,7 @@
         </is>
       </c>
       <c r="G145" s="5" t="n">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="H145" s="4" t="inlineStr">
         <is>
@@ -11625,14 +11337,10 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q145" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q145" s="4" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
@@ -11666,7 +11374,7 @@
         </is>
       </c>
       <c r="G146" s="5" t="n">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="H146" s="4" t="inlineStr">
         <is>
@@ -11706,14 +11414,10 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q146" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q146" s="4" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
@@ -11747,7 +11451,7 @@
         </is>
       </c>
       <c r="G147" s="5" t="n">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="H147" s="4" t="inlineStr">
         <is>
@@ -11787,14 +11491,10 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q147" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q147" s="4" t="n"/>
     </row>
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
@@ -11828,7 +11528,7 @@
         </is>
       </c>
       <c r="G148" s="5" t="n">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="H148" s="4" t="inlineStr">
         <is>
@@ -11868,14 +11568,10 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q148" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q148" s="4" t="n"/>
     </row>
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
@@ -11909,7 +11605,7 @@
         </is>
       </c>
       <c r="G149" s="5" t="n">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="H149" s="4" t="inlineStr">
         <is>
@@ -11949,14 +11645,10 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q149" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q149" s="4" t="n"/>
     </row>
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
@@ -11990,7 +11682,7 @@
         </is>
       </c>
       <c r="G150" s="5" t="n">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="H150" s="4" t="inlineStr">
         <is>
@@ -12030,14 +11722,10 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q150" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q150" s="4" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
@@ -12071,7 +11759,7 @@
         </is>
       </c>
       <c r="G151" s="5" t="n">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="H151" s="4" t="inlineStr">
         <is>
@@ -12111,14 +11799,10 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q151" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q151" s="4" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
@@ -12152,7 +11836,7 @@
         </is>
       </c>
       <c r="G152" s="5" t="n">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="H152" s="4" t="inlineStr">
         <is>
@@ -12192,14 +11876,10 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q152" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q152" s="4" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
@@ -12233,7 +11913,7 @@
         </is>
       </c>
       <c r="G153" s="5" t="n">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="H153" s="4" t="inlineStr">
         <is>
@@ -12273,14 +11953,10 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q153" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q153" s="4" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
@@ -12314,7 +11990,7 @@
         </is>
       </c>
       <c r="G154" s="5" t="n">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="H154" s="4" t="inlineStr">
         <is>
@@ -12354,14 +12030,10 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q154" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q154" s="4" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
@@ -12395,7 +12067,7 @@
         </is>
       </c>
       <c r="G155" s="5" t="n">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="H155" s="4" t="inlineStr">
         <is>
@@ -12435,14 +12107,10 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q155" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q155" s="4" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
@@ -12476,7 +12144,7 @@
         </is>
       </c>
       <c r="G156" s="5" t="n">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="H156" s="4" t="inlineStr">
         <is>
@@ -12516,14 +12184,10 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q156" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q156" s="4" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
@@ -12557,7 +12221,7 @@
         </is>
       </c>
       <c r="G157" s="5" t="n">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="H157" s="4" t="inlineStr">
         <is>
@@ -12597,14 +12261,10 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q157" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q157" s="4" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
@@ -12638,7 +12298,7 @@
         </is>
       </c>
       <c r="G158" s="5" t="n">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="H158" s="4" t="inlineStr">
         <is>
@@ -12678,14 +12338,10 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q158" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q158" s="4" t="n"/>
     </row>
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
@@ -12719,7 +12375,7 @@
         </is>
       </c>
       <c r="G159" s="5" t="n">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="H159" s="4" t="inlineStr">
         <is>
@@ -12759,14 +12415,10 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q159" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q159" s="4" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
@@ -12800,7 +12452,7 @@
         </is>
       </c>
       <c r="G160" s="5" t="n">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="H160" s="4" t="inlineStr">
         <is>
@@ -12840,14 +12492,10 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q160" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q160" s="4" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
@@ -12881,7 +12529,7 @@
         </is>
       </c>
       <c r="G161" s="5" t="n">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="H161" s="4" t="inlineStr">
         <is>
@@ -12921,14 +12569,10 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q161" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q161" s="4" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
@@ -12962,7 +12606,7 @@
         </is>
       </c>
       <c r="G162" s="5" t="n">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="H162" s="4" t="inlineStr">
         <is>
@@ -13002,14 +12646,10 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q162" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q162" s="4" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
@@ -13043,7 +12683,7 @@
         </is>
       </c>
       <c r="G163" s="5" t="n">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="H163" s="4" t="inlineStr">
         <is>
@@ -13083,14 +12723,10 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q163" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q163" s="4" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
@@ -13124,7 +12760,7 @@
         </is>
       </c>
       <c r="G164" s="5" t="n">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="H164" s="4" t="inlineStr">
         <is>
@@ -13164,14 +12800,10 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q164" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q164" s="4" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
@@ -13205,7 +12837,7 @@
         </is>
       </c>
       <c r="G165" s="5" t="n">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="H165" s="4" t="inlineStr">
         <is>
@@ -13245,14 +12877,10 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q165" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q165" s="4" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
@@ -13286,7 +12914,7 @@
         </is>
       </c>
       <c r="G166" s="5" t="n">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="H166" s="4" t="inlineStr">
         <is>
@@ -13326,14 +12954,10 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q166" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q166" s="4" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
@@ -13367,7 +12991,7 @@
         </is>
       </c>
       <c r="G167" s="5" t="n">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="H167" s="4" t="inlineStr">
         <is>
@@ -13407,14 +13031,10 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q167" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q167" s="4" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
@@ -13448,7 +13068,7 @@
         </is>
       </c>
       <c r="G168" s="5" t="n">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="H168" s="4" t="inlineStr">
         <is>
@@ -13488,14 +13108,10 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q168" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q168" s="4" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
@@ -13529,7 +13145,7 @@
         </is>
       </c>
       <c r="G169" s="5" t="n">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="H169" s="4" t="inlineStr">
         <is>
@@ -13569,14 +13185,10 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q169" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q169" s="4" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
@@ -13610,7 +13222,7 @@
         </is>
       </c>
       <c r="G170" s="5" t="n">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="H170" s="4" t="inlineStr">
         <is>
@@ -13650,14 +13262,10 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q170" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q170" s="4" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
@@ -13691,7 +13299,7 @@
         </is>
       </c>
       <c r="G171" s="5" t="n">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="H171" s="4" t="inlineStr">
         <is>
@@ -13731,14 +13339,10 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q171" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q171" s="4" t="n"/>
     </row>
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
@@ -13772,7 +13376,7 @@
         </is>
       </c>
       <c r="G172" s="5" t="n">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="H172" s="4" t="inlineStr">
         <is>
@@ -13812,14 +13416,10 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q172" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q172" s="4" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
@@ -13853,7 +13453,7 @@
         </is>
       </c>
       <c r="G173" s="5" t="n">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="H173" s="4" t="inlineStr">
         <is>
@@ -13893,14 +13493,10 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q173" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q173" s="4" t="n"/>
     </row>
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
@@ -13934,7 +13530,7 @@
         </is>
       </c>
       <c r="G174" s="5" t="n">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="H174" s="4" t="inlineStr">
         <is>
@@ -13974,14 +13570,10 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q174" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q174" s="4" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
@@ -14015,7 +13607,7 @@
         </is>
       </c>
       <c r="G175" s="5" t="n">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="H175" s="4" t="inlineStr">
         <is>
@@ -14055,14 +13647,10 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q175" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q175" s="4" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="4" t="inlineStr">
@@ -14096,7 +13684,7 @@
         </is>
       </c>
       <c r="G176" s="5" t="n">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="H176" s="4" t="inlineStr">
         <is>
@@ -14136,14 +13724,10 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q176" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q176" s="4" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
@@ -14177,7 +13761,7 @@
         </is>
       </c>
       <c r="G177" s="5" t="n">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="H177" s="4" t="inlineStr">
         <is>
@@ -14217,14 +13801,10 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q177" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q177" s="4" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
@@ -14258,7 +13838,7 @@
         </is>
       </c>
       <c r="G178" s="5" t="n">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="H178" s="4" t="inlineStr">
         <is>
@@ -14298,14 +13878,10 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q178" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q178" s="4" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
@@ -14339,7 +13915,7 @@
         </is>
       </c>
       <c r="G179" s="5" t="n">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="H179" s="4" t="inlineStr">
         <is>
@@ -14379,14 +13955,10 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q179" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q179" s="4" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="4" t="inlineStr">
@@ -14420,7 +13992,7 @@
         </is>
       </c>
       <c r="G180" s="5" t="n">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="H180" s="4" t="inlineStr">
         <is>
@@ -14460,14 +14032,10 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q180" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q180" s="4" t="n"/>
     </row>
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
@@ -14501,7 +14069,7 @@
         </is>
       </c>
       <c r="G181" s="5" t="n">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="H181" s="4" t="inlineStr">
         <is>
@@ -14541,14 +14109,10 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q181" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q181" s="4" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
@@ -14582,7 +14146,7 @@
         </is>
       </c>
       <c r="G182" s="5" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="H182" s="4" t="inlineStr">
         <is>
@@ -14622,14 +14186,10 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q182" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q182" s="4" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
@@ -14663,7 +14223,7 @@
         </is>
       </c>
       <c r="G183" s="5" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="H183" s="4" t="inlineStr">
         <is>
@@ -14703,14 +14263,10 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q183" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q183" s="4" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
@@ -14744,7 +14300,7 @@
         </is>
       </c>
       <c r="G184" s="5" t="n">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="H184" s="4" t="inlineStr">
         <is>
@@ -14784,14 +14340,10 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q184" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q184" s="4" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
@@ -14825,7 +14377,7 @@
         </is>
       </c>
       <c r="G185" s="5" t="n">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="H185" s="4" t="inlineStr">
         <is>
@@ -14865,14 +14417,10 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q185" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q185" s="4" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
@@ -14906,7 +14454,7 @@
         </is>
       </c>
       <c r="G186" s="5" t="n">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="H186" s="4" t="inlineStr">
         <is>
@@ -14946,14 +14494,10 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q186" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q186" s="4" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
@@ -14987,7 +14531,7 @@
         </is>
       </c>
       <c r="G187" s="5" t="n">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="H187" s="4" t="inlineStr">
         <is>
@@ -15027,14 +14571,10 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q187" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q187" s="4" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="4" t="inlineStr">
@@ -15068,7 +14608,7 @@
         </is>
       </c>
       <c r="G188" s="5" t="n">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="H188" s="4" t="inlineStr">
         <is>
@@ -15108,14 +14648,10 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q188" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q188" s="4" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
@@ -15149,7 +14685,7 @@
         </is>
       </c>
       <c r="G189" s="5" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="H189" s="4" t="inlineStr">
         <is>
@@ -15189,14 +14725,10 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q189" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q189" s="4" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="4" t="inlineStr">
@@ -15230,7 +14762,7 @@
         </is>
       </c>
       <c r="G190" s="5" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="H190" s="4" t="inlineStr">
         <is>
@@ -15270,14 +14802,10 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q190" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q190" s="4" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
@@ -15311,7 +14839,7 @@
         </is>
       </c>
       <c r="G191" s="5" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="H191" s="4" t="inlineStr">
         <is>
@@ -15351,14 +14879,10 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q191" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q191" s="4" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
@@ -15392,7 +14916,7 @@
         </is>
       </c>
       <c r="G192" s="5" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="H192" s="4" t="inlineStr">
         <is>
@@ -15432,14 +14956,10 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q192" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q192" s="4" t="n"/>
     </row>
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
@@ -15473,7 +14993,7 @@
         </is>
       </c>
       <c r="G193" s="5" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="H193" s="4" t="inlineStr">
         <is>
@@ -15513,14 +15033,10 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q193" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q193" s="4" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="4" t="inlineStr">
@@ -15554,7 +15070,7 @@
         </is>
       </c>
       <c r="G194" s="5" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="H194" s="4" t="inlineStr">
         <is>
@@ -15594,14 +15110,10 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q194" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q194" s="4" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
@@ -15635,7 +15147,7 @@
         </is>
       </c>
       <c r="G195" s="5" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="H195" s="4" t="inlineStr">
         <is>
@@ -15675,14 +15187,10 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q195" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q195" s="4" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="4" t="inlineStr">
@@ -15716,7 +15224,7 @@
         </is>
       </c>
       <c r="G196" s="5" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="H196" s="4" t="inlineStr">
         <is>
@@ -15756,14 +15264,10 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q196" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q196" s="4" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="4" t="inlineStr">
@@ -15797,7 +15301,7 @@
         </is>
       </c>
       <c r="G197" s="5" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="H197" s="4" t="inlineStr">
         <is>
@@ -15837,14 +15341,10 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q197" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q197" s="4" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="4" t="inlineStr">
@@ -15878,7 +15378,7 @@
         </is>
       </c>
       <c r="G198" s="5" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="H198" s="4" t="inlineStr">
         <is>
@@ -15918,14 +15418,10 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q198" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q198" s="4" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="4" t="inlineStr">
@@ -15959,7 +15455,7 @@
         </is>
       </c>
       <c r="G199" s="5" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="H199" s="4" t="inlineStr">
         <is>
@@ -15999,14 +15495,10 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q199" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q199" s="4" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="4" t="inlineStr">
@@ -16040,7 +15532,7 @@
         </is>
       </c>
       <c r="G200" s="5" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="H200" s="4" t="inlineStr">
         <is>
@@ -16080,14 +15572,10 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q200" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q200" s="4" t="n"/>
     </row>
     <row r="201">
       <c r="A201" s="4" t="inlineStr">
@@ -16121,7 +15609,7 @@
         </is>
       </c>
       <c r="G201" s="5" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="H201" s="4" t="inlineStr">
         <is>
@@ -16161,14 +15649,10 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q201" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q201" s="4" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="4" t="inlineStr">
@@ -16202,7 +15686,7 @@
         </is>
       </c>
       <c r="G202" s="5" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="H202" s="4" t="inlineStr">
         <is>
@@ -16242,14 +15726,10 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q202" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q202" s="4" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
@@ -16283,7 +15763,7 @@
         </is>
       </c>
       <c r="G203" s="5" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="H203" s="4" t="inlineStr">
         <is>
@@ -16323,14 +15803,10 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q203" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q203" s="4" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="4" t="inlineStr">
@@ -16364,7 +15840,7 @@
         </is>
       </c>
       <c r="G204" s="5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="H204" s="4" t="inlineStr">
         <is>
@@ -16404,14 +15880,10 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q204" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q204" s="4" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="4" t="inlineStr">
@@ -16445,7 +15917,7 @@
         </is>
       </c>
       <c r="G205" s="5" t="n">
-        <v>2025</v>
+        <v>1960</v>
       </c>
       <c r="H205" s="4" t="inlineStr">
         <is>
@@ -16459,22 +15931,22 @@
       </c>
       <c r="J205" s="4" t="inlineStr">
         <is>
-          <t>Fiscalidad</t>
+          <t>Gasto público</t>
         </is>
       </c>
       <c r="K205" s="4" t="inlineStr">
         <is>
-          <t>fiscalidad</t>
+          <t>gasto_publico</t>
         </is>
       </c>
       <c r="L205" s="4" t="inlineStr">
         <is>
-          <t>GC.TAX.TOTL.GD.ZS</t>
+          <t>GC.XPN.TOTL.GD.ZS</t>
         </is>
       </c>
       <c r="M205" s="4" t="inlineStr">
         <is>
-          <t>Ingresos tributarios como porcentaje del PIB</t>
+          <t>Gasto público como porcentaje del PIB</t>
         </is>
       </c>
       <c r="N205" s="4" t="n"/>
@@ -16485,14 +15957,10 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q205" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q205" s="4" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="4" t="inlineStr">
@@ -16526,7 +15994,7 @@
         </is>
       </c>
       <c r="G206" s="5" t="n">
-        <v>2026</v>
+        <v>1961</v>
       </c>
       <c r="H206" s="4" t="inlineStr">
         <is>
@@ -16540,22 +16008,22 @@
       </c>
       <c r="J206" s="4" t="inlineStr">
         <is>
-          <t>Fiscalidad</t>
+          <t>Gasto público</t>
         </is>
       </c>
       <c r="K206" s="4" t="inlineStr">
         <is>
-          <t>fiscalidad</t>
+          <t>gasto_publico</t>
         </is>
       </c>
       <c r="L206" s="4" t="inlineStr">
         <is>
-          <t>GC.TAX.TOTL.GD.ZS</t>
+          <t>GC.XPN.TOTL.GD.ZS</t>
         </is>
       </c>
       <c r="M206" s="4" t="inlineStr">
         <is>
-          <t>Ingresos tributarios como porcentaje del PIB</t>
+          <t>Gasto público como porcentaje del PIB</t>
         </is>
       </c>
       <c r="N206" s="4" t="n"/>
@@ -16566,14 +16034,10 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q206" s="4" t="inlineStr">
-        <is>
-          <t>The read operation timed out</t>
-        </is>
-      </c>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Q206" s="4" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
@@ -16607,7 +16071,7 @@
         </is>
       </c>
       <c r="G207" s="5" t="n">
-        <v>1960</v>
+        <v>1962</v>
       </c>
       <c r="H207" s="4" t="inlineStr">
         <is>
@@ -16647,7 +16111,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16684,7 +16148,7 @@
         </is>
       </c>
       <c r="G208" s="5" t="n">
-        <v>1961</v>
+        <v>1963</v>
       </c>
       <c r="H208" s="4" t="inlineStr">
         <is>
@@ -16724,7 +16188,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16761,7 +16225,7 @@
         </is>
       </c>
       <c r="G209" s="5" t="n">
-        <v>1962</v>
+        <v>1964</v>
       </c>
       <c r="H209" s="4" t="inlineStr">
         <is>
@@ -16801,7 +16265,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16838,7 +16302,7 @@
         </is>
       </c>
       <c r="G210" s="5" t="n">
-        <v>1963</v>
+        <v>1965</v>
       </c>
       <c r="H210" s="4" t="inlineStr">
         <is>
@@ -16878,7 +16342,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16915,7 +16379,7 @@
         </is>
       </c>
       <c r="G211" s="5" t="n">
-        <v>1964</v>
+        <v>1966</v>
       </c>
       <c r="H211" s="4" t="inlineStr">
         <is>
@@ -16955,7 +16419,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16992,7 +16456,7 @@
         </is>
       </c>
       <c r="G212" s="5" t="n">
-        <v>1965</v>
+        <v>1967</v>
       </c>
       <c r="H212" s="4" t="inlineStr">
         <is>
@@ -17032,7 +16496,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -17069,7 +16533,7 @@
         </is>
       </c>
       <c r="G213" s="5" t="n">
-        <v>1966</v>
+        <v>1968</v>
       </c>
       <c r="H213" s="4" t="inlineStr">
         <is>
@@ -17109,7 +16573,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -17146,7 +16610,7 @@
         </is>
       </c>
       <c r="G214" s="5" t="n">
-        <v>1967</v>
+        <v>1969</v>
       </c>
       <c r="H214" s="4" t="inlineStr">
         <is>
@@ -17186,7 +16650,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -17223,7 +16687,7 @@
         </is>
       </c>
       <c r="G215" s="5" t="n">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="H215" s="4" t="inlineStr">
         <is>
@@ -17263,7 +16727,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -17300,7 +16764,7 @@
         </is>
       </c>
       <c r="G216" s="5" t="n">
-        <v>1969</v>
+        <v>1971</v>
       </c>
       <c r="H216" s="4" t="inlineStr">
         <is>
@@ -17340,7 +16804,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -17377,7 +16841,7 @@
         </is>
       </c>
       <c r="G217" s="5" t="n">
-        <v>1970</v>
+        <v>1972</v>
       </c>
       <c r="H217" s="4" t="inlineStr">
         <is>
@@ -17417,7 +16881,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -17454,7 +16918,7 @@
         </is>
       </c>
       <c r="G218" s="5" t="n">
-        <v>1971</v>
+        <v>1973</v>
       </c>
       <c r="H218" s="4" t="inlineStr">
         <is>
@@ -17494,7 +16958,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17531,7 +16995,7 @@
         </is>
       </c>
       <c r="G219" s="5" t="n">
-        <v>1972</v>
+        <v>1974</v>
       </c>
       <c r="H219" s="4" t="inlineStr">
         <is>
@@ -17571,7 +17035,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17608,7 +17072,7 @@
         </is>
       </c>
       <c r="G220" s="5" t="n">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="H220" s="4" t="inlineStr">
         <is>
@@ -17648,7 +17112,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17685,7 +17149,7 @@
         </is>
       </c>
       <c r="G221" s="5" t="n">
-        <v>1974</v>
+        <v>1976</v>
       </c>
       <c r="H221" s="4" t="inlineStr">
         <is>
@@ -17725,7 +17189,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17762,7 +17226,7 @@
         </is>
       </c>
       <c r="G222" s="5" t="n">
-        <v>1975</v>
+        <v>1977</v>
       </c>
       <c r="H222" s="4" t="inlineStr">
         <is>
@@ -17802,7 +17266,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17839,7 +17303,7 @@
         </is>
       </c>
       <c r="G223" s="5" t="n">
-        <v>1976</v>
+        <v>1978</v>
       </c>
       <c r="H223" s="4" t="inlineStr">
         <is>
@@ -17879,7 +17343,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17916,7 +17380,7 @@
         </is>
       </c>
       <c r="G224" s="5" t="n">
-        <v>1977</v>
+        <v>1979</v>
       </c>
       <c r="H224" s="4" t="inlineStr">
         <is>
@@ -17956,7 +17420,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17993,7 +17457,7 @@
         </is>
       </c>
       <c r="G225" s="5" t="n">
-        <v>1978</v>
+        <v>1980</v>
       </c>
       <c r="H225" s="4" t="inlineStr">
         <is>
@@ -18033,7 +17497,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -18070,7 +17534,7 @@
         </is>
       </c>
       <c r="G226" s="5" t="n">
-        <v>1979</v>
+        <v>1981</v>
       </c>
       <c r="H226" s="4" t="inlineStr">
         <is>
@@ -18110,7 +17574,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -18147,7 +17611,7 @@
         </is>
       </c>
       <c r="G227" s="5" t="n">
-        <v>1980</v>
+        <v>1982</v>
       </c>
       <c r="H227" s="4" t="inlineStr">
         <is>
@@ -18187,7 +17651,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -18224,7 +17688,7 @@
         </is>
       </c>
       <c r="G228" s="5" t="n">
-        <v>1981</v>
+        <v>1983</v>
       </c>
       <c r="H228" s="4" t="inlineStr">
         <is>
@@ -18264,7 +17728,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -18301,7 +17765,7 @@
         </is>
       </c>
       <c r="G229" s="5" t="n">
-        <v>1982</v>
+        <v>1984</v>
       </c>
       <c r="H229" s="4" t="inlineStr">
         <is>
@@ -18341,7 +17805,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -18378,7 +17842,7 @@
         </is>
       </c>
       <c r="G230" s="5" t="n">
-        <v>1983</v>
+        <v>1985</v>
       </c>
       <c r="H230" s="4" t="inlineStr">
         <is>
@@ -18418,7 +17882,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -18455,7 +17919,7 @@
         </is>
       </c>
       <c r="G231" s="5" t="n">
-        <v>1984</v>
+        <v>1986</v>
       </c>
       <c r="H231" s="4" t="inlineStr">
         <is>
@@ -18495,7 +17959,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18532,7 +17996,7 @@
         </is>
       </c>
       <c r="G232" s="5" t="n">
-        <v>1985</v>
+        <v>1987</v>
       </c>
       <c r="H232" s="4" t="inlineStr">
         <is>
@@ -18572,7 +18036,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18609,7 +18073,7 @@
         </is>
       </c>
       <c r="G233" s="5" t="n">
-        <v>1986</v>
+        <v>1988</v>
       </c>
       <c r="H233" s="4" t="inlineStr">
         <is>
@@ -18649,7 +18113,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18686,7 +18150,7 @@
         </is>
       </c>
       <c r="G234" s="5" t="n">
-        <v>1987</v>
+        <v>1989</v>
       </c>
       <c r="H234" s="4" t="inlineStr">
         <is>
@@ -18726,7 +18190,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18763,7 +18227,7 @@
         </is>
       </c>
       <c r="G235" s="5" t="n">
-        <v>1988</v>
+        <v>1990</v>
       </c>
       <c r="H235" s="4" t="inlineStr">
         <is>
@@ -18803,7 +18267,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18840,7 +18304,7 @@
         </is>
       </c>
       <c r="G236" s="5" t="n">
-        <v>1989</v>
+        <v>1991</v>
       </c>
       <c r="H236" s="4" t="inlineStr">
         <is>
@@ -18880,7 +18344,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18917,7 +18381,7 @@
         </is>
       </c>
       <c r="G237" s="5" t="n">
-        <v>1990</v>
+        <v>1992</v>
       </c>
       <c r="H237" s="4" t="inlineStr">
         <is>
@@ -18957,7 +18421,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18994,7 +18458,7 @@
         </is>
       </c>
       <c r="G238" s="5" t="n">
-        <v>1991</v>
+        <v>1993</v>
       </c>
       <c r="H238" s="4" t="inlineStr">
         <is>
@@ -19034,7 +18498,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -19071,7 +18535,7 @@
         </is>
       </c>
       <c r="G239" s="5" t="n">
-        <v>1992</v>
+        <v>1994</v>
       </c>
       <c r="H239" s="4" t="inlineStr">
         <is>
@@ -19111,7 +18575,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -19148,7 +18612,7 @@
         </is>
       </c>
       <c r="G240" s="5" t="n">
-        <v>1993</v>
+        <v>1995</v>
       </c>
       <c r="H240" s="4" t="inlineStr">
         <is>
@@ -19188,7 +18652,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -19225,7 +18689,7 @@
         </is>
       </c>
       <c r="G241" s="5" t="n">
-        <v>1994</v>
+        <v>1996</v>
       </c>
       <c r="H241" s="4" t="inlineStr">
         <is>
@@ -19265,7 +18729,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -19302,7 +18766,7 @@
         </is>
       </c>
       <c r="G242" s="5" t="n">
-        <v>1995</v>
+        <v>1997</v>
       </c>
       <c r="H242" s="4" t="inlineStr">
         <is>
@@ -19342,7 +18806,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -19379,7 +18843,7 @@
         </is>
       </c>
       <c r="G243" s="5" t="n">
-        <v>1996</v>
+        <v>1998</v>
       </c>
       <c r="H243" s="4" t="inlineStr">
         <is>
@@ -19419,7 +18883,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -19456,7 +18920,7 @@
         </is>
       </c>
       <c r="G244" s="5" t="n">
-        <v>1997</v>
+        <v>1999</v>
       </c>
       <c r="H244" s="4" t="inlineStr">
         <is>
@@ -19496,7 +18960,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19533,7 +18997,7 @@
         </is>
       </c>
       <c r="G245" s="5" t="n">
-        <v>1998</v>
+        <v>2000</v>
       </c>
       <c r="H245" s="4" t="inlineStr">
         <is>
@@ -19573,7 +19037,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19610,7 +19074,7 @@
         </is>
       </c>
       <c r="G246" s="5" t="n">
-        <v>1999</v>
+        <v>2001</v>
       </c>
       <c r="H246" s="4" t="inlineStr">
         <is>
@@ -19650,7 +19114,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19687,7 +19151,7 @@
         </is>
       </c>
       <c r="G247" s="5" t="n">
-        <v>2000</v>
+        <v>2002</v>
       </c>
       <c r="H247" s="4" t="inlineStr">
         <is>
@@ -19727,7 +19191,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19764,7 +19228,7 @@
         </is>
       </c>
       <c r="G248" s="5" t="n">
-        <v>2001</v>
+        <v>2003</v>
       </c>
       <c r="H248" s="4" t="inlineStr">
         <is>
@@ -19804,7 +19268,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19841,7 +19305,7 @@
         </is>
       </c>
       <c r="G249" s="5" t="n">
-        <v>2002</v>
+        <v>2004</v>
       </c>
       <c r="H249" s="4" t="inlineStr">
         <is>
@@ -19881,7 +19345,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19918,7 +19382,7 @@
         </is>
       </c>
       <c r="G250" s="5" t="n">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="H250" s="4" t="inlineStr">
         <is>
@@ -19958,7 +19422,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19995,7 +19459,7 @@
         </is>
       </c>
       <c r="G251" s="5" t="n">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="H251" s="4" t="inlineStr">
         <is>
@@ -20035,7 +19499,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -20072,7 +19536,7 @@
         </is>
       </c>
       <c r="G252" s="5" t="n">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="H252" s="4" t="inlineStr">
         <is>
@@ -20112,7 +19576,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -20149,7 +19613,7 @@
         </is>
       </c>
       <c r="G253" s="5" t="n">
-        <v>2006</v>
+        <v>2008</v>
       </c>
       <c r="H253" s="4" t="inlineStr">
         <is>
@@ -20189,7 +19653,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -20226,7 +19690,7 @@
         </is>
       </c>
       <c r="G254" s="5" t="n">
-        <v>2007</v>
+        <v>2009</v>
       </c>
       <c r="H254" s="4" t="inlineStr">
         <is>
@@ -20266,7 +19730,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -20303,7 +19767,7 @@
         </is>
       </c>
       <c r="G255" s="5" t="n">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="H255" s="4" t="inlineStr">
         <is>
@@ -20343,7 +19807,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -20380,7 +19844,7 @@
         </is>
       </c>
       <c r="G256" s="5" t="n">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="H256" s="4" t="inlineStr">
         <is>
@@ -20420,7 +19884,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -20457,7 +19921,7 @@
         </is>
       </c>
       <c r="G257" s="5" t="n">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="H257" s="4" t="inlineStr">
         <is>
@@ -20497,7 +19961,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20534,7 +19998,7 @@
         </is>
       </c>
       <c r="G258" s="5" t="n">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="H258" s="4" t="inlineStr">
         <is>
@@ -20574,7 +20038,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20611,7 +20075,7 @@
         </is>
       </c>
       <c r="G259" s="5" t="n">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="H259" s="4" t="inlineStr">
         <is>
@@ -20651,7 +20115,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20688,7 +20152,7 @@
         </is>
       </c>
       <c r="G260" s="5" t="n">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="H260" s="4" t="inlineStr">
         <is>
@@ -20728,7 +20192,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20765,7 +20229,7 @@
         </is>
       </c>
       <c r="G261" s="5" t="n">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="H261" s="4" t="inlineStr">
         <is>
@@ -20805,7 +20269,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20842,7 +20306,7 @@
         </is>
       </c>
       <c r="G262" s="5" t="n">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="H262" s="4" t="inlineStr">
         <is>
@@ -20882,7 +20346,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20919,7 +20383,7 @@
         </is>
       </c>
       <c r="G263" s="5" t="n">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="H263" s="4" t="inlineStr">
         <is>
@@ -20959,7 +20423,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20996,7 +20460,7 @@
         </is>
       </c>
       <c r="G264" s="5" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="H264" s="4" t="inlineStr">
         <is>
@@ -21036,7 +20500,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -21073,7 +20537,7 @@
         </is>
       </c>
       <c r="G265" s="5" t="n">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="H265" s="4" t="inlineStr">
         <is>
@@ -21113,7 +20577,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -21150,7 +20614,7 @@
         </is>
       </c>
       <c r="G266" s="5" t="n">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="H266" s="4" t="inlineStr">
         <is>
@@ -21190,7 +20654,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -21227,7 +20691,7 @@
         </is>
       </c>
       <c r="G267" s="5" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="H267" s="4" t="inlineStr">
         <is>
@@ -21267,7 +20731,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -21304,7 +20768,7 @@
         </is>
       </c>
       <c r="G268" s="5" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="H268" s="4" t="inlineStr">
         <is>
@@ -21344,7 +20808,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -21381,7 +20845,7 @@
         </is>
       </c>
       <c r="G269" s="5" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="H269" s="4" t="inlineStr">
         <is>
@@ -21421,7 +20885,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -21458,7 +20922,7 @@
         </is>
       </c>
       <c r="G270" s="5" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="H270" s="4" t="inlineStr">
         <is>
@@ -21498,164 +20962,10 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
-    </row>
-    <row r="271">
-      <c r="A271" s="4" t="inlineStr">
-        <is>
-          <t>Venezuela</t>
-        </is>
-      </c>
-      <c r="B271" s="4" t="inlineStr">
-        <is>
-          <t>Venezuela, RB</t>
-        </is>
-      </c>
-      <c r="C271" s="4" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D271" s="4" t="inlineStr">
-        <is>
-          <t>VEN</t>
-        </is>
-      </c>
-      <c r="E271" s="4" t="inlineStr">
-        <is>
-          <t>Latin America &amp; Caribbean</t>
-        </is>
-      </c>
-      <c r="F271" s="4" t="inlineStr">
-        <is>
-          <t>Not classified</t>
-        </is>
-      </c>
-      <c r="G271" s="5" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H271" s="4" t="inlineStr">
-        <is>
-          <t>Sector público e instituciones</t>
-        </is>
-      </c>
-      <c r="I271" s="4" t="inlineStr">
-        <is>
-          <t>sector_publico_e_instituciones</t>
-        </is>
-      </c>
-      <c r="J271" s="4" t="inlineStr">
-        <is>
-          <t>Gasto público</t>
-        </is>
-      </c>
-      <c r="K271" s="4" t="inlineStr">
-        <is>
-          <t>gasto_publico</t>
-        </is>
-      </c>
-      <c r="L271" s="4" t="inlineStr">
-        <is>
-          <t>GC.XPN.TOTL.GD.ZS</t>
-        </is>
-      </c>
-      <c r="M271" s="4" t="inlineStr">
-        <is>
-          <t>Gasto público como porcentaje del PIB</t>
-        </is>
-      </c>
-      <c r="N271" s="4" t="n"/>
-      <c r="O271" s="4" t="inlineStr">
-        <is>
-          <t>Banco Mundial - World Development Indicators</t>
-        </is>
-      </c>
-      <c r="P271" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q271" s="4" t="n"/>
-    </row>
-    <row r="272">
-      <c r="A272" s="4" t="inlineStr">
-        <is>
-          <t>Venezuela</t>
-        </is>
-      </c>
-      <c r="B272" s="4" t="inlineStr">
-        <is>
-          <t>Venezuela, RB</t>
-        </is>
-      </c>
-      <c r="C272" s="4" t="inlineStr">
-        <is>
-          <t>VE</t>
-        </is>
-      </c>
-      <c r="D272" s="4" t="inlineStr">
-        <is>
-          <t>VEN</t>
-        </is>
-      </c>
-      <c r="E272" s="4" t="inlineStr">
-        <is>
-          <t>Latin America &amp; Caribbean</t>
-        </is>
-      </c>
-      <c r="F272" s="4" t="inlineStr">
-        <is>
-          <t>Not classified</t>
-        </is>
-      </c>
-      <c r="G272" s="5" t="n">
-        <v>2025</v>
-      </c>
-      <c r="H272" s="4" t="inlineStr">
-        <is>
-          <t>Sector público e instituciones</t>
-        </is>
-      </c>
-      <c r="I272" s="4" t="inlineStr">
-        <is>
-          <t>sector_publico_e_instituciones</t>
-        </is>
-      </c>
-      <c r="J272" s="4" t="inlineStr">
-        <is>
-          <t>Gasto público</t>
-        </is>
-      </c>
-      <c r="K272" s="4" t="inlineStr">
-        <is>
-          <t>gasto_publico</t>
-        </is>
-      </c>
-      <c r="L272" s="4" t="inlineStr">
-        <is>
-          <t>GC.XPN.TOTL.GD.ZS</t>
-        </is>
-      </c>
-      <c r="M272" s="4" t="inlineStr">
-        <is>
-          <t>Gasto público como porcentaje del PIB</t>
-        </is>
-      </c>
-      <c r="N272" s="4" t="n"/>
-      <c r="O272" s="4" t="inlineStr">
-        <is>
-          <t>Banco Mundial - World Development Indicators</t>
-        </is>
-      </c>
-      <c r="P272" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="Q272" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -21737,7 +21047,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -21758,7 +21068,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
   </sheetData>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_sector_publico_e_instituciones.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_sector_publico_e_instituciones.xlsx
@@ -711,7 +711,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -865,7 +865,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -942,7 +942,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3483,7 +3483,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3868,7 +3868,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4099,7 +4099,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4253,7 +4253,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4407,7 +4407,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4484,7 +4484,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4792,7 +4792,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4869,7 +4869,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -4946,7 +4946,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5023,7 +5023,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5177,7 +5177,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5331,7 +5331,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5408,7 +5408,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5485,7 +5485,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5716,7 +5716,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5870,7 +5870,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -5947,7 +5947,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6024,7 +6024,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6255,7 +6255,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6332,7 +6332,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6409,7 +6409,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6717,7 +6717,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6794,7 +6794,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6871,7 +6871,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7025,7 +7025,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7102,7 +7102,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7179,7 +7179,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7256,7 +7256,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7410,7 +7410,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7487,7 +7487,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7564,7 +7564,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7641,7 +7641,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7795,7 +7795,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7872,7 +7872,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -7949,7 +7949,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8026,7 +8026,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8180,7 +8180,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8257,7 +8257,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8334,7 +8334,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8411,7 +8411,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8488,7 +8488,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8565,7 +8565,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8642,7 +8642,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8719,7 +8719,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8796,7 +8796,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8873,7 +8873,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -8950,7 +8950,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9104,7 +9104,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9181,7 +9181,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9258,7 +9258,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9335,7 +9335,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9489,7 +9489,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9566,7 +9566,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9643,7 +9643,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9720,7 +9720,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9797,7 +9797,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -9874,7 +9874,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -9951,7 +9951,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10028,7 +10028,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10105,7 +10105,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10182,7 +10182,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10259,7 +10259,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10336,7 +10336,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10413,7 +10413,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10490,7 +10490,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10567,7 +10567,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10644,7 +10644,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10721,7 +10721,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10798,7 +10798,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -10875,7 +10875,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11029,7 +11029,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11183,7 +11183,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11260,7 +11260,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11337,7 +11337,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11414,7 +11414,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11491,7 +11491,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11568,7 +11568,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11645,7 +11645,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11722,7 +11722,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11799,7 +11799,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -11876,7 +11876,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -11953,7 +11953,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12030,7 +12030,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12107,7 +12107,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12184,7 +12184,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12261,7 +12261,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12415,7 +12415,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12492,7 +12492,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12569,7 +12569,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12646,7 +12646,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12723,7 +12723,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12800,7 +12800,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -12877,7 +12877,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -12954,7 +12954,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13031,7 +13031,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13108,7 +13108,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13185,7 +13185,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13262,7 +13262,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13339,7 +13339,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13416,7 +13416,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13493,7 +13493,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13570,7 +13570,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13647,7 +13647,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13801,7 +13801,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -13878,7 +13878,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -13955,7 +13955,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14032,7 +14032,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14109,7 +14109,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14186,7 +14186,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14263,7 +14263,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14340,7 +14340,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14417,7 +14417,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14494,7 +14494,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14571,7 +14571,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14648,7 +14648,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14725,7 +14725,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -14802,7 +14802,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -14879,7 +14879,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -14956,7 +14956,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15033,7 +15033,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15110,7 +15110,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15187,7 +15187,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15264,7 +15264,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15341,7 +15341,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15418,7 +15418,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15495,7 +15495,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15572,7 +15572,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15649,7 +15649,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15726,7 +15726,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -15803,7 +15803,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -15880,7 +15880,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -15957,7 +15957,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16034,7 +16034,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16111,7 +16111,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16188,7 +16188,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16265,7 +16265,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16342,7 +16342,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16419,7 +16419,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16496,7 +16496,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16573,7 +16573,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16650,7 +16650,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16727,7 +16727,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -16804,7 +16804,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -16881,7 +16881,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -16958,7 +16958,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17035,7 +17035,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17112,7 +17112,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17189,7 +17189,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17266,7 +17266,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17420,7 +17420,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17497,7 +17497,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17574,7 +17574,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17651,7 +17651,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17728,7 +17728,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -17805,7 +17805,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -17882,7 +17882,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -17959,7 +17959,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18036,7 +18036,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18113,7 +18113,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18190,7 +18190,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18267,7 +18267,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18344,7 +18344,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18421,7 +18421,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18498,7 +18498,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18575,7 +18575,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18652,7 +18652,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18729,7 +18729,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -18806,7 +18806,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -18883,7 +18883,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -18960,7 +18960,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19037,7 +19037,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19191,7 +19191,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19268,7 +19268,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19345,7 +19345,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19422,7 +19422,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19499,7 +19499,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19576,7 +19576,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19653,7 +19653,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -19730,7 +19730,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -19807,7 +19807,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -19884,7 +19884,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -19961,7 +19961,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20038,7 +20038,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20115,7 +20115,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20192,7 +20192,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20269,7 +20269,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20346,7 +20346,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20423,7 +20423,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20500,7 +20500,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20577,7 +20577,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20654,7 +20654,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -20731,7 +20731,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -20808,7 +20808,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -20885,7 +20885,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -20962,7 +20962,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21047,7 +21047,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_sector_publico_e_instituciones.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_sector_publico_e_instituciones.xlsx
@@ -711,7 +711,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -865,7 +865,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -942,7 +942,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3483,7 +3483,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3868,7 +3868,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4099,7 +4099,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4253,7 +4253,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4407,7 +4407,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4484,7 +4484,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4792,7 +4792,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4869,7 +4869,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -4946,7 +4946,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5023,7 +5023,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5177,7 +5177,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5331,7 +5331,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5408,7 +5408,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5485,7 +5485,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5716,7 +5716,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5870,7 +5870,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -5947,7 +5947,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6024,7 +6024,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6255,7 +6255,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6332,7 +6332,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6409,7 +6409,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6717,7 +6717,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6794,7 +6794,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6871,7 +6871,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7025,7 +7025,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7102,7 +7102,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7179,7 +7179,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7256,7 +7256,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7410,7 +7410,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7487,7 +7487,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7564,7 +7564,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7641,7 +7641,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7795,7 +7795,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7872,7 +7872,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -7949,7 +7949,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8026,7 +8026,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8180,7 +8180,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8257,7 +8257,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8334,7 +8334,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8411,7 +8411,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8488,7 +8488,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8565,7 +8565,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8642,7 +8642,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8719,7 +8719,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8796,7 +8796,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8873,7 +8873,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -8950,7 +8950,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9104,7 +9104,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9181,7 +9181,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9258,7 +9258,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9335,7 +9335,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9489,7 +9489,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9566,7 +9566,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9643,7 +9643,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9720,7 +9720,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9797,7 +9797,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -9874,7 +9874,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -9951,7 +9951,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10028,7 +10028,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10105,7 +10105,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10182,7 +10182,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10259,7 +10259,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10336,7 +10336,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10413,7 +10413,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10490,7 +10490,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10567,7 +10567,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10644,7 +10644,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10721,7 +10721,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10798,7 +10798,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -10875,7 +10875,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11029,7 +11029,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11183,7 +11183,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11260,7 +11260,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11337,7 +11337,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11414,7 +11414,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11491,7 +11491,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11568,7 +11568,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11645,7 +11645,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11722,7 +11722,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11799,7 +11799,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -11876,7 +11876,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -11953,7 +11953,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12030,7 +12030,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12107,7 +12107,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12184,7 +12184,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12261,7 +12261,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12415,7 +12415,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12492,7 +12492,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12569,7 +12569,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12646,7 +12646,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12723,7 +12723,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12800,7 +12800,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -12877,7 +12877,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -12954,7 +12954,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13031,7 +13031,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13108,7 +13108,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13185,7 +13185,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13262,7 +13262,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13339,7 +13339,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13416,7 +13416,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13493,7 +13493,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13570,7 +13570,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13647,7 +13647,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13801,7 +13801,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -13878,7 +13878,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -13955,7 +13955,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14032,7 +14032,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14109,7 +14109,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14186,7 +14186,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14263,7 +14263,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14340,7 +14340,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14417,7 +14417,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14494,7 +14494,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14571,7 +14571,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14648,7 +14648,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14725,7 +14725,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -14802,7 +14802,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -14879,7 +14879,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -14956,7 +14956,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15033,7 +15033,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15110,7 +15110,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15187,7 +15187,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15264,7 +15264,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15341,7 +15341,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15418,7 +15418,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15495,7 +15495,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15572,7 +15572,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15649,7 +15649,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15726,7 +15726,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -15803,7 +15803,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -15880,7 +15880,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -15957,7 +15957,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16034,7 +16034,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16111,7 +16111,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16188,7 +16188,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16265,7 +16265,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16342,7 +16342,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16419,7 +16419,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16496,7 +16496,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16573,7 +16573,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16650,7 +16650,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16727,7 +16727,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -16804,7 +16804,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -16881,7 +16881,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -16958,7 +16958,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17035,7 +17035,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17112,7 +17112,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17189,7 +17189,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17266,7 +17266,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17420,7 +17420,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17497,7 +17497,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17574,7 +17574,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17651,7 +17651,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17728,7 +17728,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -17805,7 +17805,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -17882,7 +17882,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -17959,7 +17959,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18036,7 +18036,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18113,7 +18113,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18190,7 +18190,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18267,7 +18267,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18344,7 +18344,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18421,7 +18421,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18498,7 +18498,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18575,7 +18575,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18652,7 +18652,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18729,7 +18729,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -18806,7 +18806,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -18883,7 +18883,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -18960,7 +18960,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19037,7 +19037,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19191,7 +19191,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19268,7 +19268,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19345,7 +19345,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19422,7 +19422,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19499,7 +19499,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19576,7 +19576,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19653,7 +19653,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -19730,7 +19730,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -19807,7 +19807,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -19884,7 +19884,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -19961,7 +19961,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20038,7 +20038,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20115,7 +20115,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20192,7 +20192,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20269,7 +20269,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20346,7 +20346,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20423,7 +20423,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20500,7 +20500,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20577,7 +20577,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20654,7 +20654,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -20731,7 +20731,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -20808,7 +20808,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -20885,7 +20885,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -20962,7 +20962,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21047,7 +21047,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>

--- a/assets/data/world-bank/excel/ove_banco_mundial_venezuela_sector_publico_e_instituciones.xlsx
+++ b/assets/data/world-bank/excel/ove_banco_mundial_venezuela_sector_publico_e_instituciones.xlsx
@@ -711,7 +711,7 @@
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q7" s="4" t="n"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n"/>
@@ -865,7 +865,7 @@
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n"/>
@@ -942,7 +942,7 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n"/>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n"/>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n"/>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n"/>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n"/>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n"/>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n"/>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n"/>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n"/>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n"/>
@@ -1789,7 +1789,7 @@
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n"/>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n"/>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n"/>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n"/>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n"/>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n"/>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n"/>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n"/>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n"/>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n"/>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n"/>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n"/>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n"/>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n"/>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n"/>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n"/>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n"/>
@@ -3252,7 +3252,7 @@
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n"/>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n"/>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n"/>
@@ -3483,7 +3483,7 @@
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n"/>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n"/>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n"/>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n"/>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n"/>
@@ -3868,7 +3868,7 @@
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n"/>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n"/>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n"/>
@@ -4099,7 +4099,7 @@
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n"/>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n"/>
@@ -4253,7 +4253,7 @@
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n"/>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n"/>
@@ -4407,7 +4407,7 @@
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n"/>
@@ -4484,7 +4484,7 @@
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n"/>
@@ -4561,7 +4561,7 @@
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n"/>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n"/>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n"/>
@@ -4792,7 +4792,7 @@
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n"/>
@@ -4869,7 +4869,7 @@
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n"/>
@@ -4946,7 +4946,7 @@
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n"/>
@@ -5023,7 +5023,7 @@
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n"/>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n"/>
@@ -5177,7 +5177,7 @@
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n"/>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n"/>
@@ -5331,7 +5331,7 @@
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n"/>
@@ -5408,7 +5408,7 @@
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n"/>
@@ -5485,7 +5485,7 @@
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n"/>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n"/>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n"/>
@@ -5716,7 +5716,7 @@
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n"/>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n"/>
@@ -5870,7 +5870,7 @@
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n"/>
@@ -5947,7 +5947,7 @@
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n"/>
@@ -6024,7 +6024,7 @@
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n"/>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n"/>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n"/>
@@ -6255,7 +6255,7 @@
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n"/>
@@ -6332,7 +6332,7 @@
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n"/>
@@ -6409,7 +6409,7 @@
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n"/>
@@ -6486,7 +6486,7 @@
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n"/>
@@ -6563,7 +6563,7 @@
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n"/>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n"/>
@@ -6717,7 +6717,7 @@
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n"/>
@@ -6794,7 +6794,7 @@
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n"/>
@@ -6871,7 +6871,7 @@
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n"/>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n"/>
@@ -7025,7 +7025,7 @@
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n"/>
@@ -7102,7 +7102,7 @@
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n"/>
@@ -7179,7 +7179,7 @@
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n"/>
@@ -7256,7 +7256,7 @@
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n"/>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n"/>
@@ -7410,7 +7410,7 @@
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n"/>
@@ -7487,7 +7487,7 @@
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n"/>
@@ -7564,7 +7564,7 @@
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n"/>
@@ -7641,7 +7641,7 @@
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n"/>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n"/>
@@ -7795,7 +7795,7 @@
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n"/>
@@ -7872,7 +7872,7 @@
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n"/>
@@ -7949,7 +7949,7 @@
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n"/>
@@ -8026,7 +8026,7 @@
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n"/>
@@ -8103,7 +8103,7 @@
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n"/>
@@ -8180,7 +8180,7 @@
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n"/>
@@ -8257,7 +8257,7 @@
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n"/>
@@ -8334,7 +8334,7 @@
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n"/>
@@ -8411,7 +8411,7 @@
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n"/>
@@ -8488,7 +8488,7 @@
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n"/>
@@ -8565,7 +8565,7 @@
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n"/>
@@ -8642,7 +8642,7 @@
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n"/>
@@ -8719,7 +8719,7 @@
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n"/>
@@ -8796,7 +8796,7 @@
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n"/>
@@ -8873,7 +8873,7 @@
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n"/>
@@ -8950,7 +8950,7 @@
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n"/>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n"/>
@@ -9104,7 +9104,7 @@
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n"/>
@@ -9181,7 +9181,7 @@
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n"/>
@@ -9258,7 +9258,7 @@
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n"/>
@@ -9335,7 +9335,7 @@
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n"/>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n"/>
@@ -9489,7 +9489,7 @@
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n"/>
@@ -9566,7 +9566,7 @@
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n"/>
@@ -9643,7 +9643,7 @@
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n"/>
@@ -9720,7 +9720,7 @@
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n"/>
@@ -9797,7 +9797,7 @@
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n"/>
@@ -9874,7 +9874,7 @@
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n"/>
@@ -9951,7 +9951,7 @@
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n"/>
@@ -10028,7 +10028,7 @@
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n"/>
@@ -10105,7 +10105,7 @@
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n"/>
@@ -10182,7 +10182,7 @@
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n"/>
@@ -10259,7 +10259,7 @@
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n"/>
@@ -10336,7 +10336,7 @@
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n"/>
@@ -10413,7 +10413,7 @@
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n"/>
@@ -10490,7 +10490,7 @@
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n"/>
@@ -10567,7 +10567,7 @@
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n"/>
@@ -10644,7 +10644,7 @@
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n"/>
@@ -10721,7 +10721,7 @@
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n"/>
@@ -10798,7 +10798,7 @@
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n"/>
@@ -10875,7 +10875,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n"/>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n"/>
@@ -11029,7 +11029,7 @@
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n"/>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n"/>
@@ -11183,7 +11183,7 @@
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n"/>
@@ -11260,7 +11260,7 @@
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n"/>
@@ -11337,7 +11337,7 @@
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n"/>
@@ -11414,7 +11414,7 @@
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n"/>
@@ -11491,7 +11491,7 @@
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n"/>
@@ -11568,7 +11568,7 @@
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n"/>
@@ -11645,7 +11645,7 @@
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n"/>
@@ -11722,7 +11722,7 @@
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n"/>
@@ -11799,7 +11799,7 @@
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n"/>
@@ -11876,7 +11876,7 @@
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n"/>
@@ -11953,7 +11953,7 @@
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n"/>
@@ -12030,7 +12030,7 @@
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n"/>
@@ -12107,7 +12107,7 @@
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n"/>
@@ -12184,7 +12184,7 @@
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n"/>
@@ -12261,7 +12261,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n"/>
@@ -12338,7 +12338,7 @@
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n"/>
@@ -12415,7 +12415,7 @@
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n"/>
@@ -12492,7 +12492,7 @@
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n"/>
@@ -12569,7 +12569,7 @@
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n"/>
@@ -12646,7 +12646,7 @@
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n"/>
@@ -12723,7 +12723,7 @@
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n"/>
@@ -12800,7 +12800,7 @@
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n"/>
@@ -12877,7 +12877,7 @@
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n"/>
@@ -12954,7 +12954,7 @@
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n"/>
@@ -13031,7 +13031,7 @@
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n"/>
@@ -13108,7 +13108,7 @@
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n"/>
@@ -13185,7 +13185,7 @@
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n"/>
@@ -13262,7 +13262,7 @@
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n"/>
@@ -13339,7 +13339,7 @@
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n"/>
@@ -13416,7 +13416,7 @@
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n"/>
@@ -13493,7 +13493,7 @@
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n"/>
@@ -13570,7 +13570,7 @@
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n"/>
@@ -13647,7 +13647,7 @@
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n"/>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n"/>
@@ -13801,7 +13801,7 @@
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n"/>
@@ -13878,7 +13878,7 @@
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n"/>
@@ -13955,7 +13955,7 @@
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n"/>
@@ -14032,7 +14032,7 @@
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n"/>
@@ -14109,7 +14109,7 @@
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n"/>
@@ -14186,7 +14186,7 @@
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n"/>
@@ -14263,7 +14263,7 @@
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n"/>
@@ -14340,7 +14340,7 @@
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n"/>
@@ -14417,7 +14417,7 @@
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n"/>
@@ -14494,7 +14494,7 @@
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n"/>
@@ -14571,7 +14571,7 @@
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n"/>
@@ -14648,7 +14648,7 @@
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n"/>
@@ -14725,7 +14725,7 @@
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n"/>
@@ -14802,7 +14802,7 @@
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n"/>
@@ -14879,7 +14879,7 @@
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n"/>
@@ -14956,7 +14956,7 @@
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n"/>
@@ -15033,7 +15033,7 @@
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n"/>
@@ -15110,7 +15110,7 @@
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n"/>
@@ -15187,7 +15187,7 @@
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n"/>
@@ -15264,7 +15264,7 @@
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n"/>
@@ -15341,7 +15341,7 @@
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n"/>
@@ -15418,7 +15418,7 @@
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n"/>
@@ -15495,7 +15495,7 @@
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n"/>
@@ -15572,7 +15572,7 @@
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n"/>
@@ -15649,7 +15649,7 @@
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n"/>
@@ -15726,7 +15726,7 @@
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n"/>
@@ -15803,7 +15803,7 @@
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n"/>
@@ -15880,7 +15880,7 @@
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n"/>
@@ -15957,7 +15957,7 @@
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n"/>
@@ -16034,7 +16034,7 @@
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n"/>
@@ -16111,7 +16111,7 @@
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n"/>
@@ -16188,7 +16188,7 @@
       </c>
       <c r="P208" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q208" s="4" t="n"/>
@@ -16265,7 +16265,7 @@
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n"/>
@@ -16342,7 +16342,7 @@
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n"/>
@@ -16419,7 +16419,7 @@
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n"/>
@@ -16496,7 +16496,7 @@
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n"/>
@@ -16573,7 +16573,7 @@
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n"/>
@@ -16650,7 +16650,7 @@
       </c>
       <c r="P214" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q214" s="4" t="n"/>
@@ -16727,7 +16727,7 @@
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n"/>
@@ -16804,7 +16804,7 @@
       </c>
       <c r="P216" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q216" s="4" t="n"/>
@@ -16881,7 +16881,7 @@
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n"/>
@@ -16958,7 +16958,7 @@
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n"/>
@@ -17035,7 +17035,7 @@
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n"/>
@@ -17112,7 +17112,7 @@
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n"/>
@@ -17189,7 +17189,7 @@
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n"/>
@@ -17266,7 +17266,7 @@
       </c>
       <c r="P222" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q222" s="4" t="n"/>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="P223" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q223" s="4" t="n"/>
@@ -17420,7 +17420,7 @@
       </c>
       <c r="P224" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q224" s="4" t="n"/>
@@ -17497,7 +17497,7 @@
       </c>
       <c r="P225" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q225" s="4" t="n"/>
@@ -17574,7 +17574,7 @@
       </c>
       <c r="P226" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q226" s="4" t="n"/>
@@ -17651,7 +17651,7 @@
       </c>
       <c r="P227" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q227" s="4" t="n"/>
@@ -17728,7 +17728,7 @@
       </c>
       <c r="P228" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q228" s="4" t="n"/>
@@ -17805,7 +17805,7 @@
       </c>
       <c r="P229" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q229" s="4" t="n"/>
@@ -17882,7 +17882,7 @@
       </c>
       <c r="P230" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q230" s="4" t="n"/>
@@ -17959,7 +17959,7 @@
       </c>
       <c r="P231" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q231" s="4" t="n"/>
@@ -18036,7 +18036,7 @@
       </c>
       <c r="P232" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q232" s="4" t="n"/>
@@ -18113,7 +18113,7 @@
       </c>
       <c r="P233" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q233" s="4" t="n"/>
@@ -18190,7 +18190,7 @@
       </c>
       <c r="P234" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q234" s="4" t="n"/>
@@ -18267,7 +18267,7 @@
       </c>
       <c r="P235" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q235" s="4" t="n"/>
@@ -18344,7 +18344,7 @@
       </c>
       <c r="P236" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q236" s="4" t="n"/>
@@ -18421,7 +18421,7 @@
       </c>
       <c r="P237" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q237" s="4" t="n"/>
@@ -18498,7 +18498,7 @@
       </c>
       <c r="P238" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q238" s="4" t="n"/>
@@ -18575,7 +18575,7 @@
       </c>
       <c r="P239" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q239" s="4" t="n"/>
@@ -18652,7 +18652,7 @@
       </c>
       <c r="P240" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q240" s="4" t="n"/>
@@ -18729,7 +18729,7 @@
       </c>
       <c r="P241" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q241" s="4" t="n"/>
@@ -18806,7 +18806,7 @@
       </c>
       <c r="P242" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q242" s="4" t="n"/>
@@ -18883,7 +18883,7 @@
       </c>
       <c r="P243" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q243" s="4" t="n"/>
@@ -18960,7 +18960,7 @@
       </c>
       <c r="P244" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q244" s="4" t="n"/>
@@ -19037,7 +19037,7 @@
       </c>
       <c r="P245" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q245" s="4" t="n"/>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="P246" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q246" s="4" t="n"/>
@@ -19191,7 +19191,7 @@
       </c>
       <c r="P247" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q247" s="4" t="n"/>
@@ -19268,7 +19268,7 @@
       </c>
       <c r="P248" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q248" s="4" t="n"/>
@@ -19345,7 +19345,7 @@
       </c>
       <c r="P249" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q249" s="4" t="n"/>
@@ -19422,7 +19422,7 @@
       </c>
       <c r="P250" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q250" s="4" t="n"/>
@@ -19499,7 +19499,7 @@
       </c>
       <c r="P251" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q251" s="4" t="n"/>
@@ -19576,7 +19576,7 @@
       </c>
       <c r="P252" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q252" s="4" t="n"/>
@@ -19653,7 +19653,7 @@
       </c>
       <c r="P253" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q253" s="4" t="n"/>
@@ -19730,7 +19730,7 @@
       </c>
       <c r="P254" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q254" s="4" t="n"/>
@@ -19807,7 +19807,7 @@
       </c>
       <c r="P255" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q255" s="4" t="n"/>
@@ -19884,7 +19884,7 @@
       </c>
       <c r="P256" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q256" s="4" t="n"/>
@@ -19961,7 +19961,7 @@
       </c>
       <c r="P257" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q257" s="4" t="n"/>
@@ -20038,7 +20038,7 @@
       </c>
       <c r="P258" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q258" s="4" t="n"/>
@@ -20115,7 +20115,7 @@
       </c>
       <c r="P259" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q259" s="4" t="n"/>
@@ -20192,7 +20192,7 @@
       </c>
       <c r="P260" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q260" s="4" t="n"/>
@@ -20269,7 +20269,7 @@
       </c>
       <c r="P261" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q261" s="4" t="n"/>
@@ -20346,7 +20346,7 @@
       </c>
       <c r="P262" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q262" s="4" t="n"/>
@@ -20423,7 +20423,7 @@
       </c>
       <c r="P263" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q263" s="4" t="n"/>
@@ -20500,7 +20500,7 @@
       </c>
       <c r="P264" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q264" s="4" t="n"/>
@@ -20577,7 +20577,7 @@
       </c>
       <c r="P265" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q265" s="4" t="n"/>
@@ -20654,7 +20654,7 @@
       </c>
       <c r="P266" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q266" s="4" t="n"/>
@@ -20731,7 +20731,7 @@
       </c>
       <c r="P267" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q267" s="4" t="n"/>
@@ -20808,7 +20808,7 @@
       </c>
       <c r="P268" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q268" s="4" t="n"/>
@@ -20885,7 +20885,7 @@
       </c>
       <c r="P269" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q269" s="4" t="n"/>
@@ -20962,7 +20962,7 @@
       </c>
       <c r="P270" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="Q270" s="4" t="n"/>
@@ -21047,7 +21047,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
